--- a/xiuxian配置表/indir/境界.xlsx
+++ b/xiuxian配置表/indir/境界.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\godot\xiuxian\xiuxian配置表\indir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B886A0-3AC6-4A15-9C70-0F4F664EB3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C59509-7641-45F6-A22E-80CC1F74A029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="495" windowWidth="28650" windowHeight="9915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="5940" windowWidth="25260" windowHeight="11565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="z_realms" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="148">
   <si>
     <t>等级</t>
   </si>
@@ -361,9 +361,6 @@
   </si>
   <si>
     <t>渡劫十一层</t>
-  </si>
-  <si>
-    <t>速度</t>
   </si>
   <si>
     <t>roushen</t>
@@ -459,6 +456,38 @@
   </si>
   <si>
     <t>属性评分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力 = 灵力 * 5 + 80</t>
+  </si>
+  <si>
+    <t>物攻 = 肉身 * 2.5</t>
+  </si>
+  <si>
+    <t>法攻 = 灵力 * 2.3 + 神识 * 0.5</t>
+  </si>
+  <si>
+    <t>物防 = 肉身 * 1.2</t>
+  </si>
+  <si>
+    <t>法防 = 灵力 * 1.1 + 神识 * 0.8</t>
+  </si>
+  <si>
+    <t>出手速度 = 身法 * 2 + 神识 * 0.5 + 100</t>
+  </si>
+  <si>
+    <t>出手速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制强度 = 神识 * 1.6 + 灵力 * 0.5</t>
+  </si>
+  <si>
+    <t>控制抗性 = 肉身 * 1 + 神识 * 1.2</t>
+  </si>
+  <si>
+    <t>气血 = 肉身 * 10 + 80</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -518,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -527,6 +556,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -851,43 +883,43 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" t="s">
         <v>119</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>120</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>121</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>123</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q1" t="s">
         <v>124</v>
       </c>
-      <c r="P1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>125</v>
-      </c>
-      <c r="R1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -904,16 +936,16 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.15">
@@ -929,34 +961,73 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
       <c r="T3" t="s">
+        <v>136</v>
+      </c>
+      <c r="U3" t="s">
+        <v>132</v>
+      </c>
+      <c r="V3" t="s">
+        <v>133</v>
+      </c>
+      <c r="W3" t="s">
+        <v>134</v>
+      </c>
+      <c r="X3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y3" t="s">
         <v>137</v>
       </c>
-      <c r="U3" t="s">
-        <v>133</v>
-      </c>
-      <c r="V3" t="s">
-        <v>134</v>
-      </c>
-      <c r="W3" t="s">
-        <v>135</v>
-      </c>
-      <c r="X3" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="4" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="L4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -985,67 +1056,67 @@
         <v>10</v>
       </c>
       <c r="J5" s="3">
-        <f xml:space="preserve"> 50 +E5*10</f>
-        <v>150</v>
+        <f xml:space="preserve"> 80 +E5*10</f>
+        <v>180</v>
       </c>
       <c r="K5" s="3">
-        <f xml:space="preserve"> 50 +F5*5</f>
-        <v>75</v>
+        <f xml:space="preserve"> 80 +F5*5</f>
+        <v>105</v>
       </c>
       <c r="L5" s="3">
-        <f t="shared" ref="L5:L13" si="0" xml:space="preserve"> E5*2</f>
-        <v>20</v>
+        <f xml:space="preserve"> E5*2.5</f>
+        <v>25</v>
       </c>
       <c r="M5">
-        <f>F5*2.5+G5*0.8</f>
-        <v>16.5</v>
+        <f>F5*2.3+G5*0.5</f>
+        <v>14</v>
       </c>
       <c r="N5">
         <f>E5*1.2</f>
         <v>12</v>
       </c>
       <c r="O5">
-        <f>F5*1.2+G5*1.2</f>
-        <v>12</v>
+        <f>F5*1.1+G5*0.8</f>
+        <v>9.5</v>
       </c>
       <c r="P5">
-        <f xml:space="preserve"> 50+H5*3 + G5*1.5</f>
-        <v>87.5</v>
+        <f xml:space="preserve"> 100+H5*2 + G5*0.5</f>
+        <v>122.5</v>
       </c>
       <c r="Q5">
-        <f>G5*2+F5</f>
-        <v>15</v>
+        <f>G5*1.6+F5*0.5</f>
+        <v>10.5</v>
       </c>
       <c r="R5">
-        <f>G5*2 + E5</f>
-        <v>20</v>
+        <f>G5*1.2 + E5</f>
+        <v>16</v>
       </c>
       <c r="T5">
         <f>J5*(1+N5/1000*0.5 + O5/1000*0.5)*0.3</f>
-        <v>45.54</v>
+        <v>54.580500000000001</v>
       </c>
       <c r="U5">
         <f>(L5*0.5+M5*0.5)*P5/100*5</f>
-        <v>79.84375</v>
+        <v>119.4375</v>
       </c>
       <c r="V5">
         <f>Q5*P5/100*2</f>
-        <v>26.25</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="W5">
         <f>R5*1.5</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="X5">
         <f>K5*0.3</f>
-        <v>22.5</v>
+        <v>31.5</v>
       </c>
       <c r="Y5">
         <f>FLOOR(SUM(T5:X5),1)</f>
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="AA5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1074,67 +1145,67 @@
         <v>11</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" ref="J6:J15" si="1" xml:space="preserve"> 50 +E6*10</f>
-        <v>170</v>
+        <f t="shared" ref="J6:J69" si="0" xml:space="preserve"> 80 +E6*10</f>
+        <v>200</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" ref="K6:K15" si="2" xml:space="preserve"> 50 +F6*5</f>
-        <v>80</v>
+        <f t="shared" ref="K6:K69" si="1" xml:space="preserve"> 80 +F6*5</f>
+        <v>110</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" ref="L6:L15" si="3" xml:space="preserve"> E6*2</f>
-        <v>24</v>
+        <f t="shared" ref="L6:L69" si="2" xml:space="preserve"> E6*2.5</f>
+        <v>30</v>
       </c>
       <c r="M6">
-        <f t="shared" ref="M6:M15" si="4">F6*2.5+G6*0.8</f>
-        <v>19.8</v>
+        <f t="shared" ref="M6:M69" si="3">F6*2.3+G6*0.5</f>
+        <v>16.799999999999997</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:N15" si="5">E6*1.2</f>
+        <f t="shared" ref="N6:N69" si="4">E6*1.2</f>
         <v>14.399999999999999</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O15" si="6">F6*1.2+G6*1.2</f>
-        <v>14.399999999999999</v>
+        <f t="shared" ref="O6:O69" si="5">F6*1.1+G6*0.8</f>
+        <v>11.400000000000002</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:P15" si="7" xml:space="preserve"> 50+H6*3 + G6*1.5</f>
-        <v>92</v>
+        <f t="shared" ref="P6:P69" si="6" xml:space="preserve"> 100+H6*2 + G6*0.5</f>
+        <v>125</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q15" si="8">G6*2+F6</f>
-        <v>18</v>
+        <f t="shared" ref="Q6:Q69" si="7">G6*1.6+F6*0.5</f>
+        <v>12.600000000000001</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R6:R15" si="9">G6*2 + E6</f>
-        <v>24</v>
+        <f t="shared" ref="R6:R69" si="8">G6*1.2 + E6</f>
+        <v>19.2</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T15" si="10">J6*(1+N6/1000*0.5 + O6/1000*0.5)*0.3</f>
-        <v>51.734400000000008</v>
+        <f t="shared" ref="T6:T15" si="9">J6*(1+N6/1000*0.5 + O6/1000*0.5)*0.3</f>
+        <v>60.774000000000008</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U15" si="11">(L6*0.5+M6*0.5)*P6/100*5</f>
-        <v>100.74</v>
+        <f t="shared" ref="U6:U15" si="10">(L6*0.5+M6*0.5)*P6/100*5</f>
+        <v>146.25</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V15" si="12">Q6*P6/100*2</f>
-        <v>33.119999999999997</v>
+        <f t="shared" ref="V6:V15" si="11">Q6*P6/100*2</f>
+        <v>31.500000000000004</v>
       </c>
       <c r="W6">
-        <f t="shared" ref="W6:W15" si="13">R6*1.5</f>
-        <v>36</v>
+        <f t="shared" ref="W6:W15" si="12">R6*1.5</f>
+        <v>28.799999999999997</v>
       </c>
       <c r="X6">
-        <f t="shared" ref="X6:X15" si="14">K6*0.3</f>
-        <v>24</v>
+        <f t="shared" ref="X6:X15" si="13">K6*0.3</f>
+        <v>33</v>
       </c>
       <c r="Y6">
-        <f t="shared" ref="Y6:Y63" si="15">FLOOR(SUM(T6:X6),1)</f>
-        <v>245</v>
+        <f t="shared" ref="Y6:Y63" si="14">FLOOR(SUM(T6:X6),1)</f>
+        <v>300</v>
       </c>
       <c r="AA6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1163,67 +1234,67 @@
         <v>12</v>
       </c>
       <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="K7" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
-      </c>
-      <c r="K7" s="3">
+        <v>115</v>
+      </c>
+      <c r="L7" s="3">
         <f t="shared" si="2"/>
-        <v>85</v>
-      </c>
-      <c r="L7" s="3">
+        <v>35</v>
+      </c>
+      <c r="M7">
         <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="M7">
+        <v>19.599999999999998</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="4"/>
-        <v>23.1</v>
-      </c>
-      <c r="N7">
+        <v>16.8</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="5"/>
-        <v>16.8</v>
-      </c>
-      <c r="O7">
+        <v>13.3</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="6"/>
-        <v>16.8</v>
-      </c>
-      <c r="P7">
+        <v>127.5</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="7"/>
-        <v>96.5</v>
-      </c>
-      <c r="Q7">
+        <v>14.700000000000001</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="R7">
+        <v>22.4</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="9"/>
-        <v>28</v>
-      </c>
-      <c r="T7">
+        <v>66.993300000000005</v>
+      </c>
+      <c r="U7">
         <f t="shared" si="10"/>
-        <v>57.957599999999992</v>
-      </c>
-      <c r="U7">
+        <v>174.03749999999999</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="11"/>
-        <v>123.27875</v>
-      </c>
-      <c r="V7">
+        <v>37.485000000000007</v>
+      </c>
+      <c r="W7">
         <f t="shared" si="12"/>
-        <v>40.53</v>
-      </c>
-      <c r="W7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="X7">
         <f t="shared" si="13"/>
-        <v>42</v>
-      </c>
-      <c r="X7">
+        <v>34.5</v>
+      </c>
+      <c r="Y7">
         <f t="shared" si="14"/>
-        <v>25.5</v>
-      </c>
-      <c r="Y7">
-        <f t="shared" si="15"/>
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="AA7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1252,67 +1323,67 @@
         <v>13</v>
       </c>
       <c r="J8" s="3">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="K8" s="3">
         <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="K8" s="3">
+        <v>120</v>
+      </c>
+      <c r="L8" s="3">
         <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="L8" s="3">
+        <v>40</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="M8">
+        <v>22.4</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="4"/>
-        <v>26.4</v>
-      </c>
-      <c r="N8">
+        <v>19.2</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="5"/>
-        <v>19.2</v>
-      </c>
-      <c r="O8">
+        <v>15.200000000000001</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="6"/>
-        <v>19.2</v>
-      </c>
-      <c r="P8">
+        <v>130</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="7"/>
-        <v>101</v>
-      </c>
-      <c r="Q8">
+        <v>16.8</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="8"/>
-        <v>24</v>
-      </c>
-      <c r="R8">
+        <v>25.6</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="9"/>
-        <v>32</v>
-      </c>
-      <c r="T8">
+        <v>73.238399999999999</v>
+      </c>
+      <c r="U8">
         <f t="shared" si="10"/>
-        <v>64.209599999999995</v>
-      </c>
-      <c r="U8">
+        <v>202.8</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="11"/>
-        <v>147.45999999999998</v>
-      </c>
-      <c r="V8">
+        <v>43.68</v>
+      </c>
+      <c r="W8">
         <f t="shared" si="12"/>
-        <v>48.48</v>
-      </c>
-      <c r="W8">
+        <v>38.400000000000006</v>
+      </c>
+      <c r="X8">
         <f t="shared" si="13"/>
-        <v>48</v>
-      </c>
-      <c r="X8">
+        <v>36</v>
+      </c>
+      <c r="Y8">
         <f t="shared" si="14"/>
-        <v>27</v>
-      </c>
-      <c r="Y8">
-        <f t="shared" si="15"/>
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="AA8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1341,64 +1412,64 @@
         <v>14</v>
       </c>
       <c r="J9" s="3">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="K9" s="3">
         <f t="shared" si="1"/>
-        <v>230</v>
-      </c>
-      <c r="K9" s="3">
+        <v>125</v>
+      </c>
+      <c r="L9" s="3">
         <f t="shared" si="2"/>
-        <v>95</v>
-      </c>
-      <c r="L9" s="3">
+        <v>45</v>
+      </c>
+      <c r="M9">
         <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="M9">
+        <v>25.2</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="4"/>
-        <v>29.7</v>
-      </c>
-      <c r="N9">
+        <v>21.599999999999998</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="5"/>
-        <v>21.599999999999998</v>
-      </c>
-      <c r="O9">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="6"/>
-        <v>21.599999999999998</v>
-      </c>
-      <c r="P9">
+        <v>132.5</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="7"/>
-        <v>105.5</v>
-      </c>
-      <c r="Q9">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="8"/>
-        <v>27</v>
-      </c>
-      <c r="R9">
+        <v>28.799999999999997</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="9"/>
-        <v>36</v>
-      </c>
-      <c r="T9">
+        <v>79.509299999999996</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="10"/>
-        <v>70.49039999999998</v>
-      </c>
-      <c r="U9">
+        <v>232.53749999999999</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="11"/>
-        <v>173.28375</v>
-      </c>
-      <c r="V9">
+        <v>50.085000000000001</v>
+      </c>
+      <c r="W9">
         <f t="shared" si="12"/>
-        <v>56.97</v>
-      </c>
-      <c r="W9">
+        <v>43.199999999999996</v>
+      </c>
+      <c r="X9">
         <f t="shared" si="13"/>
-        <v>54</v>
-      </c>
-      <c r="X9">
+        <v>37.5</v>
+      </c>
+      <c r="Y9">
         <f t="shared" si="14"/>
-        <v>28.5</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="15"/>
-        <v>383</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1427,64 +1498,64 @@
         <v>15</v>
       </c>
       <c r="J10" s="3">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="K10" s="3">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="K10" s="3">
+        <v>130</v>
+      </c>
+      <c r="L10" s="3">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="L10" s="3">
+        <v>50</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="M10">
+        <v>28</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="4"/>
-        <v>33</v>
-      </c>
-      <c r="N10">
+        <v>24</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="6"/>
-        <v>24</v>
-      </c>
-      <c r="P10">
+        <v>135</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="7"/>
-        <v>110</v>
-      </c>
-      <c r="Q10">
+        <v>21</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="8"/>
-        <v>30</v>
-      </c>
-      <c r="R10">
+        <v>32</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="9"/>
-        <v>40</v>
-      </c>
-      <c r="T10">
+        <v>85.806000000000012</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="10"/>
-        <v>76.8</v>
-      </c>
-      <c r="U10">
+        <v>263.25</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="11"/>
-        <v>200.75</v>
-      </c>
-      <c r="V10">
+        <v>56.7</v>
+      </c>
+      <c r="W10">
         <f t="shared" si="12"/>
-        <v>66</v>
-      </c>
-      <c r="W10">
+        <v>48</v>
+      </c>
+      <c r="X10">
         <f t="shared" si="13"/>
-        <v>60</v>
-      </c>
-      <c r="X10">
+        <v>39</v>
+      </c>
+      <c r="Y10">
         <f t="shared" si="14"/>
-        <v>30</v>
-      </c>
-      <c r="Y10">
-        <f t="shared" si="15"/>
-        <v>433</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1513,64 +1584,64 @@
         <v>16</v>
       </c>
       <c r="J11" s="3">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="K11" s="3">
         <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="K11" s="3">
+        <v>135</v>
+      </c>
+      <c r="L11" s="3">
         <f t="shared" si="2"/>
-        <v>105</v>
-      </c>
-      <c r="L11" s="3">
+        <v>55</v>
+      </c>
+      <c r="M11">
         <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="M11">
+        <v>30.799999999999997</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="4"/>
-        <v>36.299999999999997</v>
-      </c>
-      <c r="N11">
+        <v>26.4</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="5"/>
-        <v>26.4</v>
-      </c>
-      <c r="O11">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="6"/>
-        <v>26.4</v>
-      </c>
-      <c r="P11">
+        <v>137.5</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="7"/>
-        <v>114.5</v>
-      </c>
-      <c r="Q11">
+        <v>23.1</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="8"/>
-        <v>33</v>
-      </c>
-      <c r="R11">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="9"/>
-        <v>44</v>
-      </c>
-      <c r="T11">
+        <v>92.128500000000003</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="10"/>
-        <v>83.138400000000004</v>
-      </c>
-      <c r="U11">
+        <v>294.9375</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="11"/>
-        <v>229.85874999999999</v>
-      </c>
-      <c r="V11">
+        <v>63.524999999999999</v>
+      </c>
+      <c r="W11">
         <f t="shared" si="12"/>
-        <v>75.569999999999993</v>
-      </c>
-      <c r="W11">
+        <v>52.800000000000004</v>
+      </c>
+      <c r="X11">
         <f t="shared" si="13"/>
-        <v>66</v>
-      </c>
-      <c r="X11">
+        <v>40.5</v>
+      </c>
+      <c r="Y11">
         <f t="shared" si="14"/>
-        <v>31.5</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="15"/>
-        <v>486</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1599,64 +1670,64 @@
         <v>17</v>
       </c>
       <c r="J12" s="3">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="K12" s="3">
         <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="K12" s="3">
+        <v>140</v>
+      </c>
+      <c r="L12" s="3">
         <f t="shared" si="2"/>
-        <v>110</v>
-      </c>
-      <c r="L12" s="3">
+        <v>60</v>
+      </c>
+      <c r="M12">
         <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="M12">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="4"/>
-        <v>39.6</v>
-      </c>
-      <c r="N12">
+        <v>28.799999999999997</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="5"/>
-        <v>28.799999999999997</v>
-      </c>
-      <c r="O12">
+        <v>22.800000000000004</v>
+      </c>
+      <c r="P12">
         <f t="shared" si="6"/>
-        <v>28.799999999999997</v>
-      </c>
-      <c r="P12">
+        <v>140</v>
+      </c>
+      <c r="Q12">
         <f t="shared" si="7"/>
-        <v>119</v>
-      </c>
-      <c r="Q12">
+        <v>25.200000000000003</v>
+      </c>
+      <c r="R12">
         <f t="shared" si="8"/>
-        <v>36</v>
-      </c>
-      <c r="R12">
+        <v>38.4</v>
+      </c>
+      <c r="T12">
         <f t="shared" si="9"/>
-        <v>48</v>
-      </c>
-      <c r="T12">
+        <v>98.476800000000011</v>
+      </c>
+      <c r="U12">
         <f t="shared" si="10"/>
-        <v>89.505599999999987</v>
-      </c>
-      <c r="U12">
+        <v>327.59999999999997</v>
+      </c>
+      <c r="V12">
         <f t="shared" si="11"/>
-        <v>260.61</v>
-      </c>
-      <c r="V12">
+        <v>70.56</v>
+      </c>
+      <c r="W12">
         <f t="shared" si="12"/>
-        <v>85.68</v>
-      </c>
-      <c r="W12">
+        <v>57.599999999999994</v>
+      </c>
+      <c r="X12">
         <f t="shared" si="13"/>
-        <v>72</v>
-      </c>
-      <c r="X12">
+        <v>42</v>
+      </c>
+      <c r="Y12">
         <f t="shared" si="14"/>
-        <v>33</v>
-      </c>
-      <c r="Y12">
-        <f t="shared" si="15"/>
-        <v>540</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1685,64 +1756,64 @@
         <v>18</v>
       </c>
       <c r="J13" s="3">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="K13" s="3">
         <f t="shared" si="1"/>
-        <v>310</v>
-      </c>
-      <c r="K13" s="3">
+        <v>145</v>
+      </c>
+      <c r="L13" s="3">
         <f t="shared" si="2"/>
-        <v>115</v>
-      </c>
-      <c r="L13" s="3">
+        <v>65</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="M13">
+        <v>36.4</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="4"/>
-        <v>42.9</v>
-      </c>
-      <c r="N13">
+        <v>31.2</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="5"/>
-        <v>31.2</v>
-      </c>
-      <c r="O13">
+        <v>24.700000000000003</v>
+      </c>
+      <c r="P13">
         <f t="shared" si="6"/>
-        <v>31.2</v>
-      </c>
-      <c r="P13">
+        <v>142.5</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="7"/>
-        <v>123.5</v>
-      </c>
-      <c r="Q13">
+        <v>27.3</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="8"/>
-        <v>39</v>
-      </c>
-      <c r="R13">
+        <v>41.6</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="9"/>
-        <v>52</v>
-      </c>
-      <c r="T13">
+        <v>104.85090000000001</v>
+      </c>
+      <c r="U13">
         <f t="shared" si="10"/>
-        <v>95.901600000000002</v>
-      </c>
-      <c r="U13">
+        <v>361.23750000000001</v>
+      </c>
+      <c r="V13">
         <f t="shared" si="11"/>
-        <v>293.00375000000003</v>
-      </c>
-      <c r="V13">
+        <v>77.805000000000007</v>
+      </c>
+      <c r="W13">
         <f t="shared" si="12"/>
-        <v>96.33</v>
-      </c>
-      <c r="W13">
+        <v>62.400000000000006</v>
+      </c>
+      <c r="X13">
         <f t="shared" si="13"/>
-        <v>78</v>
-      </c>
-      <c r="X13">
+        <v>43.5</v>
+      </c>
+      <c r="Y13">
         <f t="shared" si="14"/>
-        <v>34.5</v>
-      </c>
-      <c r="Y13">
-        <f t="shared" si="15"/>
-        <v>597</v>
+        <v>649</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1763,76 +1834,76 @@
         <v>78</v>
       </c>
       <c r="F14">
-        <f t="shared" ref="F14:H14" si="16">F13*3</f>
+        <f t="shared" ref="F14:H14" si="15">F13*3</f>
         <v>39</v>
       </c>
       <c r="G14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>39</v>
       </c>
       <c r="H14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>54</v>
       </c>
       <c r="J14" s="3">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="K14" s="3">
         <f t="shared" si="1"/>
-        <v>830</v>
-      </c>
-      <c r="K14" s="3">
+        <v>275</v>
+      </c>
+      <c r="L14" s="3">
         <f t="shared" si="2"/>
-        <v>245</v>
-      </c>
-      <c r="L14" s="3">
+        <v>195</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="3"/>
-        <v>156</v>
-      </c>
-      <c r="M14">
+        <v>109.19999999999999</v>
+      </c>
+      <c r="N14">
         <f t="shared" si="4"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="N14">
+        <v>93.6</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="5"/>
-        <v>93.6</v>
-      </c>
-      <c r="O14">
+        <v>74.100000000000009</v>
+      </c>
+      <c r="P14">
         <f t="shared" si="6"/>
-        <v>93.6</v>
-      </c>
-      <c r="P14">
+        <v>227.5</v>
+      </c>
+      <c r="Q14">
         <f t="shared" si="7"/>
-        <v>270.5</v>
-      </c>
-      <c r="Q14">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R14">
         <f t="shared" si="8"/>
-        <v>117</v>
-      </c>
-      <c r="R14">
+        <v>124.8</v>
+      </c>
+      <c r="T14">
         <f t="shared" si="9"/>
-        <v>156</v>
-      </c>
-      <c r="T14">
+        <v>279.63329999999996</v>
+      </c>
+      <c r="U14">
         <f t="shared" si="10"/>
-        <v>272.30639999999994</v>
-      </c>
-      <c r="U14">
+        <v>1730.1374999999998</v>
+      </c>
+      <c r="V14">
         <f t="shared" si="11"/>
-        <v>1925.2837499999998</v>
-      </c>
-      <c r="V14">
+        <v>372.64499999999998</v>
+      </c>
+      <c r="W14">
         <f t="shared" si="12"/>
-        <v>632.97</v>
-      </c>
-      <c r="W14">
+        <v>187.2</v>
+      </c>
+      <c r="X14">
         <f t="shared" si="13"/>
-        <v>234</v>
-      </c>
-      <c r="X14">
+        <v>82.5</v>
+      </c>
+      <c r="Y14">
         <f t="shared" si="14"/>
-        <v>73.5</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="15"/>
-        <v>3138</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1865,64 +1936,64 @@
         <v>55</v>
       </c>
       <c r="J15" s="3">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="K15" s="3">
         <f t="shared" si="1"/>
-        <v>870</v>
-      </c>
-      <c r="K15" s="3">
+        <v>285</v>
+      </c>
+      <c r="L15" s="3">
         <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="L15" s="3">
+        <v>205</v>
+      </c>
+      <c r="M15">
         <f t="shared" si="3"/>
-        <v>164</v>
-      </c>
-      <c r="M15">
+        <v>114.8</v>
+      </c>
+      <c r="N15">
         <f t="shared" si="4"/>
-        <v>135.30000000000001</v>
-      </c>
-      <c r="N15">
+        <v>98.399999999999991</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="5"/>
-        <v>98.399999999999991</v>
-      </c>
-      <c r="O15">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="P15">
         <f t="shared" si="6"/>
-        <v>98.399999999999991</v>
-      </c>
-      <c r="P15">
+        <v>230.5</v>
+      </c>
+      <c r="Q15">
         <f t="shared" si="7"/>
-        <v>276.5</v>
-      </c>
-      <c r="Q15">
+        <v>86.100000000000009</v>
+      </c>
+      <c r="R15">
         <f t="shared" si="8"/>
-        <v>123</v>
-      </c>
-      <c r="R15">
+        <v>131.19999999999999</v>
+      </c>
+      <c r="T15">
         <f t="shared" si="9"/>
-        <v>164</v>
-      </c>
-      <c r="T15">
+        <v>293.80049999999994</v>
+      </c>
+      <c r="U15">
         <f t="shared" si="10"/>
-        <v>286.68239999999992</v>
-      </c>
-      <c r="U15">
+        <v>1842.8475000000003</v>
+      </c>
+      <c r="V15">
         <f t="shared" si="11"/>
-        <v>2068.9112500000001</v>
-      </c>
-      <c r="V15">
+        <v>396.92100000000005</v>
+      </c>
+      <c r="W15">
         <f t="shared" si="12"/>
-        <v>680.19</v>
-      </c>
-      <c r="W15">
+        <v>196.79999999999998</v>
+      </c>
+      <c r="X15">
         <f t="shared" si="13"/>
-        <v>246</v>
-      </c>
-      <c r="X15">
+        <v>85.5</v>
+      </c>
+      <c r="Y15">
         <f t="shared" si="14"/>
-        <v>76.5</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="15"/>
-        <v>3358</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15.75" x14ac:dyDescent="0.3">
@@ -1939,80 +2010,80 @@
         <v>5933</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16:E23" si="17">E15+4</f>
+        <f t="shared" ref="E16:E23" si="16">E15+4</f>
         <v>86</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F16:F23" si="18">F15+2</f>
+        <f t="shared" ref="F16:F23" si="17">F15+2</f>
         <v>43</v>
       </c>
       <c r="G16">
-        <f t="shared" ref="G16:G23" si="19">G15+2</f>
+        <f t="shared" ref="G16:G23" si="18">G15+2</f>
         <v>43</v>
       </c>
       <c r="H16">
-        <f t="shared" ref="H16:H23" si="20">H15+1</f>
+        <f t="shared" ref="H16:H23" si="19">H15+1</f>
         <v>56</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16:J24" si="21" xml:space="preserve"> 50 +E16*10</f>
-        <v>910</v>
+        <f t="shared" si="0"/>
+        <v>940</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" ref="K16:K23" si="22" xml:space="preserve"> 50 +F16*5</f>
-        <v>265</v>
+        <f t="shared" si="1"/>
+        <v>295</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" ref="L16:L24" si="23" xml:space="preserve"> E16*2</f>
-        <v>172</v>
+        <f t="shared" si="2"/>
+        <v>215</v>
       </c>
       <c r="M16">
-        <f t="shared" ref="M16:M23" si="24">F16*2.5+G16*0.8</f>
-        <v>141.9</v>
+        <f t="shared" si="3"/>
+        <v>120.39999999999999</v>
       </c>
       <c r="N16">
-        <f t="shared" ref="N16:N24" si="25">E16*1.2</f>
+        <f t="shared" si="4"/>
         <v>103.2</v>
       </c>
       <c r="O16">
-        <f t="shared" ref="O16:O23" si="26">F16*1.2+G16*1.2</f>
-        <v>103.2</v>
+        <f t="shared" si="5"/>
+        <v>81.7</v>
       </c>
       <c r="P16">
-        <f t="shared" ref="P16:P23" si="27" xml:space="preserve"> 50+H16*3 + G16*1.5</f>
-        <v>282.5</v>
+        <f t="shared" si="6"/>
+        <v>233.5</v>
       </c>
       <c r="Q16">
-        <f t="shared" ref="Q16:Q23" si="28">G16*2+F16</f>
-        <v>129</v>
+        <f t="shared" si="7"/>
+        <v>90.3</v>
       </c>
       <c r="R16">
-        <f t="shared" ref="R16:R23" si="29">G16*2 + E16</f>
-        <v>172</v>
+        <f t="shared" si="8"/>
+        <v>137.6</v>
       </c>
       <c r="T16">
-        <f t="shared" ref="T16:T23" si="30">J16*(1+N16/1000*0.5 + O16/1000*0.5)*0.3</f>
-        <v>301.17360000000002</v>
+        <f t="shared" ref="T16:T23" si="20">J16*(1+N16/1000*0.5 + O16/1000*0.5)*0.3</f>
+        <v>308.07090000000005</v>
       </c>
       <c r="U16">
-        <f t="shared" ref="U16:U23" si="31">(L16*0.5+M16*0.5)*P16/100*5</f>
-        <v>2216.9187500000003</v>
+        <f t="shared" ref="U16:U23" si="21">(L16*0.5+M16*0.5)*P16/100*5</f>
+        <v>1957.8975</v>
       </c>
       <c r="V16">
-        <f t="shared" ref="V16:V23" si="32">Q16*P16/100*2</f>
-        <v>728.85</v>
+        <f t="shared" ref="V16:V23" si="22">Q16*P16/100*2</f>
+        <v>421.70099999999996</v>
       </c>
       <c r="W16">
-        <f t="shared" ref="W16:W23" si="33">R16*1.5</f>
-        <v>258</v>
+        <f t="shared" ref="W16:W23" si="23">R16*1.5</f>
+        <v>206.39999999999998</v>
       </c>
       <c r="X16">
-        <f t="shared" ref="X16:X23" si="34">K16*0.3</f>
-        <v>79.5</v>
+        <f t="shared" ref="X16:X23" si="24">K16*0.3</f>
+        <v>88.5</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="15"/>
-        <v>3584</v>
+        <f t="shared" si="14"/>
+        <v>2982</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2029,81 +2100,81 @@
         <v>6900</v>
       </c>
       <c r="E17">
+        <f t="shared" si="16"/>
+        <v>90</v>
+      </c>
+      <c r="F17">
         <f t="shared" si="17"/>
-        <v>90</v>
-      </c>
-      <c r="F17">
+        <v>45</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="18"/>
         <v>45</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <f t="shared" si="19"/>
-        <v>45</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="20"/>
         <v>57</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="3">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="1"/>
+        <v>305</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="2"/>
+        <v>225</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>125.99999999999999</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="4"/>
+        <v>108</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="5"/>
+        <v>85.5</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="6"/>
+        <v>236.5</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="7"/>
+        <v>94.5</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="8"/>
+        <v>144</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="20"/>
+        <v>322.44450000000001</v>
+      </c>
+      <c r="U17">
         <f t="shared" si="21"/>
-        <v>950</v>
-      </c>
-      <c r="K17" s="3">
+        <v>2075.2874999999999</v>
+      </c>
+      <c r="V17">
         <f t="shared" si="22"/>
-        <v>275</v>
-      </c>
-      <c r="L17" s="3">
+        <v>446.98500000000001</v>
+      </c>
+      <c r="W17">
         <f t="shared" si="23"/>
-        <v>180</v>
-      </c>
-      <c r="M17">
+        <v>216</v>
+      </c>
+      <c r="X17">
         <f t="shared" si="24"/>
-        <v>148.5</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="25"/>
-        <v>108</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="26"/>
-        <v>108</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="27"/>
-        <v>288.5</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="28"/>
-        <v>135</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="29"/>
-        <v>180</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="30"/>
-        <v>315.78000000000003</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="31"/>
-        <v>2369.3062500000001</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="32"/>
-        <v>778.95</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="33"/>
-        <v>270</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="34"/>
-        <v>82.5</v>
+        <v>91.5</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="15"/>
-        <v>3816</v>
+        <f t="shared" si="14"/>
+        <v>3152</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2120,81 +2191,81 @@
         <v>8067</v>
       </c>
       <c r="E18">
+        <f t="shared" si="16"/>
+        <v>94</v>
+      </c>
+      <c r="F18">
         <f t="shared" si="17"/>
-        <v>94</v>
-      </c>
-      <c r="F18">
+        <v>47</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="18"/>
         <v>47</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <f t="shared" si="19"/>
-        <v>47</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="20"/>
         <v>58</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="3">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="2"/>
+        <v>235</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>131.6</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="4"/>
+        <v>112.8</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="5"/>
+        <v>89.300000000000011</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="6"/>
+        <v>239.5</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="7"/>
+        <v>98.7</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="8"/>
+        <v>150.4</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="20"/>
+        <v>336.92130000000003</v>
+      </c>
+      <c r="U18">
         <f t="shared" si="21"/>
-        <v>990</v>
-      </c>
-      <c r="K18" s="3">
+        <v>2195.0174999999999</v>
+      </c>
+      <c r="V18">
         <f t="shared" si="22"/>
-        <v>285</v>
-      </c>
-      <c r="L18" s="3">
+        <v>472.77300000000002</v>
+      </c>
+      <c r="W18">
         <f t="shared" si="23"/>
-        <v>188</v>
-      </c>
-      <c r="M18">
+        <v>225.60000000000002</v>
+      </c>
+      <c r="X18">
         <f t="shared" si="24"/>
-        <v>155.1</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="25"/>
-        <v>112.8</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="26"/>
-        <v>112.8</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="27"/>
-        <v>294.5</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="28"/>
-        <v>141</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="29"/>
-        <v>188</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="30"/>
-        <v>330.5016</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="31"/>
-        <v>2526.07375</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="32"/>
-        <v>830.49</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="33"/>
-        <v>282</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="34"/>
-        <v>85.5</v>
+        <v>94.5</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="15"/>
-        <v>4054</v>
+        <f t="shared" si="14"/>
+        <v>3324</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2211,81 +2282,81 @@
         <v>9233</v>
       </c>
       <c r="E19">
+        <f t="shared" si="16"/>
+        <v>98</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="17"/>
-        <v>98</v>
-      </c>
-      <c r="F19">
+        <v>49</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="18"/>
         <v>49</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <f t="shared" si="19"/>
-        <v>49</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="20"/>
         <v>59</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="3">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="1"/>
+        <v>325</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="2"/>
+        <v>245</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>137.19999999999999</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="4"/>
+        <v>117.6</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>93.100000000000009</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="6"/>
+        <v>242.5</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="7"/>
+        <v>102.9</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="8"/>
+        <v>156.80000000000001</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="20"/>
+        <v>351.50130000000001</v>
+      </c>
+      <c r="U19">
         <f t="shared" si="21"/>
-        <v>1030</v>
-      </c>
-      <c r="K19" s="3">
+        <v>2317.0875000000001</v>
+      </c>
+      <c r="V19">
         <f t="shared" si="22"/>
-        <v>295</v>
-      </c>
-      <c r="L19" s="3">
+        <v>499.065</v>
+      </c>
+      <c r="W19">
         <f t="shared" si="23"/>
-        <v>196</v>
-      </c>
-      <c r="M19">
+        <v>235.20000000000002</v>
+      </c>
+      <c r="X19">
         <f t="shared" si="24"/>
-        <v>161.69999999999999</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="25"/>
-        <v>117.6</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="26"/>
-        <v>117.6</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="27"/>
-        <v>300.5</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="28"/>
-        <v>147</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="29"/>
-        <v>196</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="30"/>
-        <v>345.33839999999998</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="31"/>
-        <v>2687.2212500000001</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="32"/>
-        <v>883.47</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="33"/>
-        <v>294</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="34"/>
-        <v>88.5</v>
+        <v>97.5</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="15"/>
-        <v>4298</v>
+        <f t="shared" si="14"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2302,81 +2373,81 @@
         <v>10400</v>
       </c>
       <c r="E20">
+        <f t="shared" si="16"/>
+        <v>102</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="17"/>
-        <v>102</v>
-      </c>
-      <c r="F20">
+        <v>51</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="18"/>
         <v>51</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f t="shared" si="19"/>
-        <v>51</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="20"/>
         <v>60</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="3">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="1"/>
+        <v>335</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="2"/>
+        <v>255</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>142.80000000000001</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="4"/>
+        <v>122.39999999999999</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="5"/>
+        <v>96.9</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="6"/>
+        <v>245.5</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="7"/>
+        <v>107.10000000000001</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="8"/>
+        <v>163.19999999999999</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="20"/>
+        <v>366.18450000000001</v>
+      </c>
+      <c r="U20">
         <f t="shared" si="21"/>
-        <v>1070</v>
-      </c>
-      <c r="K20" s="3">
+        <v>2441.4974999999999</v>
+      </c>
+      <c r="V20">
         <f t="shared" si="22"/>
-        <v>305</v>
-      </c>
-      <c r="L20" s="3">
+        <v>525.8610000000001</v>
+      </c>
+      <c r="W20">
         <f t="shared" si="23"/>
-        <v>204</v>
-      </c>
-      <c r="M20">
+        <v>244.79999999999998</v>
+      </c>
+      <c r="X20">
         <f t="shared" si="24"/>
-        <v>168.3</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="25"/>
-        <v>122.39999999999999</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="26"/>
-        <v>122.39999999999999</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="27"/>
-        <v>306.5</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="28"/>
-        <v>153</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="29"/>
-        <v>204</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="30"/>
-        <v>360.29039999999992</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="31"/>
-        <v>2852.7487500000002</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="32"/>
-        <v>937.89</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="33"/>
-        <v>306</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="34"/>
-        <v>91.5</v>
+        <v>100.5</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="15"/>
-        <v>4548</v>
+        <f t="shared" si="14"/>
+        <v>3678</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2393,81 +2464,81 @@
         <v>13025</v>
       </c>
       <c r="E21">
+        <f t="shared" si="16"/>
+        <v>106</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="17"/>
-        <v>106</v>
-      </c>
-      <c r="F21">
+        <v>53</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="18"/>
         <v>53</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f t="shared" si="19"/>
-        <v>53</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="20"/>
         <v>61</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="3">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="1"/>
+        <v>345</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="2"/>
+        <v>265</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>148.39999999999998</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="4"/>
+        <v>127.19999999999999</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="5"/>
+        <v>100.70000000000002</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="6"/>
+        <v>248.5</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="7"/>
+        <v>111.30000000000001</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="8"/>
+        <v>169.6</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="20"/>
+        <v>380.97089999999997</v>
+      </c>
+      <c r="U21">
         <f t="shared" si="21"/>
-        <v>1110</v>
-      </c>
-      <c r="K21" s="3">
+        <v>2568.2474999999999</v>
+      </c>
+      <c r="V21">
         <f t="shared" si="22"/>
-        <v>315</v>
-      </c>
-      <c r="L21" s="3">
+        <v>553.16100000000006</v>
+      </c>
+      <c r="W21">
         <f t="shared" si="23"/>
-        <v>212</v>
-      </c>
-      <c r="M21">
+        <v>254.39999999999998</v>
+      </c>
+      <c r="X21">
         <f t="shared" si="24"/>
-        <v>174.9</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="25"/>
-        <v>127.19999999999999</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="26"/>
-        <v>127.19999999999999</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="27"/>
-        <v>312.5</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="28"/>
-        <v>159</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="29"/>
-        <v>212</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="30"/>
-        <v>375.35760000000005</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="31"/>
-        <v>3022.65625</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="32"/>
-        <v>993.75</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="33"/>
-        <v>318</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="34"/>
-        <v>94.5</v>
+        <v>103.5</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="15"/>
-        <v>4804</v>
+        <f t="shared" si="14"/>
+        <v>3860</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2484,81 +2555,81 @@
         <v>15650</v>
       </c>
       <c r="E22">
+        <f t="shared" si="16"/>
+        <v>110</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="17"/>
-        <v>110</v>
-      </c>
-      <c r="F22">
+        <v>55</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="18"/>
         <v>55</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <f t="shared" si="19"/>
-        <v>55</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="20"/>
         <v>62</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="3">
+        <f t="shared" si="0"/>
+        <v>1180</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="1"/>
+        <v>355</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="2"/>
+        <v>275</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="3"/>
+        <v>154</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="4"/>
+        <v>132</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="5"/>
+        <v>104.5</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="6"/>
+        <v>251.5</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="7"/>
+        <v>115.5</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="8"/>
+        <v>176</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="20"/>
+        <v>395.86049999999994</v>
+      </c>
+      <c r="U22">
         <f t="shared" si="21"/>
-        <v>1150</v>
-      </c>
-      <c r="K22" s="3">
+        <v>2697.3374999999996</v>
+      </c>
+      <c r="V22">
         <f t="shared" si="22"/>
-        <v>325</v>
-      </c>
-      <c r="L22" s="3">
+        <v>580.96500000000003</v>
+      </c>
+      <c r="W22">
         <f t="shared" si="23"/>
-        <v>220</v>
-      </c>
-      <c r="M22">
+        <v>264</v>
+      </c>
+      <c r="X22">
         <f t="shared" si="24"/>
-        <v>181.5</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="25"/>
-        <v>132</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="26"/>
-        <v>132</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="27"/>
-        <v>318.5</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="28"/>
-        <v>165</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="29"/>
-        <v>220</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="30"/>
-        <v>390.54</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="31"/>
-        <v>3196.9437499999999</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="32"/>
-        <v>1051.05</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="33"/>
-        <v>330</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="34"/>
-        <v>97.5</v>
+        <v>106.5</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="15"/>
-        <v>5066</v>
+        <f t="shared" si="14"/>
+        <v>4044</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2575,81 +2646,81 @@
         <v>18275</v>
       </c>
       <c r="E23">
+        <f t="shared" si="16"/>
+        <v>114</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="17"/>
-        <v>114</v>
-      </c>
-      <c r="F23">
+        <v>57</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="18"/>
         <v>57</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <f t="shared" si="19"/>
-        <v>57</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="20"/>
         <v>63</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="3">
+        <f t="shared" si="0"/>
+        <v>1220</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="1"/>
+        <v>365</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="2"/>
+        <v>285</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="3"/>
+        <v>159.6</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="4"/>
+        <v>136.79999999999998</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="5"/>
+        <v>108.30000000000001</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="6"/>
+        <v>254.5</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="7"/>
+        <v>119.7</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="8"/>
+        <v>182.39999999999998</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="20"/>
+        <v>410.85329999999999</v>
+      </c>
+      <c r="U23">
         <f t="shared" si="21"/>
-        <v>1190</v>
-      </c>
-      <c r="K23" s="3">
+        <v>2828.7674999999999</v>
+      </c>
+      <c r="V23">
         <f t="shared" si="22"/>
-        <v>335</v>
-      </c>
-      <c r="L23" s="3">
+        <v>609.27300000000002</v>
+      </c>
+      <c r="W23">
         <f t="shared" si="23"/>
-        <v>228</v>
-      </c>
-      <c r="M23">
+        <v>273.59999999999997</v>
+      </c>
+      <c r="X23">
         <f t="shared" si="24"/>
-        <v>188.1</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="25"/>
-        <v>136.79999999999998</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="26"/>
-        <v>136.79999999999998</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="27"/>
-        <v>324.5</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="28"/>
-        <v>171</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="29"/>
-        <v>228</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="30"/>
-        <v>405.83760000000001</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="31"/>
-        <v>3375.6112499999999</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="32"/>
-        <v>1109.79</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="33"/>
-        <v>342</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="34"/>
-        <v>100.5</v>
+        <v>109.5</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="15"/>
-        <v>5333</v>
+        <f t="shared" si="14"/>
+        <v>4231</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2670,77 +2741,77 @@
         <v>285</v>
       </c>
       <c r="F24">
-        <f t="shared" ref="F24:H24" si="35">F23*2.5</f>
+        <f t="shared" ref="F24:H24" si="25">F23*2.5</f>
         <v>142.5</v>
       </c>
       <c r="G24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="25"/>
         <v>142.5</v>
       </c>
       <c r="H24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="25"/>
         <v>157.5</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:J35" si="36" xml:space="preserve"> 50 +E24*10</f>
-        <v>2900</v>
+        <f t="shared" si="0"/>
+        <v>2930</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" ref="K24:K33" si="37" xml:space="preserve"> 50 +F24*5</f>
-        <v>762.5</v>
+        <f t="shared" si="1"/>
+        <v>792.5</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" ref="L24:L35" si="38" xml:space="preserve"> E24*2</f>
-        <v>570</v>
+        <f t="shared" si="2"/>
+        <v>712.5</v>
       </c>
       <c r="M24">
-        <f t="shared" ref="M24:M33" si="39">F24*2.5+G24*0.8</f>
-        <v>470.25</v>
+        <f t="shared" si="3"/>
+        <v>399</v>
       </c>
       <c r="N24">
-        <f t="shared" ref="N24:N35" si="40">E24*1.2</f>
+        <f t="shared" si="4"/>
         <v>342</v>
       </c>
       <c r="O24">
-        <f t="shared" ref="O24:O33" si="41">F24*1.2+G24*1.2</f>
-        <v>342</v>
+        <f t="shared" si="5"/>
+        <v>270.75</v>
       </c>
       <c r="P24">
-        <f t="shared" ref="P24:P33" si="42" xml:space="preserve"> 50+H24*3 + G24*1.5</f>
-        <v>736.25</v>
+        <f t="shared" si="6"/>
+        <v>486.25</v>
       </c>
       <c r="Q24">
-        <f t="shared" ref="Q24:Q33" si="43">G24*2+F24</f>
-        <v>427.5</v>
+        <f t="shared" si="7"/>
+        <v>299.25</v>
       </c>
       <c r="R24">
-        <f t="shared" ref="R24:R33" si="44">G24*2 + E24</f>
-        <v>570</v>
+        <f t="shared" si="8"/>
+        <v>456</v>
       </c>
       <c r="T24">
-        <f t="shared" ref="T24:T33" si="45">J24*(1+N24/1000*0.5 + O24/1000*0.5)*0.3</f>
-        <v>1167.54</v>
+        <f t="shared" ref="T24:T33" si="26">J24*(1+N24/1000*0.5 + O24/1000*0.5)*0.3</f>
+        <v>1148.303625</v>
       </c>
       <c r="U24">
-        <f t="shared" ref="U24:U33" si="46">(L24*0.5+M24*0.5)*P24/100*5</f>
-        <v>19147.1015625</v>
+        <f t="shared" ref="U24:U33" si="27">(L24*0.5+M24*0.5)*P24/100*5</f>
+        <v>13511.671875</v>
       </c>
       <c r="V24">
-        <f t="shared" ref="V24:V33" si="47">Q24*P24/100*2</f>
-        <v>6294.9375</v>
+        <f t="shared" ref="V24:V33" si="28">Q24*P24/100*2</f>
+        <v>2910.2062500000002</v>
       </c>
       <c r="W24">
-        <f t="shared" ref="W24:W33" si="48">R24*1.5</f>
-        <v>855</v>
+        <f t="shared" ref="W24:W33" si="29">R24*1.5</f>
+        <v>684</v>
       </c>
       <c r="X24">
-        <f t="shared" ref="X24:X33" si="49">K24*0.3</f>
-        <v>228.75</v>
+        <f t="shared" ref="X24:X33" si="30">K24*0.3</f>
+        <v>237.75</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="15"/>
-        <v>27693</v>
+        <f t="shared" si="14"/>
+        <v>18491</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2774,64 +2845,64 @@
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="3">
-        <f t="shared" si="36"/>
-        <v>2970</v>
+        <f t="shared" si="0"/>
+        <v>3000</v>
       </c>
       <c r="K25" s="3">
-        <f t="shared" si="37"/>
-        <v>782.5</v>
+        <f t="shared" si="1"/>
+        <v>812.5</v>
       </c>
       <c r="L25" s="3">
-        <f t="shared" si="38"/>
-        <v>584</v>
+        <f t="shared" si="2"/>
+        <v>730</v>
       </c>
       <c r="M25">
-        <f t="shared" si="39"/>
-        <v>483.45</v>
+        <f t="shared" si="3"/>
+        <v>410.2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>350.4</v>
       </c>
       <c r="O25">
-        <f t="shared" si="41"/>
-        <v>351.59999999999997</v>
+        <f t="shared" si="5"/>
+        <v>278.35000000000002</v>
       </c>
       <c r="P25">
-        <f t="shared" si="42"/>
-        <v>754.25</v>
+        <f t="shared" si="6"/>
+        <v>496.25</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="43"/>
-        <v>439.5</v>
+        <f t="shared" si="7"/>
+        <v>307.64999999999998</v>
       </c>
       <c r="R25">
-        <f t="shared" si="44"/>
-        <v>585</v>
+        <f t="shared" si="8"/>
+        <v>467.79999999999995</v>
       </c>
       <c r="T25">
-        <f t="shared" si="45"/>
-        <v>1203.741</v>
+        <f t="shared" si="26"/>
+        <v>1182.9375</v>
       </c>
       <c r="U25">
-        <f t="shared" si="46"/>
-        <v>20128.104062499999</v>
+        <f t="shared" si="27"/>
+        <v>14145.606250000001</v>
       </c>
       <c r="V25">
-        <f t="shared" si="47"/>
-        <v>6629.8575000000001</v>
+        <f t="shared" si="28"/>
+        <v>3053.42625</v>
       </c>
       <c r="W25">
-        <f t="shared" si="48"/>
-        <v>877.5</v>
+        <f t="shared" si="29"/>
+        <v>701.69999999999993</v>
       </c>
       <c r="X25">
-        <f t="shared" si="49"/>
-        <v>234.75</v>
+        <f t="shared" si="30"/>
+        <v>243.75</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="15"/>
-        <v>29073</v>
+        <f t="shared" si="14"/>
+        <v>19327</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2848,81 +2919,81 @@
         <v>28433</v>
       </c>
       <c r="E26">
-        <f t="shared" ref="E26:E33" si="50">E25+7</f>
+        <f t="shared" ref="E26:E33" si="31">E25+7</f>
         <v>299</v>
       </c>
       <c r="F26">
-        <f t="shared" ref="F26:F33" si="51">F25+4</f>
+        <f t="shared" ref="F26:F33" si="32">F25+4</f>
         <v>150.5</v>
       </c>
       <c r="G26">
-        <f t="shared" ref="G26:G33" si="52">G25+4</f>
+        <f t="shared" ref="G26:G33" si="33">G25+4</f>
         <v>150.5</v>
       </c>
       <c r="H26">
-        <f t="shared" ref="H26:H33" si="53">H25+4</f>
+        <f t="shared" ref="H26:H33" si="34">H25+4</f>
         <v>165.5</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="3">
-        <f t="shared" si="36"/>
-        <v>3040</v>
+        <f t="shared" si="0"/>
+        <v>3070</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="37"/>
-        <v>802.5</v>
+        <f t="shared" si="1"/>
+        <v>832.5</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="38"/>
-        <v>598</v>
+        <f t="shared" si="2"/>
+        <v>747.5</v>
       </c>
       <c r="M26">
-        <f t="shared" si="39"/>
-        <v>496.65</v>
+        <f t="shared" si="3"/>
+        <v>421.4</v>
       </c>
       <c r="N26">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>358.8</v>
       </c>
       <c r="O26">
-        <f t="shared" si="41"/>
-        <v>361.2</v>
+        <f t="shared" si="5"/>
+        <v>285.95000000000005</v>
       </c>
       <c r="P26">
-        <f t="shared" si="42"/>
-        <v>772.25</v>
+        <f t="shared" si="6"/>
+        <v>506.25</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="43"/>
-        <v>451.5</v>
+        <f t="shared" si="7"/>
+        <v>316.05</v>
       </c>
       <c r="R26">
-        <f t="shared" si="44"/>
-        <v>600</v>
+        <f t="shared" si="8"/>
+        <v>479.6</v>
       </c>
       <c r="T26">
-        <f t="shared" si="45"/>
-        <v>1240.32</v>
+        <f t="shared" si="26"/>
+        <v>1217.907375</v>
       </c>
       <c r="U26">
-        <f t="shared" si="46"/>
-        <v>21133.586562500001</v>
+        <f t="shared" si="27"/>
+        <v>14793.890625</v>
       </c>
       <c r="V26">
-        <f t="shared" si="47"/>
-        <v>6973.4174999999996</v>
+        <f t="shared" si="28"/>
+        <v>3200.0062499999999</v>
       </c>
       <c r="W26">
-        <f t="shared" si="48"/>
-        <v>900</v>
+        <f t="shared" si="29"/>
+        <v>719.40000000000009</v>
       </c>
       <c r="X26">
-        <f t="shared" si="49"/>
-        <v>240.75</v>
+        <f t="shared" si="30"/>
+        <v>249.75</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="15"/>
-        <v>30488</v>
+        <f t="shared" si="14"/>
+        <v>20180</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -2939,81 +3010,81 @@
         <v>32200</v>
       </c>
       <c r="E27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>306</v>
       </c>
       <c r="F27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>154.5</v>
       </c>
       <c r="G27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>154.5</v>
       </c>
       <c r="H27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>169.5</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="3">
-        <f t="shared" si="36"/>
-        <v>3110</v>
+        <f t="shared" si="0"/>
+        <v>3140</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="37"/>
-        <v>822.5</v>
+        <f t="shared" si="1"/>
+        <v>852.5</v>
       </c>
       <c r="L27" s="3">
-        <f t="shared" si="38"/>
-        <v>612</v>
+        <f t="shared" si="2"/>
+        <v>765</v>
       </c>
       <c r="M27">
-        <f t="shared" si="39"/>
-        <v>509.85</v>
+        <f t="shared" si="3"/>
+        <v>432.59999999999997</v>
       </c>
       <c r="N27">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>367.2</v>
       </c>
       <c r="O27">
-        <f t="shared" si="41"/>
-        <v>370.8</v>
+        <f t="shared" si="5"/>
+        <v>293.55</v>
       </c>
       <c r="P27">
-        <f t="shared" si="42"/>
-        <v>790.25</v>
+        <f t="shared" si="6"/>
+        <v>516.25</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="43"/>
-        <v>463.5</v>
+        <f t="shared" si="7"/>
+        <v>324.45000000000005</v>
       </c>
       <c r="R27">
-        <f t="shared" si="44"/>
-        <v>615</v>
+        <f t="shared" si="8"/>
+        <v>491.4</v>
       </c>
       <c r="T27">
-        <f t="shared" si="45"/>
-        <v>1277.277</v>
+        <f t="shared" si="26"/>
+        <v>1253.21325</v>
       </c>
       <c r="U27">
-        <f t="shared" si="46"/>
-        <v>22163.549062499995</v>
+        <f t="shared" si="27"/>
+        <v>15456.525</v>
       </c>
       <c r="V27">
-        <f t="shared" si="47"/>
-        <v>7325.6175000000003</v>
+        <f t="shared" si="28"/>
+        <v>3349.9462500000004</v>
       </c>
       <c r="W27">
-        <f t="shared" si="48"/>
-        <v>922.5</v>
+        <f t="shared" si="29"/>
+        <v>737.09999999999991</v>
       </c>
       <c r="X27">
-        <f t="shared" si="49"/>
-        <v>246.75</v>
+        <f t="shared" si="30"/>
+        <v>255.75</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="15"/>
-        <v>31935</v>
+        <f t="shared" si="14"/>
+        <v>21052</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3030,81 +3101,81 @@
         <v>36267</v>
       </c>
       <c r="E28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>313</v>
       </c>
       <c r="F28">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>158.5</v>
       </c>
       <c r="G28">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>158.5</v>
       </c>
       <c r="H28">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>173.5</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="3">
-        <f t="shared" si="36"/>
-        <v>3180</v>
+        <f t="shared" si="0"/>
+        <v>3210</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="37"/>
-        <v>842.5</v>
+        <f t="shared" si="1"/>
+        <v>872.5</v>
       </c>
       <c r="L28" s="3">
-        <f t="shared" si="38"/>
-        <v>626</v>
+        <f t="shared" si="2"/>
+        <v>782.5</v>
       </c>
       <c r="M28">
-        <f t="shared" si="39"/>
-        <v>523.04999999999995</v>
+        <f t="shared" si="3"/>
+        <v>443.79999999999995</v>
       </c>
       <c r="N28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>375.59999999999997</v>
       </c>
       <c r="O28">
-        <f t="shared" si="41"/>
-        <v>380.4</v>
+        <f t="shared" si="5"/>
+        <v>301.15000000000003</v>
       </c>
       <c r="P28">
-        <f t="shared" si="42"/>
-        <v>808.25</v>
+        <f t="shared" si="6"/>
+        <v>526.25</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="43"/>
-        <v>475.5</v>
+        <f t="shared" si="7"/>
+        <v>332.85</v>
       </c>
       <c r="R28">
-        <f t="shared" si="44"/>
-        <v>630</v>
+        <f t="shared" si="8"/>
+        <v>503.2</v>
       </c>
       <c r="T28">
-        <f t="shared" si="45"/>
-        <v>1314.6119999999999</v>
+        <f t="shared" si="26"/>
+        <v>1288.855125</v>
       </c>
       <c r="U28">
-        <f t="shared" si="46"/>
-        <v>23217.991562499999</v>
+        <f t="shared" si="27"/>
+        <v>16133.509375000001</v>
       </c>
       <c r="V28">
-        <f t="shared" si="47"/>
-        <v>7686.4575000000004</v>
+        <f t="shared" si="28"/>
+        <v>3503.2462500000001</v>
       </c>
       <c r="W28">
-        <f t="shared" si="48"/>
-        <v>945</v>
+        <f t="shared" si="29"/>
+        <v>754.8</v>
       </c>
       <c r="X28">
-        <f t="shared" si="49"/>
-        <v>252.75</v>
+        <f t="shared" si="30"/>
+        <v>261.75</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="15"/>
-        <v>33416</v>
+        <f t="shared" si="14"/>
+        <v>21942</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3121,80 +3192,80 @@
         <v>40333</v>
       </c>
       <c r="E29">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>320</v>
       </c>
       <c r="F29">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>162.5</v>
       </c>
       <c r="G29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>162.5</v>
       </c>
       <c r="H29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>177.5</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="36"/>
-        <v>3250</v>
+        <f t="shared" si="0"/>
+        <v>3280</v>
       </c>
       <c r="K29" s="3">
-        <f t="shared" si="37"/>
-        <v>862.5</v>
+        <f t="shared" si="1"/>
+        <v>892.5</v>
       </c>
       <c r="L29" s="3">
-        <f t="shared" si="38"/>
-        <v>640</v>
+        <f t="shared" si="2"/>
+        <v>800</v>
       </c>
       <c r="M29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="3"/>
+        <v>454.99999999999994</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="4"/>
+        <v>384</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="5"/>
+        <v>308.75</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="6"/>
         <v>536.25</v>
       </c>
-      <c r="N29">
-        <f t="shared" si="40"/>
-        <v>384</v>
-      </c>
-      <c r="O29">
-        <f t="shared" si="41"/>
-        <v>390</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="42"/>
-        <v>826.25</v>
-      </c>
       <c r="Q29">
-        <f t="shared" si="43"/>
-        <v>487.5</v>
+        <f t="shared" si="7"/>
+        <v>341.25</v>
       </c>
       <c r="R29">
-        <f t="shared" si="44"/>
-        <v>645</v>
+        <f t="shared" si="8"/>
+        <v>515</v>
       </c>
       <c r="T29">
-        <f t="shared" si="45"/>
-        <v>1352.325</v>
+        <f t="shared" si="26"/>
+        <v>1324.8329999999999</v>
       </c>
       <c r="U29">
-        <f t="shared" si="46"/>
-        <v>24296.9140625</v>
+        <f t="shared" si="27"/>
+        <v>16824.84375</v>
       </c>
       <c r="V29">
-        <f t="shared" si="47"/>
-        <v>8055.9375</v>
+        <f t="shared" si="28"/>
+        <v>3659.90625</v>
       </c>
       <c r="W29">
-        <f t="shared" si="48"/>
-        <v>967.5</v>
+        <f t="shared" si="29"/>
+        <v>772.5</v>
       </c>
       <c r="X29">
-        <f t="shared" si="49"/>
-        <v>258.75</v>
+        <f t="shared" si="30"/>
+        <v>267.75</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="15"/>
-        <v>34931</v>
+        <f t="shared" si="14"/>
+        <v>22849</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3211,80 +3282,80 @@
         <v>44400</v>
       </c>
       <c r="E30">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>327</v>
       </c>
       <c r="F30">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>166.5</v>
       </c>
       <c r="G30">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>166.5</v>
       </c>
       <c r="H30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>181.5</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="36"/>
-        <v>3320</v>
+        <f t="shared" si="0"/>
+        <v>3350</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="37"/>
-        <v>882.5</v>
+        <f t="shared" si="1"/>
+        <v>912.5</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" si="38"/>
-        <v>654</v>
+        <f t="shared" si="2"/>
+        <v>817.5</v>
       </c>
       <c r="M30">
-        <f t="shared" si="39"/>
-        <v>549.45000000000005</v>
+        <f t="shared" si="3"/>
+        <v>466.2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>392.4</v>
       </c>
       <c r="O30">
-        <f t="shared" si="41"/>
-        <v>399.59999999999997</v>
+        <f t="shared" si="5"/>
+        <v>316.35000000000002</v>
       </c>
       <c r="P30">
-        <f t="shared" si="42"/>
-        <v>844.25</v>
+        <f t="shared" si="6"/>
+        <v>546.25</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="43"/>
-        <v>499.5</v>
+        <f t="shared" si="7"/>
+        <v>349.65000000000003</v>
       </c>
       <c r="R30">
-        <f t="shared" si="44"/>
-        <v>660</v>
+        <f t="shared" si="8"/>
+        <v>526.79999999999995</v>
       </c>
       <c r="T30">
-        <f t="shared" si="45"/>
-        <v>1390.4159999999997</v>
+        <f t="shared" si="26"/>
+        <v>1361.1468749999999</v>
       </c>
       <c r="U30">
-        <f t="shared" si="46"/>
-        <v>25400.316562500004</v>
+        <f t="shared" si="27"/>
+        <v>17530.528125000001</v>
       </c>
       <c r="V30">
-        <f t="shared" si="47"/>
-        <v>8434.0575000000008</v>
+        <f t="shared" si="28"/>
+        <v>3819.9262500000004</v>
       </c>
       <c r="W30">
-        <f t="shared" si="48"/>
-        <v>990</v>
+        <f t="shared" si="29"/>
+        <v>790.19999999999993</v>
       </c>
       <c r="X30">
-        <f t="shared" si="49"/>
-        <v>264.75</v>
+        <f t="shared" si="30"/>
+        <v>273.75</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="15"/>
-        <v>36479</v>
+        <f t="shared" si="14"/>
+        <v>23775</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3301,80 +3372,80 @@
         <v>53550</v>
       </c>
       <c r="E31">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>334</v>
       </c>
       <c r="F31">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>170.5</v>
       </c>
       <c r="G31">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>170.5</v>
       </c>
       <c r="H31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>185.5</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="36"/>
-        <v>3390</v>
+        <f t="shared" si="0"/>
+        <v>3420</v>
       </c>
       <c r="K31" s="3">
-        <f t="shared" si="37"/>
-        <v>902.5</v>
+        <f t="shared" si="1"/>
+        <v>932.5</v>
       </c>
       <c r="L31" s="3">
-        <f t="shared" si="38"/>
-        <v>668</v>
+        <f t="shared" si="2"/>
+        <v>835</v>
       </c>
       <c r="M31">
-        <f t="shared" si="39"/>
-        <v>562.65</v>
+        <f t="shared" si="3"/>
+        <v>477.4</v>
       </c>
       <c r="N31">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>400.8</v>
       </c>
       <c r="O31">
-        <f t="shared" si="41"/>
-        <v>409.2</v>
+        <f t="shared" si="5"/>
+        <v>323.95000000000005</v>
       </c>
       <c r="P31">
-        <f t="shared" si="42"/>
-        <v>862.25</v>
+        <f t="shared" si="6"/>
+        <v>556.25</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="43"/>
-        <v>511.5</v>
+        <f t="shared" si="7"/>
+        <v>358.05</v>
       </c>
       <c r="R31">
-        <f t="shared" si="44"/>
-        <v>675</v>
+        <f t="shared" si="8"/>
+        <v>538.6</v>
       </c>
       <c r="T31">
-        <f t="shared" si="45"/>
-        <v>1428.8849999999995</v>
+        <f t="shared" si="26"/>
+        <v>1397.7967499999997</v>
       </c>
       <c r="U31">
-        <f t="shared" si="46"/>
-        <v>26528.199062500003</v>
+        <f t="shared" si="27"/>
+        <v>18250.5625</v>
       </c>
       <c r="V31">
-        <f t="shared" si="47"/>
-        <v>8820.8174999999992</v>
+        <f t="shared" si="28"/>
+        <v>3983.3062500000001</v>
       </c>
       <c r="W31">
-        <f t="shared" si="48"/>
-        <v>1012.5</v>
+        <f t="shared" si="29"/>
+        <v>807.90000000000009</v>
       </c>
       <c r="X31">
-        <f t="shared" si="49"/>
-        <v>270.75</v>
+        <f t="shared" si="30"/>
+        <v>279.75</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="15"/>
-        <v>38061</v>
+        <f t="shared" si="14"/>
+        <v>24719</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3391,80 +3462,80 @@
         <v>62700</v>
       </c>
       <c r="E32">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>341</v>
       </c>
       <c r="F32">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>174.5</v>
       </c>
       <c r="G32">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>174.5</v>
       </c>
       <c r="H32">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>189.5</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" si="36"/>
-        <v>3460</v>
+        <f t="shared" si="0"/>
+        <v>3490</v>
       </c>
       <c r="K32" s="3">
-        <f t="shared" si="37"/>
-        <v>922.5</v>
+        <f t="shared" si="1"/>
+        <v>952.5</v>
       </c>
       <c r="L32" s="3">
-        <f t="shared" si="38"/>
-        <v>682</v>
+        <f t="shared" si="2"/>
+        <v>852.5</v>
       </c>
       <c r="M32">
-        <f t="shared" si="39"/>
-        <v>575.85</v>
+        <f t="shared" si="3"/>
+        <v>488.59999999999997</v>
       </c>
       <c r="N32">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>409.2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="41"/>
-        <v>418.8</v>
+        <f t="shared" si="5"/>
+        <v>331.55</v>
       </c>
       <c r="P32">
-        <f t="shared" si="42"/>
-        <v>880.25</v>
+        <f t="shared" si="6"/>
+        <v>566.25</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="43"/>
-        <v>523.5</v>
+        <f t="shared" si="7"/>
+        <v>366.45</v>
       </c>
       <c r="R32">
-        <f t="shared" si="44"/>
-        <v>690</v>
+        <f t="shared" si="8"/>
+        <v>550.4</v>
       </c>
       <c r="T32">
-        <f t="shared" si="45"/>
-        <v>1467.7320000000002</v>
+        <f t="shared" si="26"/>
+        <v>1434.7826250000001</v>
       </c>
       <c r="U32">
-        <f t="shared" si="46"/>
-        <v>27680.561562499999</v>
+        <f t="shared" si="27"/>
+        <v>18984.946875000001</v>
       </c>
       <c r="V32">
-        <f t="shared" si="47"/>
-        <v>9216.2175000000007</v>
+        <f t="shared" si="28"/>
+        <v>4150.0462500000003</v>
       </c>
       <c r="W32">
-        <f t="shared" si="48"/>
-        <v>1035</v>
+        <f t="shared" si="29"/>
+        <v>825.59999999999991</v>
       </c>
       <c r="X32">
-        <f t="shared" si="49"/>
-        <v>276.75</v>
+        <f t="shared" si="30"/>
+        <v>285.75</v>
       </c>
       <c r="Y32">
-        <f t="shared" si="15"/>
-        <v>39676</v>
+        <f t="shared" si="14"/>
+        <v>25681</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3481,80 +3552,80 @@
         <v>71850</v>
       </c>
       <c r="E33">
-        <f t="shared" si="50"/>
+        <f t="shared" si="31"/>
         <v>348</v>
       </c>
       <c r="F33">
-        <f t="shared" si="51"/>
+        <f t="shared" si="32"/>
         <v>178.5</v>
       </c>
       <c r="G33">
-        <f t="shared" si="52"/>
+        <f t="shared" si="33"/>
         <v>178.5</v>
       </c>
       <c r="H33">
-        <f t="shared" si="53"/>
+        <f t="shared" si="34"/>
         <v>193.5</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="36"/>
-        <v>3530</v>
+        <f t="shared" si="0"/>
+        <v>3560</v>
       </c>
       <c r="K33" s="3">
-        <f t="shared" si="37"/>
-        <v>942.5</v>
+        <f t="shared" si="1"/>
+        <v>972.5</v>
       </c>
       <c r="L33" s="3">
-        <f t="shared" si="38"/>
-        <v>696</v>
+        <f t="shared" si="2"/>
+        <v>870</v>
       </c>
       <c r="M33">
-        <f t="shared" si="39"/>
-        <v>589.04999999999995</v>
+        <f t="shared" si="3"/>
+        <v>499.79999999999995</v>
       </c>
       <c r="N33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="4"/>
         <v>417.59999999999997</v>
       </c>
       <c r="O33">
-        <f t="shared" si="41"/>
-        <v>428.4</v>
+        <f t="shared" si="5"/>
+        <v>339.15000000000003</v>
       </c>
       <c r="P33">
-        <f t="shared" si="42"/>
-        <v>898.25</v>
+        <f t="shared" si="6"/>
+        <v>576.25</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="43"/>
-        <v>535.5</v>
+        <f t="shared" si="7"/>
+        <v>374.85</v>
       </c>
       <c r="R33">
-        <f t="shared" si="44"/>
-        <v>705</v>
+        <f t="shared" si="8"/>
+        <v>562.20000000000005</v>
       </c>
       <c r="T33">
-        <f t="shared" si="45"/>
-        <v>1506.9570000000001</v>
+        <f t="shared" si="26"/>
+        <v>1472.1045000000001</v>
       </c>
       <c r="U33">
-        <f t="shared" si="46"/>
-        <v>28857.404062499994</v>
+        <f t="shared" si="27"/>
+        <v>19733.681250000001</v>
       </c>
       <c r="V33">
-        <f t="shared" si="47"/>
-        <v>9620.2574999999997</v>
+        <f t="shared" si="28"/>
+        <v>4320.1462499999998</v>
       </c>
       <c r="W33">
-        <f t="shared" si="48"/>
-        <v>1057.5</v>
+        <f t="shared" si="29"/>
+        <v>843.30000000000007</v>
       </c>
       <c r="X33">
-        <f t="shared" si="49"/>
-        <v>282.75</v>
+        <f t="shared" si="30"/>
+        <v>291.75</v>
       </c>
       <c r="Y33">
-        <f t="shared" si="15"/>
-        <v>41324</v>
+        <f t="shared" si="14"/>
+        <v>26660</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3575,76 +3646,76 @@
         <v>696</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:H34" si="54">F33*2</f>
+        <f t="shared" ref="F34:H34" si="35">F33*2</f>
         <v>357</v>
       </c>
       <c r="G34">
-        <f t="shared" si="54"/>
+        <f t="shared" si="35"/>
         <v>357</v>
       </c>
       <c r="H34">
-        <f t="shared" si="54"/>
+        <f t="shared" si="35"/>
         <v>387</v>
       </c>
       <c r="J34" s="3">
-        <f t="shared" ref="J34:J63" si="55" xml:space="preserve"> 50 +E34*10</f>
-        <v>7010</v>
+        <f t="shared" si="0"/>
+        <v>7040</v>
       </c>
       <c r="K34" s="3">
-        <f t="shared" ref="K34:K63" si="56" xml:space="preserve"> 50 +F34*5</f>
-        <v>1835</v>
+        <f t="shared" si="1"/>
+        <v>1865</v>
       </c>
       <c r="L34" s="3">
-        <f t="shared" ref="L34:L63" si="57" xml:space="preserve"> E34*2</f>
-        <v>1392</v>
+        <f t="shared" si="2"/>
+        <v>1740</v>
       </c>
       <c r="M34">
-        <f t="shared" ref="M34:M63" si="58">F34*2.5+G34*0.8</f>
-        <v>1178.0999999999999</v>
+        <f t="shared" si="3"/>
+        <v>999.59999999999991</v>
       </c>
       <c r="N34">
-        <f t="shared" ref="N34:N63" si="59">E34*1.2</f>
+        <f t="shared" si="4"/>
         <v>835.19999999999993</v>
       </c>
       <c r="O34">
-        <f t="shared" ref="O34:O63" si="60">F34*1.2+G34*1.2</f>
-        <v>856.8</v>
+        <f t="shared" si="5"/>
+        <v>678.30000000000007</v>
       </c>
       <c r="P34">
-        <f t="shared" ref="P34:P63" si="61" xml:space="preserve"> 50+H34*3 + G34*1.5</f>
-        <v>1746.5</v>
+        <f t="shared" si="6"/>
+        <v>1052.5</v>
       </c>
       <c r="Q34">
-        <f t="shared" ref="Q34:Q63" si="62">G34*2+F34</f>
-        <v>1071</v>
+        <f t="shared" si="7"/>
+        <v>749.7</v>
       </c>
       <c r="R34">
-        <f t="shared" ref="R34:R63" si="63">G34*2 + E34</f>
-        <v>1410</v>
+        <f t="shared" si="8"/>
+        <v>1124.4000000000001</v>
       </c>
       <c r="T34">
-        <f t="shared" ref="T34:T63" si="64">J34*(1+N34/1000*0.5 + O34/1000*0.5)*0.3</f>
-        <v>3882.1379999999999</v>
+        <f t="shared" ref="T34:T63" si="36">J34*(1+N34/1000*0.5 + O34/1000*0.5)*0.3</f>
+        <v>3710.2559999999999</v>
       </c>
       <c r="U34">
-        <f t="shared" ref="U34:U63" si="65">(L34*0.5+M34*0.5)*P34/100*5</f>
-        <v>112216.99124999999</v>
+        <f t="shared" ref="U34:U63" si="37">(L34*0.5+M34*0.5)*P34/100*5</f>
+        <v>72085.725000000006</v>
       </c>
       <c r="V34">
-        <f t="shared" ref="V34:V63" si="66">Q34*P34/100*2</f>
-        <v>37410.03</v>
+        <f t="shared" ref="V34:V63" si="38">Q34*P34/100*2</f>
+        <v>15781.184999999999</v>
       </c>
       <c r="W34">
-        <f t="shared" ref="W34:W63" si="67">R34*1.5</f>
-        <v>2115</v>
+        <f t="shared" ref="W34:W63" si="39">R34*1.5</f>
+        <v>1686.6000000000001</v>
       </c>
       <c r="X34">
-        <f t="shared" ref="X34:X63" si="68">K34*0.3</f>
-        <v>550.5</v>
+        <f t="shared" ref="X34:X63" si="40">K34*0.3</f>
+        <v>559.5</v>
       </c>
       <c r="Y34">
-        <f t="shared" si="15"/>
-        <v>156174</v>
+        <f t="shared" si="14"/>
+        <v>93823</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3669,72 +3740,72 @@
         <v>363</v>
       </c>
       <c r="G35">
-        <f t="shared" ref="G35:H35" si="69">G34+6</f>
+        <f t="shared" ref="G35:H35" si="41">G34+6</f>
         <v>363</v>
       </c>
       <c r="H35">
-        <f t="shared" si="69"/>
+        <f t="shared" si="41"/>
         <v>393</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" si="55"/>
-        <v>7130</v>
+        <f t="shared" si="0"/>
+        <v>7160</v>
       </c>
       <c r="K35" s="3">
-        <f t="shared" si="56"/>
-        <v>1865</v>
+        <f t="shared" si="1"/>
+        <v>1895</v>
       </c>
       <c r="L35" s="3">
-        <f t="shared" si="57"/>
-        <v>1416</v>
+        <f t="shared" si="2"/>
+        <v>1770</v>
       </c>
       <c r="M35">
-        <f t="shared" si="58"/>
-        <v>1197.9000000000001</v>
+        <f t="shared" si="3"/>
+        <v>1016.4</v>
       </c>
       <c r="N35">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>849.6</v>
       </c>
       <c r="O35">
-        <f t="shared" si="60"/>
-        <v>871.19999999999993</v>
+        <f t="shared" si="5"/>
+        <v>689.7</v>
       </c>
       <c r="P35">
-        <f t="shared" si="61"/>
-        <v>1773.5</v>
+        <f t="shared" si="6"/>
+        <v>1067.5</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="62"/>
-        <v>1089</v>
+        <f t="shared" si="7"/>
+        <v>762.30000000000007</v>
       </c>
       <c r="R35">
-        <f t="shared" si="63"/>
-        <v>1434</v>
+        <f t="shared" si="8"/>
+        <v>1143.5999999999999</v>
       </c>
       <c r="T35">
-        <f t="shared" si="64"/>
-        <v>3979.3955999999998</v>
+        <f t="shared" si="36"/>
+        <v>3801.2082</v>
       </c>
       <c r="U35">
-        <f t="shared" si="65"/>
-        <v>115893.79125000001</v>
+        <f t="shared" si="37"/>
+        <v>74362.05</v>
       </c>
       <c r="V35">
-        <f t="shared" si="66"/>
-        <v>38626.83</v>
+        <f t="shared" si="38"/>
+        <v>16275.105000000003</v>
       </c>
       <c r="W35">
-        <f t="shared" si="67"/>
-        <v>2151</v>
+        <f t="shared" si="39"/>
+        <v>1715.3999999999999</v>
       </c>
       <c r="X35">
-        <f t="shared" si="68"/>
-        <v>559.5</v>
+        <f t="shared" si="40"/>
+        <v>568.5</v>
       </c>
       <c r="Y35">
-        <f t="shared" si="15"/>
-        <v>161210</v>
+        <f t="shared" si="14"/>
+        <v>96722</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3751,80 +3822,80 @@
         <v>106133</v>
       </c>
       <c r="E36">
-        <f t="shared" ref="E36:E43" si="70">E35+12</f>
+        <f t="shared" ref="E36:E43" si="42">E35+12</f>
         <v>720</v>
       </c>
       <c r="F36">
-        <f t="shared" ref="F36:F43" si="71">F35+6</f>
+        <f t="shared" ref="F36:F43" si="43">F35+6</f>
         <v>369</v>
       </c>
       <c r="G36">
-        <f t="shared" ref="G36:G43" si="72">G35+6</f>
+        <f t="shared" ref="G36:G43" si="44">G35+6</f>
         <v>369</v>
       </c>
       <c r="H36">
-        <f t="shared" ref="H36:H43" si="73">H35+6</f>
+        <f t="shared" ref="H36:H43" si="45">H35+6</f>
         <v>399</v>
       </c>
       <c r="J36" s="3">
-        <f t="shared" si="55"/>
-        <v>7250</v>
+        <f t="shared" si="0"/>
+        <v>7280</v>
       </c>
       <c r="K36" s="3">
-        <f t="shared" si="56"/>
-        <v>1895</v>
+        <f t="shared" si="1"/>
+        <v>1925</v>
       </c>
       <c r="L36" s="3">
-        <f t="shared" si="57"/>
-        <v>1440</v>
+        <f t="shared" si="2"/>
+        <v>1800</v>
       </c>
       <c r="M36">
-        <f t="shared" si="58"/>
-        <v>1217.7</v>
+        <f t="shared" si="3"/>
+        <v>1033.1999999999998</v>
       </c>
       <c r="N36">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>864</v>
       </c>
       <c r="O36">
-        <f t="shared" si="60"/>
-        <v>885.6</v>
+        <f t="shared" si="5"/>
+        <v>701.1</v>
       </c>
       <c r="P36">
-        <f t="shared" si="61"/>
-        <v>1800.5</v>
+        <f t="shared" si="6"/>
+        <v>1082.5</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="62"/>
-        <v>1107</v>
+        <f t="shared" si="7"/>
+        <v>774.9</v>
       </c>
       <c r="R36">
-        <f t="shared" si="63"/>
-        <v>1458</v>
+        <f t="shared" si="8"/>
+        <v>1162.8</v>
       </c>
       <c r="T36">
-        <f t="shared" si="64"/>
-        <v>4077.6899999999996</v>
+        <f t="shared" si="36"/>
+        <v>3893.0891999999999</v>
       </c>
       <c r="U36">
-        <f t="shared" si="65"/>
-        <v>119629.72124999999</v>
+        <f t="shared" si="37"/>
+        <v>76673.475000000006</v>
       </c>
       <c r="V36">
-        <f t="shared" si="66"/>
-        <v>39863.07</v>
+        <f t="shared" si="38"/>
+        <v>16776.584999999999</v>
       </c>
       <c r="W36">
-        <f t="shared" si="67"/>
-        <v>2187</v>
+        <f t="shared" si="39"/>
+        <v>1744.1999999999998</v>
       </c>
       <c r="X36">
-        <f t="shared" si="68"/>
-        <v>568.5</v>
+        <f t="shared" si="40"/>
+        <v>577.5</v>
       </c>
       <c r="Y36">
-        <f t="shared" si="15"/>
-        <v>166325</v>
+        <f t="shared" si="14"/>
+        <v>99664</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3841,80 +3912,80 @@
         <v>118700</v>
       </c>
       <c r="E37">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>732</v>
       </c>
       <c r="F37">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>375</v>
       </c>
       <c r="G37">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>375</v>
       </c>
       <c r="H37">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>405</v>
       </c>
       <c r="J37" s="3">
-        <f t="shared" si="55"/>
-        <v>7370</v>
+        <f t="shared" si="0"/>
+        <v>7400</v>
       </c>
       <c r="K37" s="3">
-        <f t="shared" si="56"/>
-        <v>1925</v>
+        <f t="shared" si="1"/>
+        <v>1955</v>
       </c>
       <c r="L37" s="3">
-        <f t="shared" si="57"/>
-        <v>1464</v>
+        <f t="shared" si="2"/>
+        <v>1830</v>
       </c>
       <c r="M37">
-        <f t="shared" si="58"/>
-        <v>1237.5</v>
+        <f t="shared" si="3"/>
+        <v>1050</v>
       </c>
       <c r="N37">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>878.4</v>
       </c>
       <c r="O37">
-        <f t="shared" si="60"/>
-        <v>900</v>
+        <f t="shared" si="5"/>
+        <v>712.5</v>
       </c>
       <c r="P37">
-        <f t="shared" si="61"/>
-        <v>1827.5</v>
+        <f t="shared" si="6"/>
+        <v>1097.5</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="62"/>
-        <v>1125</v>
+        <f t="shared" si="7"/>
+        <v>787.5</v>
       </c>
       <c r="R37">
-        <f t="shared" si="63"/>
-        <v>1482</v>
+        <f t="shared" si="8"/>
+        <v>1182</v>
       </c>
       <c r="T37">
-        <f t="shared" si="64"/>
-        <v>4177.0212000000001</v>
+        <f t="shared" si="36"/>
+        <v>3985.8989999999999</v>
       </c>
       <c r="U37">
-        <f t="shared" si="65"/>
-        <v>123424.78125</v>
+        <f t="shared" si="37"/>
+        <v>79020</v>
       </c>
       <c r="V37">
-        <f t="shared" si="66"/>
-        <v>41118.75</v>
+        <f t="shared" si="38"/>
+        <v>17285.625</v>
       </c>
       <c r="W37">
-        <f t="shared" si="67"/>
-        <v>2223</v>
+        <f t="shared" si="39"/>
+        <v>1773</v>
       </c>
       <c r="X37">
-        <f t="shared" si="68"/>
-        <v>577.5</v>
+        <f t="shared" si="40"/>
+        <v>586.5</v>
       </c>
       <c r="Y37">
-        <f t="shared" si="15"/>
-        <v>171521</v>
+        <f t="shared" si="14"/>
+        <v>102651</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -3931,80 +4002,80 @@
         <v>131667</v>
       </c>
       <c r="E38">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>744</v>
       </c>
       <c r="F38">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>381</v>
       </c>
       <c r="G38">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>381</v>
       </c>
       <c r="H38">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>411</v>
       </c>
       <c r="J38" s="3">
-        <f t="shared" si="55"/>
-        <v>7490</v>
+        <f t="shared" si="0"/>
+        <v>7520</v>
       </c>
       <c r="K38" s="3">
-        <f t="shared" si="56"/>
-        <v>1955</v>
+        <f t="shared" si="1"/>
+        <v>1985</v>
       </c>
       <c r="L38" s="3">
-        <f t="shared" si="57"/>
-        <v>1488</v>
+        <f t="shared" si="2"/>
+        <v>1860</v>
       </c>
       <c r="M38">
-        <f t="shared" si="58"/>
-        <v>1257.3</v>
+        <f t="shared" si="3"/>
+        <v>1066.8</v>
       </c>
       <c r="N38">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>892.8</v>
       </c>
       <c r="O38">
-        <f t="shared" si="60"/>
-        <v>914.4</v>
+        <f t="shared" si="5"/>
+        <v>723.90000000000009</v>
       </c>
       <c r="P38">
-        <f t="shared" si="61"/>
-        <v>1854.5</v>
+        <f t="shared" si="6"/>
+        <v>1112.5</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="62"/>
-        <v>1143</v>
+        <f t="shared" si="7"/>
+        <v>800.1</v>
       </c>
       <c r="R38">
-        <f t="shared" si="63"/>
-        <v>1506</v>
+        <f t="shared" si="8"/>
+        <v>1201.2</v>
       </c>
       <c r="T38">
-        <f t="shared" si="64"/>
-        <v>4277.3891999999996</v>
+        <f t="shared" si="36"/>
+        <v>4079.6375999999996</v>
       </c>
       <c r="U38">
-        <f t="shared" si="65"/>
-        <v>127278.97125000002</v>
+        <f t="shared" si="37"/>
+        <v>81401.625</v>
       </c>
       <c r="V38">
-        <f t="shared" si="66"/>
-        <v>42393.87</v>
+        <f t="shared" si="38"/>
+        <v>17802.224999999999</v>
       </c>
       <c r="W38">
-        <f t="shared" si="67"/>
-        <v>2259</v>
+        <f t="shared" si="39"/>
+        <v>1801.8000000000002</v>
       </c>
       <c r="X38">
-        <f t="shared" si="68"/>
-        <v>586.5</v>
+        <f t="shared" si="40"/>
+        <v>595.5</v>
       </c>
       <c r="Y38">
-        <f t="shared" si="15"/>
-        <v>176795</v>
+        <f t="shared" si="14"/>
+        <v>105680</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4021,80 +4092,80 @@
         <v>144633</v>
       </c>
       <c r="E39">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>756</v>
       </c>
       <c r="F39">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>387</v>
       </c>
       <c r="G39">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>387</v>
       </c>
       <c r="H39">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>417</v>
       </c>
       <c r="J39" s="3">
-        <f t="shared" si="55"/>
-        <v>7610</v>
+        <f t="shared" si="0"/>
+        <v>7640</v>
       </c>
       <c r="K39" s="3">
-        <f t="shared" si="56"/>
-        <v>1985</v>
+        <f t="shared" si="1"/>
+        <v>2015</v>
       </c>
       <c r="L39" s="3">
-        <f t="shared" si="57"/>
-        <v>1512</v>
+        <f t="shared" si="2"/>
+        <v>1890</v>
       </c>
       <c r="M39">
-        <f t="shared" si="58"/>
-        <v>1277.0999999999999</v>
+        <f t="shared" si="3"/>
+        <v>1083.5999999999999</v>
       </c>
       <c r="N39">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>907.19999999999993</v>
       </c>
       <c r="O39">
-        <f t="shared" si="60"/>
-        <v>928.8</v>
+        <f t="shared" si="5"/>
+        <v>735.30000000000007</v>
       </c>
       <c r="P39">
-        <f t="shared" si="61"/>
-        <v>1881.5</v>
+        <f t="shared" si="6"/>
+        <v>1127.5</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="62"/>
-        <v>1161</v>
+        <f t="shared" si="7"/>
+        <v>812.7</v>
       </c>
       <c r="R39">
-        <f t="shared" si="63"/>
-        <v>1530</v>
+        <f t="shared" si="8"/>
+        <v>1220.4000000000001</v>
       </c>
       <c r="T39">
-        <f t="shared" si="64"/>
-        <v>4378.7939999999999</v>
+        <f t="shared" si="36"/>
+        <v>4174.3050000000003</v>
       </c>
       <c r="U39">
-        <f t="shared" si="65"/>
-        <v>131192.29124999998</v>
+        <f t="shared" si="37"/>
+        <v>83818.349999999991</v>
       </c>
       <c r="V39">
-        <f t="shared" si="66"/>
-        <v>43688.43</v>
+        <f t="shared" si="38"/>
+        <v>18326.384999999998</v>
       </c>
       <c r="W39">
-        <f t="shared" si="67"/>
-        <v>2295</v>
+        <f t="shared" si="39"/>
+        <v>1830.6000000000001</v>
       </c>
       <c r="X39">
-        <f t="shared" si="68"/>
-        <v>595.5</v>
+        <f t="shared" si="40"/>
+        <v>604.5</v>
       </c>
       <c r="Y39">
-        <f t="shared" si="15"/>
-        <v>182150</v>
+        <f t="shared" si="14"/>
+        <v>108754</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4111,80 +4182,80 @@
         <v>157600</v>
       </c>
       <c r="E40">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>768</v>
       </c>
       <c r="F40">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>393</v>
       </c>
       <c r="G40">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>393</v>
       </c>
       <c r="H40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>423</v>
       </c>
       <c r="J40" s="3">
-        <f t="shared" si="55"/>
-        <v>7730</v>
+        <f t="shared" si="0"/>
+        <v>7760</v>
       </c>
       <c r="K40" s="3">
-        <f t="shared" si="56"/>
-        <v>2015</v>
+        <f t="shared" si="1"/>
+        <v>2045</v>
       </c>
       <c r="L40" s="3">
-        <f t="shared" si="57"/>
-        <v>1536</v>
+        <f t="shared" si="2"/>
+        <v>1920</v>
       </c>
       <c r="M40">
-        <f t="shared" si="58"/>
-        <v>1296.9000000000001</v>
+        <f t="shared" si="3"/>
+        <v>1100.4000000000001</v>
       </c>
       <c r="N40">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>921.59999999999991</v>
       </c>
       <c r="O40">
-        <f t="shared" si="60"/>
-        <v>943.19999999999993</v>
+        <f t="shared" si="5"/>
+        <v>746.7</v>
       </c>
       <c r="P40">
-        <f t="shared" si="61"/>
-        <v>1908.5</v>
+        <f t="shared" si="6"/>
+        <v>1142.5</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="62"/>
-        <v>1179</v>
+        <f t="shared" si="7"/>
+        <v>825.30000000000007</v>
       </c>
       <c r="R40">
-        <f t="shared" si="63"/>
-        <v>1554</v>
+        <f t="shared" si="8"/>
+        <v>1239.5999999999999</v>
       </c>
       <c r="T40">
-        <f t="shared" si="64"/>
-        <v>4481.2356</v>
+        <f t="shared" si="36"/>
+        <v>4269.9011999999993</v>
       </c>
       <c r="U40">
-        <f t="shared" si="65"/>
-        <v>135164.74125000002</v>
+        <f t="shared" si="37"/>
+        <v>86270.175000000003</v>
       </c>
       <c r="V40">
-        <f t="shared" si="66"/>
-        <v>45002.43</v>
+        <f t="shared" si="38"/>
+        <v>18858.105000000003</v>
       </c>
       <c r="W40">
-        <f t="shared" si="67"/>
-        <v>2331</v>
+        <f t="shared" si="39"/>
+        <v>1859.3999999999999</v>
       </c>
       <c r="X40">
-        <f t="shared" si="68"/>
-        <v>604.5</v>
+        <f t="shared" si="40"/>
+        <v>613.5</v>
       </c>
       <c r="Y40">
-        <f t="shared" si="15"/>
-        <v>187583</v>
+        <f t="shared" si="14"/>
+        <v>111871</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4201,80 +4272,80 @@
         <v>186775</v>
       </c>
       <c r="E41">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>780</v>
       </c>
       <c r="F41">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>399</v>
       </c>
       <c r="G41">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>399</v>
       </c>
       <c r="H41">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>429</v>
       </c>
       <c r="J41" s="3">
-        <f t="shared" si="55"/>
-        <v>7850</v>
+        <f t="shared" si="0"/>
+        <v>7880</v>
       </c>
       <c r="K41" s="3">
-        <f t="shared" si="56"/>
-        <v>2045</v>
+        <f t="shared" si="1"/>
+        <v>2075</v>
       </c>
       <c r="L41" s="3">
-        <f t="shared" si="57"/>
-        <v>1560</v>
+        <f t="shared" si="2"/>
+        <v>1950</v>
       </c>
       <c r="M41">
-        <f t="shared" si="58"/>
-        <v>1316.7</v>
+        <f t="shared" si="3"/>
+        <v>1117.1999999999998</v>
       </c>
       <c r="N41">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>936</v>
       </c>
       <c r="O41">
-        <f t="shared" si="60"/>
-        <v>957.59999999999991</v>
+        <f t="shared" si="5"/>
+        <v>758.10000000000014</v>
       </c>
       <c r="P41">
-        <f t="shared" si="61"/>
-        <v>1935.5</v>
+        <f t="shared" si="6"/>
+        <v>1157.5</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="62"/>
-        <v>1197</v>
+        <f t="shared" si="7"/>
+        <v>837.90000000000009</v>
       </c>
       <c r="R41">
-        <f t="shared" si="63"/>
-        <v>1578</v>
+        <f t="shared" si="8"/>
+        <v>1258.8</v>
       </c>
       <c r="T41">
-        <f t="shared" si="64"/>
-        <v>4584.7139999999999</v>
+        <f t="shared" si="36"/>
+        <v>4366.4261999999999</v>
       </c>
       <c r="U41">
-        <f t="shared" si="65"/>
-        <v>139196.32124999998</v>
+        <f t="shared" si="37"/>
+        <v>88757.099999999991</v>
       </c>
       <c r="V41">
-        <f t="shared" si="66"/>
-        <v>46335.87</v>
+        <f t="shared" si="38"/>
+        <v>19397.385000000002</v>
       </c>
       <c r="W41">
-        <f t="shared" si="67"/>
-        <v>2367</v>
+        <f t="shared" si="39"/>
+        <v>1888.1999999999998</v>
       </c>
       <c r="X41">
-        <f t="shared" si="68"/>
-        <v>613.5</v>
+        <f t="shared" si="40"/>
+        <v>622.5</v>
       </c>
       <c r="Y41">
-        <f t="shared" si="15"/>
-        <v>193097</v>
+        <f t="shared" si="14"/>
+        <v>115031</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4291,80 +4362,80 @@
         <v>215950</v>
       </c>
       <c r="E42">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>792</v>
       </c>
       <c r="F42">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>405</v>
       </c>
       <c r="G42">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>405</v>
       </c>
       <c r="H42">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>435</v>
       </c>
       <c r="J42" s="3">
-        <f t="shared" si="55"/>
-        <v>7970</v>
+        <f t="shared" si="0"/>
+        <v>8000</v>
       </c>
       <c r="K42" s="3">
-        <f t="shared" si="56"/>
-        <v>2075</v>
+        <f t="shared" si="1"/>
+        <v>2105</v>
       </c>
       <c r="L42" s="3">
-        <f t="shared" si="57"/>
-        <v>1584</v>
+        <f t="shared" si="2"/>
+        <v>1980</v>
       </c>
       <c r="M42">
-        <f t="shared" si="58"/>
-        <v>1336.5</v>
+        <f t="shared" si="3"/>
+        <v>1134</v>
       </c>
       <c r="N42">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>950.4</v>
       </c>
       <c r="O42">
-        <f t="shared" si="60"/>
-        <v>972</v>
+        <f t="shared" si="5"/>
+        <v>769.5</v>
       </c>
       <c r="P42">
-        <f t="shared" si="61"/>
-        <v>1962.5</v>
+        <f t="shared" si="6"/>
+        <v>1172.5</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="62"/>
-        <v>1215</v>
+        <f t="shared" si="7"/>
+        <v>850.5</v>
       </c>
       <c r="R42">
-        <f t="shared" si="63"/>
-        <v>1602</v>
+        <f t="shared" si="8"/>
+        <v>1278</v>
       </c>
       <c r="T42">
-        <f t="shared" si="64"/>
-        <v>4689.2291999999998</v>
+        <f t="shared" si="36"/>
+        <v>4463.88</v>
       </c>
       <c r="U42">
-        <f t="shared" si="65"/>
-        <v>143287.03125</v>
+        <f t="shared" si="37"/>
+        <v>91279.125</v>
       </c>
       <c r="V42">
-        <f t="shared" si="66"/>
-        <v>47688.75</v>
+        <f t="shared" si="38"/>
+        <v>19944.224999999999</v>
       </c>
       <c r="W42">
-        <f t="shared" si="67"/>
-        <v>2403</v>
+        <f t="shared" si="39"/>
+        <v>1917</v>
       </c>
       <c r="X42">
-        <f t="shared" si="68"/>
-        <v>622.5</v>
+        <f t="shared" si="40"/>
+        <v>631.5</v>
       </c>
       <c r="Y42">
-        <f t="shared" si="15"/>
-        <v>198690</v>
+        <f t="shared" si="14"/>
+        <v>118235</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4381,80 +4452,80 @@
         <v>245125</v>
       </c>
       <c r="E43">
-        <f t="shared" si="70"/>
+        <f t="shared" si="42"/>
         <v>804</v>
       </c>
       <c r="F43">
-        <f t="shared" si="71"/>
+        <f t="shared" si="43"/>
         <v>411</v>
       </c>
       <c r="G43">
-        <f t="shared" si="72"/>
+        <f t="shared" si="44"/>
         <v>411</v>
       </c>
       <c r="H43">
-        <f t="shared" si="73"/>
+        <f t="shared" si="45"/>
         <v>441</v>
       </c>
       <c r="J43" s="3">
-        <f t="shared" si="55"/>
-        <v>8090</v>
+        <f t="shared" si="0"/>
+        <v>8120</v>
       </c>
       <c r="K43" s="3">
-        <f t="shared" si="56"/>
-        <v>2105</v>
+        <f t="shared" si="1"/>
+        <v>2135</v>
       </c>
       <c r="L43" s="3">
-        <f t="shared" si="57"/>
-        <v>1608</v>
+        <f t="shared" si="2"/>
+        <v>2010</v>
       </c>
       <c r="M43">
-        <f t="shared" si="58"/>
-        <v>1356.3</v>
+        <f t="shared" si="3"/>
+        <v>1150.8</v>
       </c>
       <c r="N43">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>964.8</v>
       </c>
       <c r="O43">
-        <f t="shared" si="60"/>
-        <v>986.4</v>
+        <f t="shared" si="5"/>
+        <v>780.90000000000009</v>
       </c>
       <c r="P43">
-        <f t="shared" si="61"/>
-        <v>1989.5</v>
+        <f t="shared" si="6"/>
+        <v>1187.5</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="62"/>
-        <v>1233</v>
+        <f t="shared" si="7"/>
+        <v>863.1</v>
       </c>
       <c r="R43">
-        <f t="shared" si="63"/>
-        <v>1626</v>
+        <f t="shared" si="8"/>
+        <v>1297.2</v>
       </c>
       <c r="T43">
-        <f t="shared" si="64"/>
-        <v>4794.7811999999994</v>
+        <f t="shared" si="36"/>
+        <v>4562.2626</v>
       </c>
       <c r="U43">
-        <f t="shared" si="65"/>
-        <v>147436.87125000003</v>
+        <f t="shared" si="37"/>
+        <v>93836.25</v>
       </c>
       <c r="V43">
-        <f t="shared" si="66"/>
-        <v>49061.07</v>
+        <f t="shared" si="38"/>
+        <v>20498.625</v>
       </c>
       <c r="W43">
-        <f t="shared" si="67"/>
-        <v>2439</v>
+        <f t="shared" si="39"/>
+        <v>1945.8000000000002</v>
       </c>
       <c r="X43">
-        <f t="shared" si="68"/>
-        <v>631.5</v>
+        <f t="shared" si="40"/>
+        <v>640.5</v>
       </c>
       <c r="Y43">
-        <f t="shared" si="15"/>
-        <v>204363</v>
+        <f t="shared" si="14"/>
+        <v>121483</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4475,76 +4546,76 @@
         <v>1447</v>
       </c>
       <c r="F44">
-        <f t="shared" ref="F44:H44" si="74">FLOOR(F43*1.8,1)</f>
+        <f t="shared" ref="F44:H44" si="46">FLOOR(F43*1.8,1)</f>
         <v>739</v>
       </c>
       <c r="G44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="46"/>
         <v>739</v>
       </c>
       <c r="H44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="46"/>
         <v>793</v>
       </c>
       <c r="J44" s="3">
-        <f t="shared" si="55"/>
-        <v>14520</v>
+        <f t="shared" si="0"/>
+        <v>14550</v>
       </c>
       <c r="K44" s="3">
-        <f t="shared" si="56"/>
-        <v>3745</v>
+        <f t="shared" si="1"/>
+        <v>3775</v>
       </c>
       <c r="L44" s="3">
-        <f t="shared" si="57"/>
-        <v>2894</v>
+        <f t="shared" si="2"/>
+        <v>3617.5</v>
       </c>
       <c r="M44">
-        <f t="shared" si="58"/>
-        <v>2438.6999999999998</v>
+        <f t="shared" si="3"/>
+        <v>2069.1999999999998</v>
       </c>
       <c r="N44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1736.3999999999999</v>
       </c>
       <c r="O44">
-        <f t="shared" si="60"/>
-        <v>1773.6</v>
+        <f t="shared" si="5"/>
+        <v>1404.1000000000001</v>
       </c>
       <c r="P44">
-        <f t="shared" si="61"/>
-        <v>3537.5</v>
+        <f t="shared" si="6"/>
+        <v>2055.5</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="62"/>
-        <v>2217</v>
+        <f t="shared" si="7"/>
+        <v>1551.9</v>
       </c>
       <c r="R44">
-        <f t="shared" si="63"/>
-        <v>2925</v>
+        <f t="shared" si="8"/>
+        <v>2333.8000000000002</v>
       </c>
       <c r="T44">
-        <f t="shared" si="64"/>
-        <v>12000.779999999999</v>
+        <f t="shared" si="36"/>
+        <v>11219.141249999999</v>
       </c>
       <c r="U44">
-        <f t="shared" si="65"/>
-        <v>471610.65625</v>
+        <f t="shared" si="37"/>
+        <v>292225.29625000001</v>
       </c>
       <c r="V44">
-        <f t="shared" si="66"/>
-        <v>156852.75</v>
+        <f t="shared" si="38"/>
+        <v>63798.609000000004</v>
       </c>
       <c r="W44">
-        <f t="shared" si="67"/>
-        <v>4387.5</v>
+        <f t="shared" si="39"/>
+        <v>3500.7000000000003</v>
       </c>
       <c r="X44">
-        <f t="shared" si="68"/>
-        <v>1123.5</v>
+        <f t="shared" si="40"/>
+        <v>1132.5</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="15"/>
-        <v>645975</v>
+        <f t="shared" si="14"/>
+        <v>371876</v>
       </c>
     </row>
     <row r="45" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4569,72 +4640,72 @@
         <v>747</v>
       </c>
       <c r="G45">
-        <f t="shared" ref="G45:H45" si="75">G44+8</f>
+        <f t="shared" ref="G45:H45" si="47">G44+8</f>
         <v>747</v>
       </c>
       <c r="H45">
-        <f t="shared" si="75"/>
+        <f t="shared" si="47"/>
         <v>801</v>
       </c>
       <c r="J45" s="3">
-        <f t="shared" si="55"/>
-        <v>14720</v>
+        <f t="shared" si="0"/>
+        <v>14750</v>
       </c>
       <c r="K45" s="3">
-        <f t="shared" si="56"/>
-        <v>3785</v>
+        <f t="shared" si="1"/>
+        <v>3815</v>
       </c>
       <c r="L45" s="3">
-        <f t="shared" si="57"/>
-        <v>2934</v>
+        <f t="shared" si="2"/>
+        <v>3667.5</v>
       </c>
       <c r="M45">
-        <f t="shared" si="58"/>
-        <v>2465.1</v>
+        <f t="shared" si="3"/>
+        <v>2091.6</v>
       </c>
       <c r="N45">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1760.3999999999999</v>
       </c>
       <c r="O45">
-        <f t="shared" si="60"/>
-        <v>1792.8</v>
+        <f t="shared" si="5"/>
+        <v>1419.3000000000002</v>
       </c>
       <c r="P45">
-        <f t="shared" si="61"/>
-        <v>3573.5</v>
+        <f t="shared" si="6"/>
+        <v>2075.5</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="62"/>
-        <v>2241</v>
+        <f t="shared" si="7"/>
+        <v>1568.7</v>
       </c>
       <c r="R45">
-        <f t="shared" si="63"/>
-        <v>2961</v>
+        <f t="shared" si="8"/>
+        <v>2363.4</v>
       </c>
       <c r="T45">
-        <f t="shared" si="64"/>
-        <v>12261.465599999998</v>
+        <f t="shared" si="36"/>
+        <v>11460.086250000002</v>
       </c>
       <c r="U45">
-        <f t="shared" si="65"/>
-        <v>482342.09625000006</v>
+        <f t="shared" si="37"/>
+        <v>298825.30125000002</v>
       </c>
       <c r="V45">
-        <f t="shared" si="66"/>
-        <v>160164.26999999999</v>
+        <f t="shared" si="38"/>
+        <v>65116.737000000001</v>
       </c>
       <c r="W45">
-        <f t="shared" si="67"/>
-        <v>4441.5</v>
+        <f t="shared" si="39"/>
+        <v>3545.1000000000004</v>
       </c>
       <c r="X45">
-        <f t="shared" si="68"/>
-        <v>1135.5</v>
+        <f t="shared" si="40"/>
+        <v>1144.5</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="15"/>
-        <v>660344</v>
+        <f t="shared" si="14"/>
+        <v>380091</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4651,80 +4722,80 @@
         <v>353033</v>
       </c>
       <c r="E46">
-        <f t="shared" ref="E46:E53" si="76">E45+20</f>
+        <f t="shared" ref="E46:E53" si="48">E45+20</f>
         <v>1487</v>
       </c>
       <c r="F46">
-        <f t="shared" ref="F46:F53" si="77">F45+8</f>
+        <f t="shared" ref="F46:F53" si="49">F45+8</f>
         <v>755</v>
       </c>
       <c r="G46">
-        <f t="shared" ref="G46:G53" si="78">G45+8</f>
+        <f t="shared" ref="G46:G53" si="50">G45+8</f>
         <v>755</v>
       </c>
       <c r="H46">
-        <f t="shared" ref="H46:H53" si="79">H45+8</f>
+        <f t="shared" ref="H46:H53" si="51">H45+8</f>
         <v>809</v>
       </c>
       <c r="J46" s="3">
-        <f t="shared" si="55"/>
-        <v>14920</v>
+        <f t="shared" si="0"/>
+        <v>14950</v>
       </c>
       <c r="K46" s="3">
-        <f t="shared" si="56"/>
-        <v>3825</v>
+        <f t="shared" si="1"/>
+        <v>3855</v>
       </c>
       <c r="L46" s="3">
-        <f t="shared" si="57"/>
-        <v>2974</v>
+        <f t="shared" si="2"/>
+        <v>3717.5</v>
       </c>
       <c r="M46">
-        <f t="shared" si="58"/>
-        <v>2491.5</v>
+        <f t="shared" si="3"/>
+        <v>2114</v>
       </c>
       <c r="N46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1784.3999999999999</v>
       </c>
       <c r="O46">
-        <f t="shared" si="60"/>
-        <v>1812</v>
+        <f t="shared" si="5"/>
+        <v>1434.5</v>
       </c>
       <c r="P46">
-        <f t="shared" si="61"/>
-        <v>3609.5</v>
+        <f t="shared" si="6"/>
+        <v>2095.5</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="62"/>
-        <v>2265</v>
+        <f t="shared" si="7"/>
+        <v>1585.5</v>
       </c>
       <c r="R46">
-        <f t="shared" si="63"/>
-        <v>2997</v>
+        <f t="shared" si="8"/>
+        <v>2393</v>
       </c>
       <c r="T46">
-        <f t="shared" si="64"/>
-        <v>12524.743199999999</v>
+        <f t="shared" si="36"/>
+        <v>11703.383249999999</v>
       </c>
       <c r="U46">
-        <f t="shared" si="65"/>
-        <v>493193.05625000002</v>
+        <f t="shared" si="37"/>
+        <v>305497.70624999999</v>
       </c>
       <c r="V46">
-        <f t="shared" si="66"/>
-        <v>163510.35</v>
+        <f t="shared" si="38"/>
+        <v>66448.304999999993</v>
       </c>
       <c r="W46">
-        <f t="shared" si="67"/>
-        <v>4495.5</v>
+        <f t="shared" si="39"/>
+        <v>3589.5</v>
       </c>
       <c r="X46">
-        <f t="shared" si="68"/>
-        <v>1147.5</v>
+        <f t="shared" si="40"/>
+        <v>1156.5</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="15"/>
-        <v>674871</v>
+        <f t="shared" si="14"/>
+        <v>388395</v>
       </c>
     </row>
     <row r="47" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4741,80 +4812,80 @@
         <v>392400</v>
       </c>
       <c r="E47">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1507</v>
       </c>
       <c r="F47">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>763</v>
       </c>
       <c r="G47">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>763</v>
       </c>
       <c r="H47">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>817</v>
       </c>
       <c r="J47" s="3">
-        <f t="shared" si="55"/>
-        <v>15120</v>
+        <f t="shared" si="0"/>
+        <v>15150</v>
       </c>
       <c r="K47" s="3">
-        <f t="shared" si="56"/>
-        <v>3865</v>
+        <f t="shared" si="1"/>
+        <v>3895</v>
       </c>
       <c r="L47" s="3">
-        <f t="shared" si="57"/>
-        <v>3014</v>
+        <f t="shared" si="2"/>
+        <v>3767.5</v>
       </c>
       <c r="M47">
-        <f t="shared" si="58"/>
-        <v>2517.9</v>
+        <f t="shared" si="3"/>
+        <v>2136.3999999999996</v>
       </c>
       <c r="N47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1808.3999999999999</v>
       </c>
       <c r="O47">
-        <f t="shared" si="60"/>
-        <v>1831.2</v>
+        <f t="shared" si="5"/>
+        <v>1449.7</v>
       </c>
       <c r="P47">
-        <f t="shared" si="61"/>
-        <v>3645.5</v>
+        <f t="shared" si="6"/>
+        <v>2115.5</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="62"/>
-        <v>2289</v>
+        <f t="shared" si="7"/>
+        <v>1602.3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="63"/>
-        <v>3033</v>
+        <f t="shared" si="8"/>
+        <v>2422.6</v>
       </c>
       <c r="T47">
-        <f t="shared" si="64"/>
-        <v>12790.612799999999</v>
+        <f t="shared" si="36"/>
+        <v>11949.032249999998</v>
       </c>
       <c r="U47">
-        <f t="shared" si="65"/>
-        <v>504163.53624999995</v>
+        <f t="shared" si="37"/>
+        <v>312242.51124999998</v>
       </c>
       <c r="V47">
-        <f t="shared" si="66"/>
-        <v>166890.99</v>
+        <f t="shared" si="38"/>
+        <v>67793.312999999995</v>
       </c>
       <c r="W47">
-        <f t="shared" si="67"/>
-        <v>4549.5</v>
+        <f t="shared" si="39"/>
+        <v>3633.8999999999996</v>
       </c>
       <c r="X47">
-        <f t="shared" si="68"/>
-        <v>1159.5</v>
+        <f t="shared" si="40"/>
+        <v>1168.5</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="15"/>
-        <v>689554</v>
+        <f t="shared" si="14"/>
+        <v>396787</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4831,80 +4902,80 @@
         <v>432267</v>
       </c>
       <c r="E48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1527</v>
       </c>
       <c r="F48">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>771</v>
       </c>
       <c r="G48">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>771</v>
       </c>
       <c r="H48">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>825</v>
       </c>
       <c r="J48" s="3">
-        <f t="shared" si="55"/>
-        <v>15320</v>
+        <f t="shared" si="0"/>
+        <v>15350</v>
       </c>
       <c r="K48" s="3">
-        <f t="shared" si="56"/>
-        <v>3905</v>
+        <f t="shared" si="1"/>
+        <v>3935</v>
       </c>
       <c r="L48" s="3">
-        <f t="shared" si="57"/>
-        <v>3054</v>
+        <f t="shared" si="2"/>
+        <v>3817.5</v>
       </c>
       <c r="M48">
-        <f t="shared" si="58"/>
-        <v>2544.3000000000002</v>
+        <f t="shared" si="3"/>
+        <v>2158.8000000000002</v>
       </c>
       <c r="N48">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1832.3999999999999</v>
       </c>
       <c r="O48">
-        <f t="shared" si="60"/>
-        <v>1850.3999999999999</v>
+        <f t="shared" si="5"/>
+        <v>1464.9</v>
       </c>
       <c r="P48">
-        <f t="shared" si="61"/>
-        <v>3681.5</v>
+        <f t="shared" si="6"/>
+        <v>2135.5</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="62"/>
-        <v>2313</v>
+        <f t="shared" si="7"/>
+        <v>1619.1000000000001</v>
       </c>
       <c r="R48">
-        <f t="shared" si="63"/>
-        <v>3069</v>
+        <f t="shared" si="8"/>
+        <v>2452.1999999999998</v>
       </c>
       <c r="T48">
-        <f t="shared" si="64"/>
-        <v>13059.074399999998</v>
+        <f t="shared" si="36"/>
+        <v>12197.033249999999</v>
       </c>
       <c r="U48">
-        <f t="shared" si="65"/>
-        <v>515253.53624999995</v>
+        <f t="shared" si="37"/>
+        <v>319059.71625</v>
       </c>
       <c r="V48">
-        <f t="shared" si="66"/>
-        <v>170306.19</v>
+        <f t="shared" si="38"/>
+        <v>69151.760999999999</v>
       </c>
       <c r="W48">
-        <f t="shared" si="67"/>
-        <v>4603.5</v>
+        <f t="shared" si="39"/>
+        <v>3678.2999999999997</v>
       </c>
       <c r="X48">
-        <f t="shared" si="68"/>
-        <v>1171.5</v>
+        <f t="shared" si="40"/>
+        <v>1180.5</v>
       </c>
       <c r="Y48">
-        <f t="shared" si="15"/>
-        <v>704393</v>
+        <f t="shared" si="14"/>
+        <v>405267</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -4921,80 +4992,80 @@
         <v>472133</v>
       </c>
       <c r="E49">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1547</v>
       </c>
       <c r="F49">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>779</v>
       </c>
       <c r="G49">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>779</v>
       </c>
       <c r="H49">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>833</v>
       </c>
       <c r="J49" s="3">
-        <f t="shared" si="55"/>
-        <v>15520</v>
+        <f t="shared" si="0"/>
+        <v>15550</v>
       </c>
       <c r="K49" s="3">
-        <f t="shared" si="56"/>
-        <v>3945</v>
+        <f t="shared" si="1"/>
+        <v>3975</v>
       </c>
       <c r="L49" s="3">
-        <f t="shared" si="57"/>
-        <v>3094</v>
+        <f t="shared" si="2"/>
+        <v>3867.5</v>
       </c>
       <c r="M49">
-        <f t="shared" si="58"/>
-        <v>2570.6999999999998</v>
+        <f t="shared" si="3"/>
+        <v>2181.1999999999998</v>
       </c>
       <c r="N49">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1856.3999999999999</v>
       </c>
       <c r="O49">
-        <f t="shared" si="60"/>
-        <v>1869.6</v>
+        <f t="shared" si="5"/>
+        <v>1480.1000000000001</v>
       </c>
       <c r="P49">
-        <f t="shared" si="61"/>
-        <v>3717.5</v>
+        <f t="shared" si="6"/>
+        <v>2155.5</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="62"/>
-        <v>2337</v>
+        <f t="shared" si="7"/>
+        <v>1635.9</v>
       </c>
       <c r="R49">
-        <f t="shared" si="63"/>
-        <v>3105</v>
+        <f t="shared" si="8"/>
+        <v>2481.8000000000002</v>
       </c>
       <c r="T49">
-        <f t="shared" si="64"/>
-        <v>13330.128000000001</v>
+        <f t="shared" si="36"/>
+        <v>12447.38625</v>
       </c>
       <c r="U49">
-        <f t="shared" si="65"/>
-        <v>526463.05625000002</v>
+        <f t="shared" si="37"/>
+        <v>325949.32124999998</v>
       </c>
       <c r="V49">
-        <f t="shared" si="66"/>
-        <v>173755.95</v>
+        <f t="shared" si="38"/>
+        <v>70523.649000000005</v>
       </c>
       <c r="W49">
-        <f t="shared" si="67"/>
-        <v>4657.5</v>
+        <f t="shared" si="39"/>
+        <v>3722.7000000000003</v>
       </c>
       <c r="X49">
-        <f t="shared" si="68"/>
-        <v>1183.5</v>
+        <f t="shared" si="40"/>
+        <v>1192.5</v>
       </c>
       <c r="Y49">
-        <f t="shared" si="15"/>
-        <v>719390</v>
+        <f t="shared" si="14"/>
+        <v>413835</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5011,80 +5082,80 @@
         <v>512000</v>
       </c>
       <c r="E50">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1567</v>
       </c>
       <c r="F50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>787</v>
       </c>
       <c r="G50">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>787</v>
       </c>
       <c r="H50">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>841</v>
       </c>
       <c r="J50" s="3">
-        <f t="shared" si="55"/>
-        <v>15720</v>
+        <f t="shared" si="0"/>
+        <v>15750</v>
       </c>
       <c r="K50" s="3">
-        <f t="shared" si="56"/>
-        <v>3985</v>
+        <f t="shared" si="1"/>
+        <v>4015</v>
       </c>
       <c r="L50" s="3">
-        <f t="shared" si="57"/>
-        <v>3134</v>
+        <f t="shared" si="2"/>
+        <v>3917.5</v>
       </c>
       <c r="M50">
-        <f t="shared" si="58"/>
-        <v>2597.1</v>
+        <f t="shared" si="3"/>
+        <v>2203.6</v>
       </c>
       <c r="N50">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1880.3999999999999</v>
       </c>
       <c r="O50">
-        <f t="shared" si="60"/>
-        <v>1888.8</v>
+        <f t="shared" si="5"/>
+        <v>1495.3000000000002</v>
       </c>
       <c r="P50">
-        <f t="shared" si="61"/>
-        <v>3753.5</v>
+        <f t="shared" si="6"/>
+        <v>2175.5</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="62"/>
-        <v>2361</v>
+        <f t="shared" si="7"/>
+        <v>1652.7</v>
       </c>
       <c r="R50">
-        <f t="shared" si="63"/>
-        <v>3141</v>
+        <f t="shared" si="8"/>
+        <v>2511.4</v>
       </c>
       <c r="T50">
-        <f t="shared" si="64"/>
-        <v>13603.773599999999</v>
+        <f t="shared" si="36"/>
+        <v>12700.091250000001</v>
       </c>
       <c r="U50">
-        <f t="shared" si="65"/>
-        <v>537792.09625000006</v>
+        <f t="shared" si="37"/>
+        <v>332911.32624999998</v>
       </c>
       <c r="V50">
-        <f t="shared" si="66"/>
-        <v>177240.27</v>
+        <f t="shared" si="38"/>
+        <v>71908.976999999999</v>
       </c>
       <c r="W50">
-        <f t="shared" si="67"/>
-        <v>4711.5</v>
+        <f t="shared" si="39"/>
+        <v>3767.1000000000004</v>
       </c>
       <c r="X50">
-        <f t="shared" si="68"/>
-        <v>1195.5</v>
+        <f t="shared" si="40"/>
+        <v>1204.5</v>
       </c>
       <c r="Y50">
-        <f t="shared" si="15"/>
-        <v>734543</v>
+        <f t="shared" si="14"/>
+        <v>422491</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5101,80 +5172,80 @@
         <v>542300</v>
       </c>
       <c r="E51">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1587</v>
       </c>
       <c r="F51">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>795</v>
       </c>
       <c r="G51">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>795</v>
       </c>
       <c r="H51">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>849</v>
       </c>
       <c r="J51" s="3">
-        <f t="shared" si="55"/>
-        <v>15920</v>
+        <f t="shared" si="0"/>
+        <v>15950</v>
       </c>
       <c r="K51" s="3">
-        <f t="shared" si="56"/>
-        <v>4025</v>
+        <f t="shared" si="1"/>
+        <v>4055</v>
       </c>
       <c r="L51" s="3">
-        <f t="shared" si="57"/>
-        <v>3174</v>
+        <f t="shared" si="2"/>
+        <v>3967.5</v>
       </c>
       <c r="M51">
-        <f t="shared" si="58"/>
-        <v>2623.5</v>
+        <f t="shared" si="3"/>
+        <v>2226</v>
       </c>
       <c r="N51">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1904.3999999999999</v>
       </c>
       <c r="O51">
-        <f t="shared" si="60"/>
-        <v>1908</v>
+        <f t="shared" si="5"/>
+        <v>1510.5</v>
       </c>
       <c r="P51">
-        <f t="shared" si="61"/>
-        <v>3789.5</v>
+        <f t="shared" si="6"/>
+        <v>2195.5</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="62"/>
-        <v>2385</v>
+        <f t="shared" si="7"/>
+        <v>1669.5</v>
       </c>
       <c r="R51">
-        <f t="shared" si="63"/>
-        <v>3177</v>
+        <f t="shared" si="8"/>
+        <v>2541</v>
       </c>
       <c r="T51">
-        <f t="shared" si="64"/>
-        <v>13880.011200000001</v>
+        <f t="shared" si="36"/>
+        <v>12955.148249999997</v>
       </c>
       <c r="U51">
-        <f t="shared" si="65"/>
-        <v>549240.65625</v>
+        <f t="shared" si="37"/>
+        <v>339945.73125000001</v>
       </c>
       <c r="V51">
-        <f t="shared" si="66"/>
-        <v>180759.15</v>
+        <f t="shared" si="38"/>
+        <v>73307.744999999995</v>
       </c>
       <c r="W51">
-        <f t="shared" si="67"/>
-        <v>4765.5</v>
+        <f t="shared" si="39"/>
+        <v>3811.5</v>
       </c>
       <c r="X51">
-        <f t="shared" si="68"/>
-        <v>1207.5</v>
+        <f t="shared" si="40"/>
+        <v>1216.5</v>
       </c>
       <c r="Y51">
-        <f t="shared" si="15"/>
-        <v>749852</v>
+        <f t="shared" si="14"/>
+        <v>431236</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5191,80 +5262,80 @@
         <v>572600</v>
       </c>
       <c r="E52">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1607</v>
       </c>
       <c r="F52">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>803</v>
       </c>
       <c r="G52">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>803</v>
       </c>
       <c r="H52">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>857</v>
       </c>
       <c r="J52" s="3">
-        <f t="shared" si="55"/>
-        <v>16120</v>
+        <f t="shared" si="0"/>
+        <v>16150</v>
       </c>
       <c r="K52" s="3">
-        <f t="shared" si="56"/>
-        <v>4065</v>
+        <f t="shared" si="1"/>
+        <v>4095</v>
       </c>
       <c r="L52" s="3">
-        <f t="shared" si="57"/>
-        <v>3214</v>
+        <f t="shared" si="2"/>
+        <v>4017.5</v>
       </c>
       <c r="M52">
-        <f t="shared" si="58"/>
-        <v>2649.9</v>
+        <f t="shared" si="3"/>
+        <v>2248.3999999999996</v>
       </c>
       <c r="N52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1928.3999999999999</v>
       </c>
       <c r="O52">
-        <f t="shared" si="60"/>
-        <v>1927.1999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1525.7000000000003</v>
       </c>
       <c r="P52">
-        <f t="shared" si="61"/>
-        <v>3825.5</v>
+        <f t="shared" si="6"/>
+        <v>2215.5</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="62"/>
-        <v>2409</v>
+        <f t="shared" si="7"/>
+        <v>1686.3000000000002</v>
       </c>
       <c r="R52">
-        <f t="shared" si="63"/>
-        <v>3213</v>
+        <f t="shared" si="8"/>
+        <v>2570.6</v>
       </c>
       <c r="T52">
-        <f t="shared" si="64"/>
-        <v>14158.8408</v>
+        <f t="shared" si="36"/>
+        <v>13212.557250000002</v>
       </c>
       <c r="U52">
-        <f t="shared" si="65"/>
-        <v>560808.73624999996</v>
+        <f t="shared" si="37"/>
+        <v>347052.53625</v>
       </c>
       <c r="V52">
-        <f t="shared" si="66"/>
-        <v>184312.59</v>
+        <f t="shared" si="38"/>
+        <v>74719.953000000009</v>
       </c>
       <c r="W52">
-        <f t="shared" si="67"/>
-        <v>4819.5</v>
+        <f t="shared" si="39"/>
+        <v>3855.8999999999996</v>
       </c>
       <c r="X52">
-        <f t="shared" si="68"/>
-        <v>1219.5</v>
+        <f t="shared" si="40"/>
+        <v>1228.5</v>
       </c>
       <c r="Y52">
-        <f t="shared" si="15"/>
-        <v>765319</v>
+        <f t="shared" si="14"/>
+        <v>440069</v>
       </c>
     </row>
     <row r="53" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5281,80 +5352,80 @@
         <v>602900</v>
       </c>
       <c r="E53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="48"/>
         <v>1627</v>
       </c>
       <c r="F53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="49"/>
         <v>811</v>
       </c>
       <c r="G53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="50"/>
         <v>811</v>
       </c>
       <c r="H53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="51"/>
         <v>865</v>
       </c>
       <c r="J53" s="3">
-        <f t="shared" si="55"/>
-        <v>16320</v>
+        <f t="shared" si="0"/>
+        <v>16350</v>
       </c>
       <c r="K53" s="3">
-        <f t="shared" si="56"/>
-        <v>4105</v>
+        <f t="shared" si="1"/>
+        <v>4135</v>
       </c>
       <c r="L53" s="3">
-        <f t="shared" si="57"/>
-        <v>3254</v>
+        <f t="shared" si="2"/>
+        <v>4067.5</v>
       </c>
       <c r="M53">
-        <f t="shared" si="58"/>
-        <v>2676.3</v>
+        <f t="shared" si="3"/>
+        <v>2270.8000000000002</v>
       </c>
       <c r="N53">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>1952.3999999999999</v>
       </c>
       <c r="O53">
-        <f t="shared" si="60"/>
-        <v>1946.3999999999999</v>
+        <f t="shared" si="5"/>
+        <v>1540.9</v>
       </c>
       <c r="P53">
-        <f t="shared" si="61"/>
-        <v>3861.5</v>
+        <f t="shared" si="6"/>
+        <v>2235.5</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="62"/>
-        <v>2433</v>
+        <f t="shared" si="7"/>
+        <v>1703.1000000000001</v>
       </c>
       <c r="R53">
-        <f t="shared" si="63"/>
-        <v>3249</v>
+        <f t="shared" si="8"/>
+        <v>2600.1999999999998</v>
       </c>
       <c r="T53">
-        <f t="shared" si="64"/>
-        <v>14440.2624</v>
+        <f t="shared" si="36"/>
+        <v>13472.318249999998</v>
       </c>
       <c r="U53">
-        <f t="shared" si="65"/>
-        <v>572496.33624999993</v>
+        <f t="shared" si="37"/>
+        <v>354231.74124999996</v>
       </c>
       <c r="V53">
-        <f t="shared" si="66"/>
-        <v>187900.59</v>
+        <f t="shared" si="38"/>
+        <v>76145.60100000001</v>
       </c>
       <c r="W53">
-        <f t="shared" si="67"/>
-        <v>4873.5</v>
+        <f t="shared" si="39"/>
+        <v>3900.2999999999997</v>
       </c>
       <c r="X53">
-        <f t="shared" si="68"/>
-        <v>1231.5</v>
+        <f t="shared" si="40"/>
+        <v>1240.5</v>
       </c>
       <c r="Y53">
-        <f t="shared" si="15"/>
-        <v>780942</v>
+        <f t="shared" si="14"/>
+        <v>448990</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5375,76 +5446,76 @@
         <v>2440</v>
       </c>
       <c r="F54">
-        <f t="shared" ref="F54:H54" si="80">FLOOR(F53*1.5,1)</f>
+        <f t="shared" ref="F54:H54" si="52">FLOOR(F53*1.5,1)</f>
         <v>1216</v>
       </c>
       <c r="G54">
-        <f t="shared" si="80"/>
+        <f t="shared" si="52"/>
         <v>1216</v>
       </c>
       <c r="H54">
-        <f t="shared" si="80"/>
+        <f t="shared" si="52"/>
         <v>1297</v>
       </c>
       <c r="J54" s="3">
-        <f t="shared" si="55"/>
-        <v>24450</v>
+        <f t="shared" si="0"/>
+        <v>24480</v>
       </c>
       <c r="K54" s="3">
-        <f t="shared" si="56"/>
-        <v>6130</v>
+        <f t="shared" si="1"/>
+        <v>6160</v>
       </c>
       <c r="L54" s="3">
-        <f t="shared" si="57"/>
-        <v>4880</v>
+        <f t="shared" si="2"/>
+        <v>6100</v>
       </c>
       <c r="M54">
-        <f t="shared" si="58"/>
-        <v>4012.8</v>
+        <f t="shared" si="3"/>
+        <v>3404.7999999999997</v>
       </c>
       <c r="N54">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>2928</v>
       </c>
       <c r="O54">
-        <f t="shared" si="60"/>
-        <v>2918.4</v>
+        <f t="shared" si="5"/>
+        <v>2310.4</v>
       </c>
       <c r="P54">
-        <f t="shared" si="61"/>
-        <v>5765</v>
+        <f t="shared" si="6"/>
+        <v>3302</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="62"/>
-        <v>3648</v>
+        <f t="shared" si="7"/>
+        <v>2553.6000000000004</v>
       </c>
       <c r="R54">
-        <f t="shared" si="63"/>
-        <v>4872</v>
+        <f t="shared" si="8"/>
+        <v>3899.2</v>
       </c>
       <c r="T54">
-        <f t="shared" si="64"/>
-        <v>28776.672000000002</v>
+        <f t="shared" si="36"/>
+        <v>26579.4048</v>
       </c>
       <c r="U54">
-        <f t="shared" si="65"/>
-        <v>1281674.7999999998</v>
+        <f t="shared" si="37"/>
+        <v>784621.24</v>
       </c>
       <c r="V54">
-        <f t="shared" si="66"/>
-        <v>420614.40000000002</v>
+        <f t="shared" si="38"/>
+        <v>168639.74400000004</v>
       </c>
       <c r="W54">
-        <f t="shared" si="67"/>
-        <v>7308</v>
+        <f t="shared" si="39"/>
+        <v>5848.7999999999993</v>
       </c>
       <c r="X54">
-        <f t="shared" si="68"/>
-        <v>1839</v>
+        <f t="shared" si="40"/>
+        <v>1848</v>
       </c>
       <c r="Y54">
-        <f t="shared" si="15"/>
-        <v>1740212</v>
+        <f t="shared" si="14"/>
+        <v>987537</v>
       </c>
     </row>
     <row r="55" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5469,72 +5540,72 @@
         <v>1226</v>
       </c>
       <c r="G55">
-        <f t="shared" ref="G55:H55" si="81">G54+10</f>
+        <f t="shared" ref="G55:H55" si="53">G54+10</f>
         <v>1226</v>
       </c>
       <c r="H55">
-        <f t="shared" si="81"/>
+        <f t="shared" si="53"/>
         <v>1307</v>
       </c>
       <c r="J55" s="3">
-        <f t="shared" si="55"/>
-        <v>24750</v>
+        <f t="shared" si="0"/>
+        <v>24780</v>
       </c>
       <c r="K55" s="3">
-        <f t="shared" si="56"/>
-        <v>6180</v>
+        <f t="shared" si="1"/>
+        <v>6210</v>
       </c>
       <c r="L55" s="3">
-        <f t="shared" si="57"/>
-        <v>4940</v>
+        <f t="shared" si="2"/>
+        <v>6175</v>
       </c>
       <c r="M55">
-        <f t="shared" si="58"/>
-        <v>4045.8</v>
+        <f t="shared" si="3"/>
+        <v>3432.7999999999997</v>
       </c>
       <c r="N55">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>2964</v>
       </c>
       <c r="O55">
-        <f t="shared" si="60"/>
-        <v>2942.4</v>
+        <f t="shared" si="5"/>
+        <v>2329.4</v>
       </c>
       <c r="P55">
-        <f t="shared" si="61"/>
-        <v>5810</v>
+        <f t="shared" si="6"/>
+        <v>3327</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="62"/>
-        <v>3678</v>
+        <f t="shared" si="7"/>
+        <v>2574.6000000000004</v>
       </c>
       <c r="R55">
-        <f t="shared" si="63"/>
-        <v>4922</v>
+        <f t="shared" si="8"/>
+        <v>3941.2</v>
       </c>
       <c r="T55">
-        <f t="shared" si="64"/>
-        <v>29352.510000000002</v>
+        <f t="shared" si="36"/>
+        <v>27109.567799999997</v>
       </c>
       <c r="U55">
-        <f t="shared" si="65"/>
-        <v>1305187.4499999997</v>
+        <f t="shared" si="37"/>
+        <v>799128.76500000001</v>
       </c>
       <c r="V55">
-        <f t="shared" si="66"/>
-        <v>427383.6</v>
+        <f t="shared" si="38"/>
+        <v>171313.88400000002</v>
       </c>
       <c r="W55">
-        <f t="shared" si="67"/>
-        <v>7383</v>
+        <f t="shared" si="39"/>
+        <v>5911.7999999999993</v>
       </c>
       <c r="X55">
-        <f t="shared" si="68"/>
-        <v>1854</v>
+        <f t="shared" si="40"/>
+        <v>1863</v>
       </c>
       <c r="Y55">
-        <f t="shared" si="15"/>
-        <v>1771160</v>
+        <f t="shared" si="14"/>
+        <v>1005327</v>
       </c>
     </row>
     <row r="56" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5551,80 +5622,80 @@
         <v>715133</v>
       </c>
       <c r="E56">
-        <f t="shared" ref="E56:E63" si="82">E55+30</f>
+        <f t="shared" ref="E56:E63" si="54">E55+30</f>
         <v>2500</v>
       </c>
       <c r="F56">
-        <f t="shared" ref="F56:F63" si="83">F55+10</f>
+        <f t="shared" ref="F56:F63" si="55">F55+10</f>
         <v>1236</v>
       </c>
       <c r="G56">
-        <f t="shared" ref="G56:G63" si="84">G55+10</f>
+        <f t="shared" ref="G56:G63" si="56">G55+10</f>
         <v>1236</v>
       </c>
       <c r="H56">
-        <f t="shared" ref="H56:H63" si="85">H55+10</f>
+        <f t="shared" ref="H56:H63" si="57">H55+10</f>
         <v>1317</v>
       </c>
       <c r="J56" s="3">
-        <f t="shared" si="55"/>
-        <v>25050</v>
+        <f t="shared" si="0"/>
+        <v>25080</v>
       </c>
       <c r="K56" s="3">
-        <f t="shared" si="56"/>
-        <v>6230</v>
+        <f t="shared" si="1"/>
+        <v>6260</v>
       </c>
       <c r="L56" s="3">
-        <f t="shared" si="57"/>
-        <v>5000</v>
+        <f t="shared" si="2"/>
+        <v>6250</v>
       </c>
       <c r="M56">
-        <f t="shared" si="58"/>
-        <v>4078.8</v>
+        <f t="shared" si="3"/>
+        <v>3460.7999999999997</v>
       </c>
       <c r="N56">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O56">
-        <f t="shared" si="60"/>
-        <v>2966.4</v>
+        <f t="shared" si="5"/>
+        <v>2348.4</v>
       </c>
       <c r="P56">
-        <f t="shared" si="61"/>
-        <v>5855</v>
+        <f t="shared" si="6"/>
+        <v>3352</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="62"/>
-        <v>3708</v>
+        <f t="shared" si="7"/>
+        <v>2595.6000000000004</v>
       </c>
       <c r="R56">
-        <f t="shared" si="63"/>
-        <v>4972</v>
+        <f t="shared" si="8"/>
+        <v>3983.2</v>
       </c>
       <c r="T56">
-        <f t="shared" si="64"/>
-        <v>29933.748</v>
+        <f t="shared" si="36"/>
+        <v>27644.680799999998</v>
       </c>
       <c r="U56">
-        <f t="shared" si="65"/>
-        <v>1328909.3499999996</v>
+        <f t="shared" si="37"/>
+        <v>813765.04</v>
       </c>
       <c r="V56">
-        <f t="shared" si="66"/>
-        <v>434206.8</v>
+        <f t="shared" si="38"/>
+        <v>174009.02400000003</v>
       </c>
       <c r="W56">
-        <f t="shared" si="67"/>
-        <v>7458</v>
+        <f t="shared" si="39"/>
+        <v>5974.7999999999993</v>
       </c>
       <c r="X56">
-        <f t="shared" si="68"/>
-        <v>1869</v>
+        <f t="shared" si="40"/>
+        <v>1878</v>
       </c>
       <c r="Y56">
-        <f t="shared" si="15"/>
-        <v>1802376</v>
+        <f t="shared" si="14"/>
+        <v>1023271</v>
       </c>
     </row>
     <row r="57" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5641,80 +5712,80 @@
         <v>756100</v>
       </c>
       <c r="E57">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2530</v>
       </c>
       <c r="F57">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1246</v>
       </c>
       <c r="G57">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1246</v>
       </c>
       <c r="H57">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1327</v>
       </c>
       <c r="J57" s="3">
-        <f t="shared" si="55"/>
-        <v>25350</v>
+        <f t="shared" si="0"/>
+        <v>25380</v>
       </c>
       <c r="K57" s="3">
-        <f t="shared" si="56"/>
-        <v>6280</v>
+        <f t="shared" si="1"/>
+        <v>6310</v>
       </c>
       <c r="L57" s="3">
-        <f t="shared" si="57"/>
-        <v>5060</v>
+        <f t="shared" si="2"/>
+        <v>6325</v>
       </c>
       <c r="M57">
-        <f t="shared" si="58"/>
-        <v>4111.8</v>
+        <f t="shared" si="3"/>
+        <v>3488.7999999999997</v>
       </c>
       <c r="N57">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3036</v>
       </c>
       <c r="O57">
-        <f t="shared" si="60"/>
-        <v>2990.4</v>
+        <f t="shared" si="5"/>
+        <v>2367.4</v>
       </c>
       <c r="P57">
-        <f t="shared" si="61"/>
-        <v>5900</v>
+        <f t="shared" si="6"/>
+        <v>3377</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="62"/>
-        <v>3738</v>
+        <f t="shared" si="7"/>
+        <v>2616.6000000000004</v>
       </c>
       <c r="R57">
-        <f t="shared" si="63"/>
-        <v>5022</v>
+        <f t="shared" si="8"/>
+        <v>4025.2</v>
       </c>
       <c r="T57">
-        <f t="shared" si="64"/>
-        <v>30520.385999999991</v>
+        <f t="shared" si="36"/>
+        <v>28184.743799999997</v>
       </c>
       <c r="U57">
-        <f t="shared" si="65"/>
-        <v>1352840.5</v>
+        <f t="shared" si="37"/>
+        <v>828530.06499999994</v>
       </c>
       <c r="V57">
-        <f t="shared" si="66"/>
-        <v>441084</v>
+        <f t="shared" si="38"/>
+        <v>176725.16400000002</v>
       </c>
       <c r="W57">
-        <f t="shared" si="67"/>
-        <v>7533</v>
+        <f t="shared" si="39"/>
+        <v>6037.7999999999993</v>
       </c>
       <c r="X57">
-        <f t="shared" si="68"/>
-        <v>1884</v>
+        <f t="shared" si="40"/>
+        <v>1893</v>
       </c>
       <c r="Y57">
-        <f t="shared" si="15"/>
-        <v>1833861</v>
+        <f t="shared" si="14"/>
+        <v>1041370</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5731,80 +5802,80 @@
         <v>879000</v>
       </c>
       <c r="E58">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2560</v>
       </c>
       <c r="F58">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1256</v>
       </c>
       <c r="G58">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1256</v>
       </c>
       <c r="H58">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1337</v>
       </c>
       <c r="J58" s="3">
-        <f t="shared" si="55"/>
-        <v>25650</v>
+        <f t="shared" si="0"/>
+        <v>25680</v>
       </c>
       <c r="K58" s="3">
-        <f t="shared" si="56"/>
-        <v>6330</v>
+        <f t="shared" si="1"/>
+        <v>6360</v>
       </c>
       <c r="L58" s="3">
-        <f t="shared" si="57"/>
-        <v>5120</v>
+        <f t="shared" si="2"/>
+        <v>6400</v>
       </c>
       <c r="M58">
-        <f t="shared" si="58"/>
-        <v>4144.8</v>
+        <f t="shared" si="3"/>
+        <v>3516.7999999999997</v>
       </c>
       <c r="N58">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3072</v>
       </c>
       <c r="O58">
-        <f t="shared" si="60"/>
-        <v>3014.4</v>
+        <f t="shared" si="5"/>
+        <v>2386.4</v>
       </c>
       <c r="P58">
-        <f t="shared" si="61"/>
-        <v>5945</v>
+        <f t="shared" si="6"/>
+        <v>3402</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="62"/>
-        <v>3768</v>
+        <f t="shared" si="7"/>
+        <v>2637.6000000000004</v>
       </c>
       <c r="R58">
-        <f t="shared" si="63"/>
-        <v>5072</v>
+        <f t="shared" si="8"/>
+        <v>4067.2</v>
       </c>
       <c r="T58">
-        <f t="shared" si="64"/>
-        <v>31112.424000000003</v>
+        <f t="shared" si="36"/>
+        <v>28729.756799999999</v>
       </c>
       <c r="U58">
-        <f t="shared" si="65"/>
-        <v>1376980.8999999997</v>
+        <f t="shared" si="37"/>
+        <v>843423.83999999985</v>
       </c>
       <c r="V58">
-        <f t="shared" si="66"/>
-        <v>448015.2</v>
+        <f t="shared" si="38"/>
+        <v>179462.30400000003</v>
       </c>
       <c r="W58">
-        <f t="shared" si="67"/>
-        <v>7608</v>
+        <f t="shared" si="39"/>
+        <v>6100.7999999999993</v>
       </c>
       <c r="X58">
-        <f t="shared" si="68"/>
-        <v>1899</v>
+        <f t="shared" si="40"/>
+        <v>1908</v>
       </c>
       <c r="Y58">
-        <f t="shared" si="15"/>
-        <v>1865615</v>
+        <f t="shared" si="14"/>
+        <v>1059624</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5821,80 +5892,80 @@
         <v>1001900</v>
       </c>
       <c r="E59">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2590</v>
       </c>
       <c r="F59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1266</v>
       </c>
       <c r="G59">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1266</v>
       </c>
       <c r="H59">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1347</v>
       </c>
       <c r="J59" s="3">
-        <f t="shared" si="55"/>
-        <v>25950</v>
+        <f t="shared" si="0"/>
+        <v>25980</v>
       </c>
       <c r="K59" s="3">
-        <f t="shared" si="56"/>
-        <v>6380</v>
+        <f t="shared" si="1"/>
+        <v>6410</v>
       </c>
       <c r="L59" s="3">
-        <f t="shared" si="57"/>
-        <v>5180</v>
+        <f t="shared" si="2"/>
+        <v>6475</v>
       </c>
       <c r="M59">
-        <f t="shared" si="58"/>
-        <v>4177.8</v>
+        <f t="shared" si="3"/>
+        <v>3544.7999999999997</v>
       </c>
       <c r="N59">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3108</v>
       </c>
       <c r="O59">
-        <f t="shared" si="60"/>
-        <v>3038.4</v>
+        <f t="shared" si="5"/>
+        <v>2405.4</v>
       </c>
       <c r="P59">
-        <f t="shared" si="61"/>
-        <v>5990</v>
+        <f t="shared" si="6"/>
+        <v>3427</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="62"/>
-        <v>3798</v>
+        <f t="shared" si="7"/>
+        <v>2658.6000000000004</v>
       </c>
       <c r="R59">
-        <f t="shared" si="63"/>
-        <v>5122</v>
+        <f t="shared" si="8"/>
+        <v>4109.2</v>
       </c>
       <c r="T59">
-        <f t="shared" si="64"/>
-        <v>31709.861999999997</v>
+        <f t="shared" si="36"/>
+        <v>29279.719800000003</v>
       </c>
       <c r="U59">
-        <f t="shared" si="65"/>
-        <v>1401330.5499999998</v>
+        <f t="shared" si="37"/>
+        <v>858446.36499999976</v>
       </c>
       <c r="V59">
-        <f t="shared" si="66"/>
-        <v>455000.4</v>
+        <f t="shared" si="38"/>
+        <v>182220.44400000002</v>
       </c>
       <c r="W59">
-        <f t="shared" si="67"/>
-        <v>7683</v>
+        <f t="shared" si="39"/>
+        <v>6163.7999999999993</v>
       </c>
       <c r="X59">
-        <f t="shared" si="68"/>
-        <v>1914</v>
+        <f t="shared" si="40"/>
+        <v>1923</v>
       </c>
       <c r="Y59">
-        <f t="shared" si="15"/>
-        <v>1897637</v>
+        <f t="shared" si="14"/>
+        <v>1078033</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -5911,80 +5982,80 @@
         <v>1124800</v>
       </c>
       <c r="E60">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2620</v>
       </c>
       <c r="F60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1276</v>
       </c>
       <c r="G60">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1276</v>
       </c>
       <c r="H60">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1357</v>
       </c>
       <c r="J60" s="3">
-        <f t="shared" si="55"/>
-        <v>26250</v>
+        <f t="shared" si="0"/>
+        <v>26280</v>
       </c>
       <c r="K60" s="3">
-        <f t="shared" si="56"/>
-        <v>6430</v>
+        <f t="shared" si="1"/>
+        <v>6460</v>
       </c>
       <c r="L60" s="3">
-        <f t="shared" si="57"/>
-        <v>5240</v>
+        <f t="shared" si="2"/>
+        <v>6550</v>
       </c>
       <c r="M60">
-        <f t="shared" si="58"/>
-        <v>4210.8</v>
+        <f t="shared" si="3"/>
+        <v>3572.7999999999997</v>
       </c>
       <c r="N60">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3144</v>
       </c>
       <c r="O60">
-        <f t="shared" si="60"/>
-        <v>3062.4</v>
+        <f t="shared" si="5"/>
+        <v>2424.4</v>
       </c>
       <c r="P60">
-        <f t="shared" si="61"/>
-        <v>6035</v>
+        <f t="shared" si="6"/>
+        <v>3452</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="62"/>
-        <v>3828</v>
+        <f t="shared" si="7"/>
+        <v>2679.6000000000004</v>
       </c>
       <c r="R60">
-        <f t="shared" si="63"/>
-        <v>5172</v>
+        <f t="shared" si="8"/>
+        <v>4151.2</v>
       </c>
       <c r="T60">
-        <f t="shared" si="64"/>
-        <v>32312.699999999997</v>
+        <f t="shared" si="36"/>
+        <v>29834.632800000003</v>
       </c>
       <c r="U60">
-        <f t="shared" si="65"/>
-        <v>1425889.4499999997</v>
+        <f t="shared" si="37"/>
+        <v>873597.63999999978</v>
       </c>
       <c r="V60">
-        <f t="shared" si="66"/>
-        <v>462039.6</v>
+        <f t="shared" si="38"/>
+        <v>184999.58400000003</v>
       </c>
       <c r="W60">
-        <f t="shared" si="67"/>
-        <v>7758</v>
+        <f t="shared" si="39"/>
+        <v>6226.7999999999993</v>
       </c>
       <c r="X60">
-        <f t="shared" si="68"/>
-        <v>1929</v>
+        <f t="shared" si="40"/>
+        <v>1938</v>
       </c>
       <c r="Y60">
-        <f t="shared" si="15"/>
-        <v>1929928</v>
+        <f t="shared" si="14"/>
+        <v>1096596</v>
       </c>
     </row>
     <row r="61" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -6001,80 +6072,80 @@
         <v>1217450</v>
       </c>
       <c r="E61">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2650</v>
       </c>
       <c r="F61">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1286</v>
       </c>
       <c r="G61">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1286</v>
       </c>
       <c r="H61">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1367</v>
       </c>
       <c r="J61" s="3">
-        <f t="shared" si="55"/>
-        <v>26550</v>
+        <f t="shared" si="0"/>
+        <v>26580</v>
       </c>
       <c r="K61" s="3">
-        <f t="shared" si="56"/>
-        <v>6480</v>
+        <f t="shared" si="1"/>
+        <v>6510</v>
       </c>
       <c r="L61" s="3">
-        <f t="shared" si="57"/>
-        <v>5300</v>
+        <f t="shared" si="2"/>
+        <v>6625</v>
       </c>
       <c r="M61">
-        <f t="shared" si="58"/>
-        <v>4243.8</v>
+        <f t="shared" si="3"/>
+        <v>3600.7999999999997</v>
       </c>
       <c r="N61">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3180</v>
       </c>
       <c r="O61">
-        <f t="shared" si="60"/>
-        <v>3086.4</v>
+        <f t="shared" si="5"/>
+        <v>2443.4</v>
       </c>
       <c r="P61">
-        <f t="shared" si="61"/>
-        <v>6080</v>
+        <f t="shared" si="6"/>
+        <v>3477</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="62"/>
-        <v>3858</v>
+        <f t="shared" si="7"/>
+        <v>2700.6</v>
       </c>
       <c r="R61">
-        <f t="shared" si="63"/>
-        <v>5222</v>
+        <f t="shared" si="8"/>
+        <v>4193.2</v>
       </c>
       <c r="T61">
-        <f t="shared" si="64"/>
-        <v>32920.938000000002</v>
+        <f t="shared" si="36"/>
+        <v>30394.495800000001</v>
       </c>
       <c r="U61">
-        <f t="shared" si="65"/>
-        <v>1450657.5999999999</v>
+        <f t="shared" si="37"/>
+        <v>888877.6649999998</v>
       </c>
       <c r="V61">
-        <f t="shared" si="66"/>
-        <v>469132.79999999999</v>
+        <f t="shared" si="38"/>
+        <v>187799.72399999999</v>
       </c>
       <c r="W61">
-        <f t="shared" si="67"/>
-        <v>7833</v>
+        <f t="shared" si="39"/>
+        <v>6289.7999999999993</v>
       </c>
       <c r="X61">
-        <f t="shared" si="68"/>
-        <v>1944</v>
+        <f t="shared" si="40"/>
+        <v>1953</v>
       </c>
       <c r="Y61">
-        <f t="shared" si="15"/>
-        <v>1962488</v>
+        <f t="shared" si="14"/>
+        <v>1115314</v>
       </c>
     </row>
     <row r="62" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -6091,80 +6162,80 @@
         <v>1310100</v>
       </c>
       <c r="E62">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2680</v>
       </c>
       <c r="F62">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1296</v>
       </c>
       <c r="G62">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1296</v>
       </c>
       <c r="H62">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1377</v>
       </c>
       <c r="J62" s="3">
-        <f t="shared" si="55"/>
-        <v>26850</v>
+        <f t="shared" si="0"/>
+        <v>26880</v>
       </c>
       <c r="K62" s="3">
-        <f t="shared" si="56"/>
-        <v>6530</v>
+        <f t="shared" si="1"/>
+        <v>6560</v>
       </c>
       <c r="L62" s="3">
-        <f t="shared" si="57"/>
-        <v>5360</v>
+        <f t="shared" si="2"/>
+        <v>6700</v>
       </c>
       <c r="M62">
-        <f t="shared" si="58"/>
-        <v>4276.8</v>
+        <f t="shared" si="3"/>
+        <v>3628.7999999999997</v>
       </c>
       <c r="N62">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3216</v>
       </c>
       <c r="O62">
-        <f t="shared" si="60"/>
-        <v>3110.4</v>
+        <f t="shared" si="5"/>
+        <v>2462.4</v>
       </c>
       <c r="P62">
-        <f t="shared" si="61"/>
-        <v>6125</v>
+        <f t="shared" si="6"/>
+        <v>3502</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="62"/>
-        <v>3888</v>
+        <f t="shared" si="7"/>
+        <v>2721.6</v>
       </c>
       <c r="R62">
-        <f t="shared" si="63"/>
-        <v>5272</v>
+        <f t="shared" si="8"/>
+        <v>4235.2</v>
       </c>
       <c r="T62">
-        <f t="shared" si="64"/>
-        <v>33534.576000000001</v>
+        <f t="shared" si="36"/>
+        <v>30959.308799999999</v>
       </c>
       <c r="U62">
-        <f t="shared" si="65"/>
-        <v>1475634.9999999998</v>
+        <f t="shared" si="37"/>
+        <v>904286.43999999983</v>
       </c>
       <c r="V62">
-        <f t="shared" si="66"/>
-        <v>476280</v>
+        <f t="shared" si="38"/>
+        <v>190620.86399999997</v>
       </c>
       <c r="W62">
-        <f t="shared" si="67"/>
-        <v>7908</v>
+        <f t="shared" si="39"/>
+        <v>6352.7999999999993</v>
       </c>
       <c r="X62">
-        <f t="shared" si="68"/>
-        <v>1959</v>
+        <f t="shared" si="40"/>
+        <v>1968</v>
       </c>
       <c r="Y62">
-        <f t="shared" si="15"/>
-        <v>1995316</v>
+        <f t="shared" si="14"/>
+        <v>1134187</v>
       </c>
     </row>
     <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
@@ -6181,83 +6252,83 @@
         <v>1402750</v>
       </c>
       <c r="E63">
-        <f t="shared" si="82"/>
+        <f t="shared" si="54"/>
         <v>2710</v>
       </c>
       <c r="F63">
-        <f t="shared" si="83"/>
+        <f t="shared" si="55"/>
         <v>1306</v>
       </c>
       <c r="G63">
-        <f t="shared" si="84"/>
+        <f t="shared" si="56"/>
         <v>1306</v>
       </c>
       <c r="H63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="57"/>
         <v>1387</v>
       </c>
       <c r="J63" s="3">
-        <f t="shared" si="55"/>
-        <v>27150</v>
+        <f t="shared" si="0"/>
+        <v>27180</v>
       </c>
       <c r="K63" s="3">
-        <f t="shared" si="56"/>
-        <v>6580</v>
+        <f t="shared" si="1"/>
+        <v>6610</v>
       </c>
       <c r="L63" s="3">
-        <f t="shared" si="57"/>
-        <v>5420</v>
+        <f t="shared" si="2"/>
+        <v>6775</v>
       </c>
       <c r="M63">
-        <f t="shared" si="58"/>
-        <v>4309.8</v>
+        <f t="shared" si="3"/>
+        <v>3656.7999999999997</v>
       </c>
       <c r="N63">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>3252</v>
       </c>
       <c r="O63">
-        <f t="shared" si="60"/>
-        <v>3134.4</v>
+        <f t="shared" si="5"/>
+        <v>2481.4</v>
       </c>
       <c r="P63">
-        <f t="shared" si="61"/>
-        <v>6170</v>
+        <f t="shared" si="6"/>
+        <v>3527</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="62"/>
-        <v>3918</v>
+        <f t="shared" si="7"/>
+        <v>2742.6</v>
       </c>
       <c r="R63">
-        <f t="shared" si="63"/>
-        <v>5322</v>
+        <f t="shared" si="8"/>
+        <v>4277.2</v>
       </c>
       <c r="T63">
-        <f t="shared" si="64"/>
-        <v>34153.614000000001</v>
+        <f t="shared" si="36"/>
+        <v>31529.071799999994</v>
       </c>
       <c r="U63">
-        <f t="shared" si="65"/>
-        <v>1500821.65</v>
+        <f t="shared" si="37"/>
+        <v>919823.96499999985</v>
       </c>
       <c r="V63">
-        <f t="shared" si="66"/>
-        <v>483481.2</v>
+        <f t="shared" si="38"/>
+        <v>193463.00399999999</v>
       </c>
       <c r="W63">
-        <f t="shared" si="67"/>
-        <v>7983</v>
+        <f t="shared" si="39"/>
+        <v>6415.7999999999993</v>
       </c>
       <c r="X63">
-        <f t="shared" si="68"/>
-        <v>1974</v>
+        <f t="shared" si="40"/>
+        <v>1983</v>
       </c>
       <c r="Y63">
-        <f t="shared" si="15"/>
-        <v>2028413</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
+        <f t="shared" si="14"/>
+        <v>1153214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>60</v>
       </c>
@@ -6270,8 +6341,84 @@
       <c r="D64">
         <v>1495400</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E64">
+        <f>E63*1.5</f>
+        <v>4065</v>
+      </c>
+      <c r="F64">
+        <f t="shared" ref="F64:H64" si="58">F63*1.5</f>
+        <v>1959</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="58"/>
+        <v>1959</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="58"/>
+        <v>2080.5</v>
+      </c>
+      <c r="J64" s="3">
+        <f t="shared" si="0"/>
+        <v>40730</v>
+      </c>
+      <c r="K64" s="3">
+        <f t="shared" si="1"/>
+        <v>9875</v>
+      </c>
+      <c r="L64" s="3">
+        <f t="shared" si="2"/>
+        <v>10162.5</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="3"/>
+        <v>5485.2</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="4"/>
+        <v>4878</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="5"/>
+        <v>3722.1000000000004</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="6"/>
+        <v>5240.5</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="7"/>
+        <v>4113.8999999999996</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="8"/>
+        <v>6415.7999999999993</v>
+      </c>
+      <c r="T64">
+        <f t="shared" ref="T64:T94" si="59">J64*(1+N64/1000*0.5 + O64/1000*0.5)*0.3</f>
+        <v>64761.310949999999</v>
+      </c>
+      <c r="U64">
+        <f t="shared" ref="U64:U94" si="60">(L64*0.5+M64*0.5)*P64/100*5</f>
+        <v>2050044.2962500001</v>
+      </c>
+      <c r="V64">
+        <f t="shared" ref="V64:V94" si="61">Q64*P64/100*2</f>
+        <v>431177.859</v>
+      </c>
+      <c r="W64">
+        <f t="shared" ref="W64:W94" si="62">R64*1.5</f>
+        <v>9623.6999999999989</v>
+      </c>
+      <c r="X64">
+        <f t="shared" ref="X64:X94" si="63">K64*0.3</f>
+        <v>2962.5</v>
+      </c>
+      <c r="Y64">
+        <f t="shared" ref="Y64:Y94" si="64">FLOOR(SUM(T64:X64),1)</f>
+        <v>2558569</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>61</v>
       </c>
@@ -6284,8 +6431,84 @@
       <c r="D65">
         <v>1619600</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E65">
+        <f>E64+40</f>
+        <v>4105</v>
+      </c>
+      <c r="F65">
+        <f>F64+20</f>
+        <v>1979</v>
+      </c>
+      <c r="G65">
+        <f t="shared" ref="G65:H65" si="65">G64+20</f>
+        <v>1979</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="65"/>
+        <v>2100.5</v>
+      </c>
+      <c r="J65" s="3">
+        <f t="shared" si="0"/>
+        <v>41130</v>
+      </c>
+      <c r="K65" s="3">
+        <f t="shared" si="1"/>
+        <v>9975</v>
+      </c>
+      <c r="L65" s="3">
+        <f t="shared" si="2"/>
+        <v>10262.5</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="3"/>
+        <v>5541.2</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="4"/>
+        <v>4926</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="5"/>
+        <v>3760.1000000000004</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="6"/>
+        <v>5290.5</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="7"/>
+        <v>4155.8999999999996</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="8"/>
+        <v>6479.7999999999993</v>
+      </c>
+      <c r="T65">
+        <f t="shared" si="59"/>
+        <v>65927.893949999998</v>
+      </c>
+      <c r="U65">
+        <f t="shared" si="60"/>
+        <v>2090236.8712500003</v>
+      </c>
+      <c r="V65">
+        <f t="shared" si="61"/>
+        <v>439735.77899999998</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="62"/>
+        <v>9719.6999999999989</v>
+      </c>
+      <c r="X65">
+        <f t="shared" si="63"/>
+        <v>2992.5</v>
+      </c>
+      <c r="Y65">
+        <f t="shared" si="64"/>
+        <v>2608612</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>62</v>
       </c>
@@ -6298,8 +6521,84 @@
       <c r="D66">
         <v>1743800</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E66">
+        <f t="shared" ref="E66:E73" si="66">E65+40</f>
+        <v>4145</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ref="F66:F73" si="67">F65+20</f>
+        <v>1999</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ref="G66:G73" si="68">G65+20</f>
+        <v>1999</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ref="H66:H73" si="69">H65+20</f>
+        <v>2120.5</v>
+      </c>
+      <c r="J66" s="3">
+        <f t="shared" si="0"/>
+        <v>41530</v>
+      </c>
+      <c r="K66" s="3">
+        <f t="shared" si="1"/>
+        <v>10075</v>
+      </c>
+      <c r="L66" s="3">
+        <f t="shared" si="2"/>
+        <v>10362.5</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="3"/>
+        <v>5597.2</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="4"/>
+        <v>4974</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="5"/>
+        <v>3798.1000000000004</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="6"/>
+        <v>5340.5</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="7"/>
+        <v>4197.8999999999996</v>
+      </c>
+      <c r="R66">
+        <f t="shared" si="8"/>
+        <v>6543.7999999999993</v>
+      </c>
+      <c r="T66">
+        <f t="shared" si="59"/>
+        <v>67104.796950000004</v>
+      </c>
+      <c r="U66">
+        <f t="shared" si="60"/>
+        <v>2130819.4462500005</v>
+      </c>
+      <c r="V66">
+        <f t="shared" si="61"/>
+        <v>448377.69899999996</v>
+      </c>
+      <c r="W66">
+        <f t="shared" si="62"/>
+        <v>9815.6999999999989</v>
+      </c>
+      <c r="X66">
+        <f t="shared" si="63"/>
+        <v>3022.5</v>
+      </c>
+      <c r="Y66">
+        <f t="shared" si="64"/>
+        <v>2659140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>63</v>
       </c>
@@ -6312,8 +6611,84 @@
       <c r="D67">
         <v>1868000</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E67">
+        <f t="shared" si="66"/>
+        <v>4185</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="67"/>
+        <v>2019</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="68"/>
+        <v>2019</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="69"/>
+        <v>2140.5</v>
+      </c>
+      <c r="J67" s="3">
+        <f t="shared" si="0"/>
+        <v>41930</v>
+      </c>
+      <c r="K67" s="3">
+        <f t="shared" si="1"/>
+        <v>10175</v>
+      </c>
+      <c r="L67" s="3">
+        <f t="shared" si="2"/>
+        <v>10462.5</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="3"/>
+        <v>5653.2</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="4"/>
+        <v>5022</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="5"/>
+        <v>3836.1000000000004</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="6"/>
+        <v>5390.5</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="7"/>
+        <v>4239.8999999999996</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="8"/>
+        <v>6607.7999999999993</v>
+      </c>
+      <c r="T67">
+        <f t="shared" si="59"/>
+        <v>68292.019950000002</v>
+      </c>
+      <c r="U67">
+        <f t="shared" si="60"/>
+        <v>2171792.0212500002</v>
+      </c>
+      <c r="V67">
+        <f t="shared" si="61"/>
+        <v>457103.61900000001</v>
+      </c>
+      <c r="W67">
+        <f t="shared" si="62"/>
+        <v>9911.6999999999989</v>
+      </c>
+      <c r="X67">
+        <f t="shared" si="63"/>
+        <v>3052.5</v>
+      </c>
+      <c r="Y67">
+        <f t="shared" si="64"/>
+        <v>2710151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>64</v>
       </c>
@@ -6326,8 +6701,84 @@
       <c r="D68">
         <v>1992900</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E68">
+        <f t="shared" si="66"/>
+        <v>4225</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="67"/>
+        <v>2039</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="68"/>
+        <v>2039</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="69"/>
+        <v>2160.5</v>
+      </c>
+      <c r="J68" s="3">
+        <f t="shared" si="0"/>
+        <v>42330</v>
+      </c>
+      <c r="K68" s="3">
+        <f t="shared" si="1"/>
+        <v>10275</v>
+      </c>
+      <c r="L68" s="3">
+        <f t="shared" si="2"/>
+        <v>10562.5</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="3"/>
+        <v>5709.2</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="4"/>
+        <v>5070</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="5"/>
+        <v>3874.1000000000004</v>
+      </c>
+      <c r="P68">
+        <f t="shared" si="6"/>
+        <v>5440.5</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="7"/>
+        <v>4281.8999999999996</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="8"/>
+        <v>6671.7999999999993</v>
+      </c>
+      <c r="T68">
+        <f t="shared" si="59"/>
+        <v>69489.562950000007</v>
+      </c>
+      <c r="U68">
+        <f t="shared" si="60"/>
+        <v>2213154.5962500004</v>
+      </c>
+      <c r="V68">
+        <f t="shared" si="61"/>
+        <v>465913.53899999999</v>
+      </c>
+      <c r="W68">
+        <f t="shared" si="62"/>
+        <v>10007.699999999999</v>
+      </c>
+      <c r="X68">
+        <f t="shared" si="63"/>
+        <v>3082.5</v>
+      </c>
+      <c r="Y68">
+        <f t="shared" si="64"/>
+        <v>2761647</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>65</v>
       </c>
@@ -6340,8 +6791,84 @@
       <c r="D69">
         <v>2117800</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E69">
+        <f t="shared" si="66"/>
+        <v>4265</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="67"/>
+        <v>2059</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="68"/>
+        <v>2059</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="69"/>
+        <v>2180.5</v>
+      </c>
+      <c r="J69" s="3">
+        <f t="shared" si="0"/>
+        <v>42730</v>
+      </c>
+      <c r="K69" s="3">
+        <f t="shared" si="1"/>
+        <v>10375</v>
+      </c>
+      <c r="L69" s="3">
+        <f t="shared" si="2"/>
+        <v>10662.5</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="3"/>
+        <v>5765.2</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="4"/>
+        <v>5118</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="5"/>
+        <v>3912.1000000000004</v>
+      </c>
+      <c r="P69">
+        <f t="shared" si="6"/>
+        <v>5490.5</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="7"/>
+        <v>4323.8999999999996</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="8"/>
+        <v>6735.7999999999993</v>
+      </c>
+      <c r="T69">
+        <f t="shared" si="59"/>
+        <v>70697.425950000004</v>
+      </c>
+      <c r="U69">
+        <f t="shared" si="60"/>
+        <v>2254907.1712500001</v>
+      </c>
+      <c r="V69">
+        <f t="shared" si="61"/>
+        <v>474807.45899999997</v>
+      </c>
+      <c r="W69">
+        <f t="shared" si="62"/>
+        <v>10103.699999999999</v>
+      </c>
+      <c r="X69">
+        <f t="shared" si="63"/>
+        <v>3112.5</v>
+      </c>
+      <c r="Y69">
+        <f t="shared" si="64"/>
+        <v>2813628</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>66</v>
       </c>
@@ -6354,8 +6881,84 @@
       <c r="D70">
         <v>2242700</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E70">
+        <f t="shared" si="66"/>
+        <v>4305</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="67"/>
+        <v>2079</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="68"/>
+        <v>2079</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="69"/>
+        <v>2200.5</v>
+      </c>
+      <c r="J70" s="3">
+        <f t="shared" ref="J70:J94" si="70" xml:space="preserve"> 80 +E70*10</f>
+        <v>43130</v>
+      </c>
+      <c r="K70" s="3">
+        <f t="shared" ref="K70:K94" si="71" xml:space="preserve"> 80 +F70*5</f>
+        <v>10475</v>
+      </c>
+      <c r="L70" s="3">
+        <f t="shared" ref="L70:L94" si="72" xml:space="preserve"> E70*2.5</f>
+        <v>10762.5</v>
+      </c>
+      <c r="M70">
+        <f t="shared" ref="M70:M94" si="73">F70*2.3+G70*0.5</f>
+        <v>5821.2</v>
+      </c>
+      <c r="N70">
+        <f t="shared" ref="N70:N94" si="74">E70*1.2</f>
+        <v>5166</v>
+      </c>
+      <c r="O70">
+        <f t="shared" ref="O70:O94" si="75">F70*1.1+G70*0.8</f>
+        <v>3950.1000000000004</v>
+      </c>
+      <c r="P70">
+        <f t="shared" ref="P70:P94" si="76" xml:space="preserve"> 100+H70*2 + G70*0.5</f>
+        <v>5540.5</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" ref="Q70:Q94" si="77">G70*1.6+F70*0.5</f>
+        <v>4365.8999999999996</v>
+      </c>
+      <c r="R70">
+        <f t="shared" ref="R70:R94" si="78">G70*1.2 + E70</f>
+        <v>6799.7999999999993</v>
+      </c>
+      <c r="T70">
+        <f t="shared" si="59"/>
+        <v>71915.608950000009</v>
+      </c>
+      <c r="U70">
+        <f t="shared" si="60"/>
+        <v>2297049.7462500003</v>
+      </c>
+      <c r="V70">
+        <f t="shared" si="61"/>
+        <v>483785.37899999996</v>
+      </c>
+      <c r="W70">
+        <f t="shared" si="62"/>
+        <v>10199.699999999999</v>
+      </c>
+      <c r="X70">
+        <f t="shared" si="63"/>
+        <v>3142.5</v>
+      </c>
+      <c r="Y70">
+        <f t="shared" si="64"/>
+        <v>2866092</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>67</v>
       </c>
@@ -6368,8 +6971,84 @@
       <c r="D71">
         <v>2336925</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E71">
+        <f t="shared" si="66"/>
+        <v>4345</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="67"/>
+        <v>2099</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="68"/>
+        <v>2099</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="69"/>
+        <v>2220.5</v>
+      </c>
+      <c r="J71" s="3">
+        <f t="shared" si="70"/>
+        <v>43530</v>
+      </c>
+      <c r="K71" s="3">
+        <f t="shared" si="71"/>
+        <v>10575</v>
+      </c>
+      <c r="L71" s="3">
+        <f t="shared" si="72"/>
+        <v>10862.5</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="73"/>
+        <v>5877.2</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="74"/>
+        <v>5214</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="75"/>
+        <v>3988.1000000000004</v>
+      </c>
+      <c r="P71">
+        <f t="shared" si="76"/>
+        <v>5590.5</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="77"/>
+        <v>4407.8999999999996</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="78"/>
+        <v>6863.7999999999993</v>
+      </c>
+      <c r="T71">
+        <f t="shared" si="59"/>
+        <v>73144.111950000006</v>
+      </c>
+      <c r="U71">
+        <f t="shared" si="60"/>
+        <v>2339582.32125</v>
+      </c>
+      <c r="V71">
+        <f t="shared" si="61"/>
+        <v>492847.299</v>
+      </c>
+      <c r="W71">
+        <f t="shared" si="62"/>
+        <v>10295.699999999999</v>
+      </c>
+      <c r="X71">
+        <f t="shared" si="63"/>
+        <v>3172.5</v>
+      </c>
+      <c r="Y71">
+        <f t="shared" si="64"/>
+        <v>2919041</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>68</v>
       </c>
@@ -6382,8 +7061,84 @@
       <c r="D72">
         <v>2431150</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E72">
+        <f t="shared" si="66"/>
+        <v>4385</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="67"/>
+        <v>2119</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="68"/>
+        <v>2119</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="69"/>
+        <v>2240.5</v>
+      </c>
+      <c r="J72" s="3">
+        <f t="shared" si="70"/>
+        <v>43930</v>
+      </c>
+      <c r="K72" s="3">
+        <f t="shared" si="71"/>
+        <v>10675</v>
+      </c>
+      <c r="L72" s="3">
+        <f t="shared" si="72"/>
+        <v>10962.5</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="73"/>
+        <v>5933.2</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="74"/>
+        <v>5262</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="75"/>
+        <v>4026.1000000000004</v>
+      </c>
+      <c r="P72">
+        <f t="shared" si="76"/>
+        <v>5640.5</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="77"/>
+        <v>4449.8999999999996</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="78"/>
+        <v>6927.7999999999993</v>
+      </c>
+      <c r="T72">
+        <f t="shared" si="59"/>
+        <v>74382.934949999995</v>
+      </c>
+      <c r="U72">
+        <f t="shared" si="60"/>
+        <v>2382504.8962500002</v>
+      </c>
+      <c r="V72">
+        <f t="shared" si="61"/>
+        <v>501993.21899999998</v>
+      </c>
+      <c r="W72">
+        <f t="shared" si="62"/>
+        <v>10391.699999999999</v>
+      </c>
+      <c r="X72">
+        <f t="shared" si="63"/>
+        <v>3202.5</v>
+      </c>
+      <c r="Y72">
+        <f t="shared" si="64"/>
+        <v>2972475</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>69</v>
       </c>
@@ -6396,8 +7151,84 @@
       <c r="D73">
         <v>2525375</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E73">
+        <f t="shared" si="66"/>
+        <v>4425</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="67"/>
+        <v>2139</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="68"/>
+        <v>2139</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="69"/>
+        <v>2260.5</v>
+      </c>
+      <c r="J73" s="3">
+        <f t="shared" si="70"/>
+        <v>44330</v>
+      </c>
+      <c r="K73" s="3">
+        <f t="shared" si="71"/>
+        <v>10775</v>
+      </c>
+      <c r="L73" s="3">
+        <f t="shared" si="72"/>
+        <v>11062.5</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="73"/>
+        <v>5989.2</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="74"/>
+        <v>5310</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="75"/>
+        <v>4064.1000000000004</v>
+      </c>
+      <c r="P73">
+        <f t="shared" si="76"/>
+        <v>5690.5</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="77"/>
+        <v>4491.8999999999996</v>
+      </c>
+      <c r="R73">
+        <f t="shared" si="78"/>
+        <v>6991.7999999999993</v>
+      </c>
+      <c r="T73">
+        <f t="shared" si="59"/>
+        <v>75632.077949999992</v>
+      </c>
+      <c r="U73">
+        <f t="shared" si="60"/>
+        <v>2425817.4712500004</v>
+      </c>
+      <c r="V73">
+        <f t="shared" si="61"/>
+        <v>511223.13899999997</v>
+      </c>
+      <c r="W73">
+        <f t="shared" si="62"/>
+        <v>10487.699999999999</v>
+      </c>
+      <c r="X73">
+        <f t="shared" si="63"/>
+        <v>3232.5</v>
+      </c>
+      <c r="Y73">
+        <f t="shared" si="64"/>
+        <v>3026392</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>70</v>
       </c>
@@ -6410,8 +7241,84 @@
       <c r="D74">
         <v>2619600</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E74">
+        <f>E73*1.5</f>
+        <v>6637.5</v>
+      </c>
+      <c r="F74">
+        <f t="shared" ref="F74:H74" si="79">F73*1.5</f>
+        <v>3208.5</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="79"/>
+        <v>3208.5</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="79"/>
+        <v>3390.75</v>
+      </c>
+      <c r="J74" s="3">
+        <f t="shared" si="70"/>
+        <v>66455</v>
+      </c>
+      <c r="K74" s="3">
+        <f t="shared" si="71"/>
+        <v>16122.5</v>
+      </c>
+      <c r="L74" s="3">
+        <f t="shared" si="72"/>
+        <v>16593.75</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="73"/>
+        <v>8983.7999999999993</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="74"/>
+        <v>7965</v>
+      </c>
+      <c r="O74">
+        <f t="shared" si="75"/>
+        <v>6096.1500000000005</v>
+      </c>
+      <c r="P74">
+        <f t="shared" si="76"/>
+        <v>8485.75</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="77"/>
+        <v>6737.85</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="78"/>
+        <v>10487.7</v>
+      </c>
+      <c r="T74">
+        <f t="shared" si="59"/>
+        <v>160101.55848750001</v>
+      </c>
+      <c r="U74">
+        <f t="shared" si="60"/>
+        <v>5426117.3728124993</v>
+      </c>
+      <c r="V74">
+        <f t="shared" si="61"/>
+        <v>1143514.2127499999</v>
+      </c>
+      <c r="W74">
+        <f t="shared" si="62"/>
+        <v>15731.550000000001</v>
+      </c>
+      <c r="X74">
+        <f t="shared" si="63"/>
+        <v>4836.75</v>
+      </c>
+      <c r="Y74">
+        <f t="shared" si="64"/>
+        <v>6750301</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>71</v>
       </c>
@@ -6424,8 +7331,84 @@
       <c r="D75">
         <v>2996500</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E75">
+        <f t="shared" ref="E75" si="80">E74+40</f>
+        <v>6677.5</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ref="F75" si="81">F74+20</f>
+        <v>3228.5</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ref="G75" si="82">G74+20</f>
+        <v>3228.5</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ref="H75" si="83">H74+20</f>
+        <v>3410.75</v>
+      </c>
+      <c r="J75" s="3">
+        <f t="shared" si="70"/>
+        <v>66855</v>
+      </c>
+      <c r="K75" s="3">
+        <f t="shared" si="71"/>
+        <v>16222.5</v>
+      </c>
+      <c r="L75" s="3">
+        <f t="shared" si="72"/>
+        <v>16693.75</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="73"/>
+        <v>9039.7999999999993</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="74"/>
+        <v>8013</v>
+      </c>
+      <c r="O75">
+        <f t="shared" si="75"/>
+        <v>6134.1500000000005</v>
+      </c>
+      <c r="P75">
+        <f t="shared" si="76"/>
+        <v>8535.75</v>
+      </c>
+      <c r="Q75">
+        <f t="shared" si="77"/>
+        <v>6779.85</v>
+      </c>
+      <c r="R75">
+        <f t="shared" si="78"/>
+        <v>10551.7</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="59"/>
+        <v>161927.6569875</v>
+      </c>
+      <c r="U75">
+        <f t="shared" si="60"/>
+        <v>5491378.7353124991</v>
+      </c>
+      <c r="V75">
+        <f t="shared" si="61"/>
+        <v>1157422.0927500001</v>
+      </c>
+      <c r="W75">
+        <f t="shared" si="62"/>
+        <v>15827.550000000001</v>
+      </c>
+      <c r="X75">
+        <f t="shared" si="63"/>
+        <v>4866.75</v>
+      </c>
+      <c r="Y75">
+        <f t="shared" si="64"/>
+        <v>6831422</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>72</v>
       </c>
@@ -6438,8 +7421,84 @@
       <c r="D76">
         <v>3373400</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E76">
+        <f t="shared" ref="E76:E83" si="84">E75+40</f>
+        <v>6717.5</v>
+      </c>
+      <c r="F76">
+        <f t="shared" ref="F76:F83" si="85">F75+20</f>
+        <v>3248.5</v>
+      </c>
+      <c r="G76">
+        <f t="shared" ref="G76:G83" si="86">G75+20</f>
+        <v>3248.5</v>
+      </c>
+      <c r="H76">
+        <f t="shared" ref="H76:H83" si="87">H75+20</f>
+        <v>3430.75</v>
+      </c>
+      <c r="J76" s="3">
+        <f t="shared" si="70"/>
+        <v>67255</v>
+      </c>
+      <c r="K76" s="3">
+        <f t="shared" si="71"/>
+        <v>16322.5</v>
+      </c>
+      <c r="L76" s="3">
+        <f t="shared" si="72"/>
+        <v>16793.75</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="73"/>
+        <v>9095.7999999999993</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="74"/>
+        <v>8061</v>
+      </c>
+      <c r="O76">
+        <f t="shared" si="75"/>
+        <v>6172.1500000000005</v>
+      </c>
+      <c r="P76">
+        <f t="shared" si="76"/>
+        <v>8585.75</v>
+      </c>
+      <c r="Q76">
+        <f t="shared" si="77"/>
+        <v>6821.85</v>
+      </c>
+      <c r="R76">
+        <f t="shared" si="78"/>
+        <v>10615.7</v>
+      </c>
+      <c r="T76">
+        <f t="shared" si="59"/>
+        <v>163764.0754875</v>
+      </c>
+      <c r="U76">
+        <f t="shared" si="60"/>
+        <v>5557030.0978124999</v>
+      </c>
+      <c r="V76">
+        <f t="shared" si="61"/>
+        <v>1171413.97275</v>
+      </c>
+      <c r="W76">
+        <f t="shared" si="62"/>
+        <v>15923.550000000001</v>
+      </c>
+      <c r="X76">
+        <f t="shared" si="63"/>
+        <v>4896.75</v>
+      </c>
+      <c r="Y76">
+        <f t="shared" si="64"/>
+        <v>6913028</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>73</v>
       </c>
@@ -6452,8 +7511,84 @@
       <c r="D77">
         <v>3750300</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E77">
+        <f t="shared" si="84"/>
+        <v>6757.5</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="85"/>
+        <v>3268.5</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="86"/>
+        <v>3268.5</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="87"/>
+        <v>3450.75</v>
+      </c>
+      <c r="J77" s="3">
+        <f t="shared" si="70"/>
+        <v>67655</v>
+      </c>
+      <c r="K77" s="3">
+        <f t="shared" si="71"/>
+        <v>16422.5</v>
+      </c>
+      <c r="L77" s="3">
+        <f t="shared" si="72"/>
+        <v>16893.75</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="73"/>
+        <v>9151.7999999999993</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="74"/>
+        <v>8109</v>
+      </c>
+      <c r="O77">
+        <f t="shared" si="75"/>
+        <v>6210.1500000000005</v>
+      </c>
+      <c r="P77">
+        <f t="shared" si="76"/>
+        <v>8635.75</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="77"/>
+        <v>6863.85</v>
+      </c>
+      <c r="R77">
+        <f t="shared" si="78"/>
+        <v>10679.7</v>
+      </c>
+      <c r="T77">
+        <f t="shared" si="59"/>
+        <v>165610.81398749998</v>
+      </c>
+      <c r="U77">
+        <f t="shared" si="60"/>
+        <v>5623071.4603125006</v>
+      </c>
+      <c r="V77">
+        <f t="shared" si="61"/>
+        <v>1185489.8527500001</v>
+      </c>
+      <c r="W77">
+        <f t="shared" si="62"/>
+        <v>16019.550000000001</v>
+      </c>
+      <c r="X77">
+        <f t="shared" si="63"/>
+        <v>4926.75</v>
+      </c>
+      <c r="Y77">
+        <f t="shared" si="64"/>
+        <v>6995118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>74</v>
       </c>
@@ -6466,8 +7601,84 @@
       <c r="D78">
         <v>4128000</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E78">
+        <f t="shared" si="84"/>
+        <v>6797.5</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="85"/>
+        <v>3288.5</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="86"/>
+        <v>3288.5</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="87"/>
+        <v>3470.75</v>
+      </c>
+      <c r="J78" s="3">
+        <f t="shared" si="70"/>
+        <v>68055</v>
+      </c>
+      <c r="K78" s="3">
+        <f t="shared" si="71"/>
+        <v>16522.5</v>
+      </c>
+      <c r="L78" s="3">
+        <f t="shared" si="72"/>
+        <v>16993.75</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="73"/>
+        <v>9207.7999999999993</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="74"/>
+        <v>8157</v>
+      </c>
+      <c r="O78">
+        <f t="shared" si="75"/>
+        <v>6248.1500000000005</v>
+      </c>
+      <c r="P78">
+        <f t="shared" si="76"/>
+        <v>8685.75</v>
+      </c>
+      <c r="Q78">
+        <f t="shared" si="77"/>
+        <v>6905.85</v>
+      </c>
+      <c r="R78">
+        <f t="shared" si="78"/>
+        <v>10743.7</v>
+      </c>
+      <c r="T78">
+        <f t="shared" si="59"/>
+        <v>167467.87248749999</v>
+      </c>
+      <c r="U78">
+        <f t="shared" si="60"/>
+        <v>5689502.8228124995</v>
+      </c>
+      <c r="V78">
+        <f t="shared" si="61"/>
+        <v>1199649.73275</v>
+      </c>
+      <c r="W78">
+        <f t="shared" si="62"/>
+        <v>16115.550000000001</v>
+      </c>
+      <c r="X78">
+        <f t="shared" si="63"/>
+        <v>4956.75</v>
+      </c>
+      <c r="Y78">
+        <f t="shared" si="64"/>
+        <v>7077692</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>75</v>
       </c>
@@ -6480,8 +7691,84 @@
       <c r="D79">
         <v>4505700</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E79">
+        <f t="shared" si="84"/>
+        <v>6837.5</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="85"/>
+        <v>3308.5</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="86"/>
+        <v>3308.5</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="87"/>
+        <v>3490.75</v>
+      </c>
+      <c r="J79" s="3">
+        <f t="shared" si="70"/>
+        <v>68455</v>
+      </c>
+      <c r="K79" s="3">
+        <f t="shared" si="71"/>
+        <v>16622.5</v>
+      </c>
+      <c r="L79" s="3">
+        <f t="shared" si="72"/>
+        <v>17093.75</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="73"/>
+        <v>9263.7999999999993</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="74"/>
+        <v>8205</v>
+      </c>
+      <c r="O79">
+        <f t="shared" si="75"/>
+        <v>6286.1500000000005</v>
+      </c>
+      <c r="P79">
+        <f t="shared" si="76"/>
+        <v>8735.75</v>
+      </c>
+      <c r="Q79">
+        <f t="shared" si="77"/>
+        <v>6947.85</v>
+      </c>
+      <c r="R79">
+        <f t="shared" si="78"/>
+        <v>10807.7</v>
+      </c>
+      <c r="T79">
+        <f t="shared" si="59"/>
+        <v>169335.25098749998</v>
+      </c>
+      <c r="U79">
+        <f t="shared" si="60"/>
+        <v>5756324.1853125002</v>
+      </c>
+      <c r="V79">
+        <f t="shared" si="61"/>
+        <v>1213893.6127500001</v>
+      </c>
+      <c r="W79">
+        <f t="shared" si="62"/>
+        <v>16211.550000000001</v>
+      </c>
+      <c r="X79">
+        <f t="shared" si="63"/>
+        <v>4986.75</v>
+      </c>
+      <c r="Y79">
+        <f t="shared" si="64"/>
+        <v>7160751</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>76</v>
       </c>
@@ -6494,8 +7781,84 @@
       <c r="D80">
         <v>4883400</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E80">
+        <f t="shared" si="84"/>
+        <v>6877.5</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="85"/>
+        <v>3328.5</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="86"/>
+        <v>3328.5</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="87"/>
+        <v>3510.75</v>
+      </c>
+      <c r="J80" s="3">
+        <f t="shared" si="70"/>
+        <v>68855</v>
+      </c>
+      <c r="K80" s="3">
+        <f t="shared" si="71"/>
+        <v>16722.5</v>
+      </c>
+      <c r="L80" s="3">
+        <f t="shared" si="72"/>
+        <v>17193.75</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="73"/>
+        <v>9319.7999999999993</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="74"/>
+        <v>8253</v>
+      </c>
+      <c r="O80">
+        <f t="shared" si="75"/>
+        <v>6324.1500000000005</v>
+      </c>
+      <c r="P80">
+        <f t="shared" si="76"/>
+        <v>8785.75</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" si="77"/>
+        <v>6989.85</v>
+      </c>
+      <c r="R80">
+        <f t="shared" si="78"/>
+        <v>10871.7</v>
+      </c>
+      <c r="T80">
+        <f t="shared" si="59"/>
+        <v>171212.94948749998</v>
+      </c>
+      <c r="U80">
+        <f t="shared" si="60"/>
+        <v>5823535.5478124991</v>
+      </c>
+      <c r="V80">
+        <f t="shared" si="61"/>
+        <v>1228221.49275</v>
+      </c>
+      <c r="W80">
+        <f t="shared" si="62"/>
+        <v>16307.550000000001</v>
+      </c>
+      <c r="X80">
+        <f t="shared" si="63"/>
+        <v>5016.75</v>
+      </c>
+      <c r="Y80">
+        <f t="shared" si="64"/>
+        <v>7244294</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>77</v>
       </c>
@@ -6508,8 +7871,84 @@
       <c r="D81">
         <v>5167300</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E81">
+        <f t="shared" si="84"/>
+        <v>6917.5</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="85"/>
+        <v>3348.5</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="86"/>
+        <v>3348.5</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="87"/>
+        <v>3530.75</v>
+      </c>
+      <c r="J81" s="3">
+        <f t="shared" si="70"/>
+        <v>69255</v>
+      </c>
+      <c r="K81" s="3">
+        <f t="shared" si="71"/>
+        <v>16822.5</v>
+      </c>
+      <c r="L81" s="3">
+        <f t="shared" si="72"/>
+        <v>17293.75</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="73"/>
+        <v>9375.7999999999993</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="74"/>
+        <v>8301</v>
+      </c>
+      <c r="O81">
+        <f t="shared" si="75"/>
+        <v>6362.1500000000005</v>
+      </c>
+      <c r="P81">
+        <f t="shared" si="76"/>
+        <v>8835.75</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="77"/>
+        <v>7031.85</v>
+      </c>
+      <c r="R81">
+        <f t="shared" si="78"/>
+        <v>10935.7</v>
+      </c>
+      <c r="T81">
+        <f t="shared" si="59"/>
+        <v>173100.96798749999</v>
+      </c>
+      <c r="U81">
+        <f t="shared" si="60"/>
+        <v>5891136.9103124999</v>
+      </c>
+      <c r="V81">
+        <f t="shared" si="61"/>
+        <v>1242633.3727500001</v>
+      </c>
+      <c r="W81">
+        <f t="shared" si="62"/>
+        <v>16403.550000000003</v>
+      </c>
+      <c r="X81">
+        <f t="shared" si="63"/>
+        <v>5046.75</v>
+      </c>
+      <c r="Y81">
+        <f t="shared" si="64"/>
+        <v>7328321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>78</v>
       </c>
@@ -6522,8 +7961,84 @@
       <c r="D82">
         <v>5451200</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E82">
+        <f t="shared" si="84"/>
+        <v>6957.5</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="85"/>
+        <v>3368.5</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="86"/>
+        <v>3368.5</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="87"/>
+        <v>3550.75</v>
+      </c>
+      <c r="J82" s="3">
+        <f t="shared" si="70"/>
+        <v>69655</v>
+      </c>
+      <c r="K82" s="3">
+        <f t="shared" si="71"/>
+        <v>16922.5</v>
+      </c>
+      <c r="L82" s="3">
+        <f t="shared" si="72"/>
+        <v>17393.75</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="73"/>
+        <v>9431.7999999999993</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="74"/>
+        <v>8349</v>
+      </c>
+      <c r="O82">
+        <f t="shared" si="75"/>
+        <v>6400.1500000000005</v>
+      </c>
+      <c r="P82">
+        <f t="shared" si="76"/>
+        <v>8885.75</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="77"/>
+        <v>7073.85</v>
+      </c>
+      <c r="R82">
+        <f t="shared" si="78"/>
+        <v>10999.7</v>
+      </c>
+      <c r="T82">
+        <f t="shared" si="59"/>
+        <v>174999.3064875</v>
+      </c>
+      <c r="U82">
+        <f t="shared" si="60"/>
+        <v>5959128.2728125006</v>
+      </c>
+      <c r="V82">
+        <f t="shared" si="61"/>
+        <v>1257129.25275</v>
+      </c>
+      <c r="W82">
+        <f t="shared" si="62"/>
+        <v>16499.550000000003</v>
+      </c>
+      <c r="X82">
+        <f t="shared" si="63"/>
+        <v>5076.75</v>
+      </c>
+      <c r="Y82">
+        <f t="shared" si="64"/>
+        <v>7412833</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>79</v>
       </c>
@@ -6536,8 +8051,84 @@
       <c r="D83">
         <v>5735100</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E83">
+        <f t="shared" si="84"/>
+        <v>6997.5</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="85"/>
+        <v>3388.5</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="86"/>
+        <v>3388.5</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="87"/>
+        <v>3570.75</v>
+      </c>
+      <c r="J83" s="3">
+        <f t="shared" si="70"/>
+        <v>70055</v>
+      </c>
+      <c r="K83" s="3">
+        <f t="shared" si="71"/>
+        <v>17022.5</v>
+      </c>
+      <c r="L83" s="3">
+        <f t="shared" si="72"/>
+        <v>17493.75</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="73"/>
+        <v>9487.7999999999993</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="74"/>
+        <v>8397</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="75"/>
+        <v>6438.1500000000005</v>
+      </c>
+      <c r="P83">
+        <f t="shared" si="76"/>
+        <v>8935.75</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="77"/>
+        <v>7115.85</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="78"/>
+        <v>11063.7</v>
+      </c>
+      <c r="T83">
+        <f t="shared" si="59"/>
+        <v>176907.96498749999</v>
+      </c>
+      <c r="U83">
+        <f t="shared" si="60"/>
+        <v>6027509.6353125004</v>
+      </c>
+      <c r="V83">
+        <f t="shared" si="61"/>
+        <v>1271709.1327500001</v>
+      </c>
+      <c r="W83">
+        <f t="shared" si="62"/>
+        <v>16595.550000000003</v>
+      </c>
+      <c r="X83">
+        <f t="shared" si="63"/>
+        <v>5106.75</v>
+      </c>
+      <c r="Y83">
+        <f t="shared" si="64"/>
+        <v>7497829</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>80</v>
       </c>
@@ -6550,8 +8141,84 @@
       <c r="D84">
         <v>6019000</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E84">
+        <f>E83*1.5</f>
+        <v>10496.25</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ref="F84" si="88">F83*1.5</f>
+        <v>5082.75</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ref="G84" si="89">G83*1.5</f>
+        <v>5082.75</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ref="H84" si="90">H83*1.5</f>
+        <v>5356.125</v>
+      </c>
+      <c r="J84" s="3">
+        <f t="shared" si="70"/>
+        <v>105042.5</v>
+      </c>
+      <c r="K84" s="3">
+        <f t="shared" si="71"/>
+        <v>25493.75</v>
+      </c>
+      <c r="L84" s="3">
+        <f t="shared" si="72"/>
+        <v>26240.625</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="73"/>
+        <v>14231.699999999999</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="74"/>
+        <v>12595.5</v>
+      </c>
+      <c r="O84">
+        <f t="shared" si="75"/>
+        <v>9657.2250000000004</v>
+      </c>
+      <c r="P84">
+        <f t="shared" si="76"/>
+        <v>13353.625</v>
+      </c>
+      <c r="Q84">
+        <f t="shared" si="77"/>
+        <v>10673.775000000001</v>
+      </c>
+      <c r="R84">
+        <f t="shared" si="78"/>
+        <v>16595.55</v>
+      </c>
+      <c r="T84">
+        <f t="shared" si="59"/>
+        <v>382135.02987187501</v>
+      </c>
+      <c r="U84">
+        <f t="shared" si="60"/>
+        <v>13511306.273203121</v>
+      </c>
+      <c r="V84">
+        <f t="shared" si="61"/>
+        <v>2850671.7736875005</v>
+      </c>
+      <c r="W84">
+        <f t="shared" si="62"/>
+        <v>24893.324999999997</v>
+      </c>
+      <c r="X84">
+        <f t="shared" si="63"/>
+        <v>7648.125</v>
+      </c>
+      <c r="Y84">
+        <f t="shared" si="64"/>
+        <v>16776654</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>81</v>
       </c>
@@ -6564,8 +8231,84 @@
       <c r="D85">
         <v>6302900</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E85">
+        <f t="shared" ref="E85:E93" si="91">E84+40</f>
+        <v>10536.25</v>
+      </c>
+      <c r="F85">
+        <f t="shared" ref="F85:F93" si="92">F84+20</f>
+        <v>5102.75</v>
+      </c>
+      <c r="G85">
+        <f t="shared" ref="G85:G93" si="93">G84+20</f>
+        <v>5102.75</v>
+      </c>
+      <c r="H85">
+        <f t="shared" ref="H85:H93" si="94">H84+20</f>
+        <v>5376.125</v>
+      </c>
+      <c r="J85" s="3">
+        <f t="shared" si="70"/>
+        <v>105442.5</v>
+      </c>
+      <c r="K85" s="3">
+        <f t="shared" si="71"/>
+        <v>25593.75</v>
+      </c>
+      <c r="L85" s="3">
+        <f t="shared" si="72"/>
+        <v>26340.625</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="73"/>
+        <v>14287.699999999999</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="74"/>
+        <v>12643.5</v>
+      </c>
+      <c r="O85">
+        <f t="shared" si="75"/>
+        <v>9695.2250000000004</v>
+      </c>
+      <c r="P85">
+        <f t="shared" si="76"/>
+        <v>13403.625</v>
+      </c>
+      <c r="Q85">
+        <f t="shared" si="77"/>
+        <v>10715.775000000001</v>
+      </c>
+      <c r="R85">
+        <f t="shared" si="78"/>
+        <v>16659.55</v>
+      </c>
+      <c r="T85">
+        <f t="shared" si="59"/>
+        <v>384950.401621875</v>
+      </c>
+      <c r="U85">
+        <f t="shared" si="60"/>
+        <v>13614170.816953123</v>
+      </c>
+      <c r="V85">
+        <f t="shared" si="61"/>
+        <v>2872604.5936875003</v>
+      </c>
+      <c r="W85">
+        <f t="shared" si="62"/>
+        <v>24989.324999999997</v>
+      </c>
+      <c r="X85">
+        <f t="shared" si="63"/>
+        <v>7678.125</v>
+      </c>
+      <c r="Y85">
+        <f t="shared" si="64"/>
+        <v>16904393</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>82</v>
       </c>
@@ -6578,8 +8321,84 @@
       <c r="D86">
         <v>6586800</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E86">
+        <f t="shared" si="91"/>
+        <v>10576.25</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="92"/>
+        <v>5122.75</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="93"/>
+        <v>5122.75</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="94"/>
+        <v>5396.125</v>
+      </c>
+      <c r="J86" s="3">
+        <f t="shared" si="70"/>
+        <v>105842.5</v>
+      </c>
+      <c r="K86" s="3">
+        <f t="shared" si="71"/>
+        <v>25693.75</v>
+      </c>
+      <c r="L86" s="3">
+        <f t="shared" si="72"/>
+        <v>26440.625</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="73"/>
+        <v>14343.699999999999</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="74"/>
+        <v>12691.5</v>
+      </c>
+      <c r="O86">
+        <f t="shared" si="75"/>
+        <v>9733.2250000000004</v>
+      </c>
+      <c r="P86">
+        <f t="shared" si="76"/>
+        <v>13453.625</v>
+      </c>
+      <c r="Q86">
+        <f t="shared" si="77"/>
+        <v>10757.775</v>
+      </c>
+      <c r="R86">
+        <f t="shared" si="78"/>
+        <v>16723.55</v>
+      </c>
+      <c r="T86">
+        <f t="shared" si="59"/>
+        <v>387776.09337187506</v>
+      </c>
+      <c r="U86">
+        <f t="shared" si="60"/>
+        <v>13717425.360703124</v>
+      </c>
+      <c r="V86">
+        <f t="shared" si="61"/>
+        <v>2894621.4136874997</v>
+      </c>
+      <c r="W86">
+        <f t="shared" si="62"/>
+        <v>25085.324999999997</v>
+      </c>
+      <c r="X86">
+        <f t="shared" si="63"/>
+        <v>7708.125</v>
+      </c>
+      <c r="Y86">
+        <f t="shared" si="64"/>
+        <v>17032616</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>83</v>
       </c>
@@ -6592,8 +8411,84 @@
       <c r="D87">
         <v>6870700</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E87">
+        <f t="shared" si="91"/>
+        <v>10616.25</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="92"/>
+        <v>5142.75</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="93"/>
+        <v>5142.75</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="94"/>
+        <v>5416.125</v>
+      </c>
+      <c r="J87" s="3">
+        <f t="shared" si="70"/>
+        <v>106242.5</v>
+      </c>
+      <c r="K87" s="3">
+        <f t="shared" si="71"/>
+        <v>25793.75</v>
+      </c>
+      <c r="L87" s="3">
+        <f t="shared" si="72"/>
+        <v>26540.625</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="73"/>
+        <v>14399.699999999999</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="74"/>
+        <v>12739.5</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="75"/>
+        <v>9771.2250000000004</v>
+      </c>
+      <c r="P87">
+        <f t="shared" si="76"/>
+        <v>13503.625</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="77"/>
+        <v>10799.775</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="78"/>
+        <v>16787.55</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="59"/>
+        <v>390612.10512187501</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="60"/>
+        <v>13821069.904453123</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="61"/>
+        <v>2916722.2336874995</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="62"/>
+        <v>25181.324999999997</v>
+      </c>
+      <c r="X87">
+        <f t="shared" si="63"/>
+        <v>7738.125</v>
+      </c>
+      <c r="Y87">
+        <f t="shared" si="64"/>
+        <v>17161323</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84</v>
       </c>
@@ -6606,8 +8501,84 @@
       <c r="D88">
         <v>7154600</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E88">
+        <f t="shared" si="91"/>
+        <v>10656.25</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="92"/>
+        <v>5162.75</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="93"/>
+        <v>5162.75</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="94"/>
+        <v>5436.125</v>
+      </c>
+      <c r="J88" s="3">
+        <f t="shared" si="70"/>
+        <v>106642.5</v>
+      </c>
+      <c r="K88" s="3">
+        <f t="shared" si="71"/>
+        <v>25893.75</v>
+      </c>
+      <c r="L88" s="3">
+        <f t="shared" si="72"/>
+        <v>26640.625</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="73"/>
+        <v>14455.699999999999</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="74"/>
+        <v>12787.5</v>
+      </c>
+      <c r="O88">
+        <f t="shared" si="75"/>
+        <v>9809.2250000000004</v>
+      </c>
+      <c r="P88">
+        <f t="shared" si="76"/>
+        <v>13553.625</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" si="77"/>
+        <v>10841.775</v>
+      </c>
+      <c r="R88">
+        <f t="shared" si="78"/>
+        <v>16851.55</v>
+      </c>
+      <c r="T88">
+        <f t="shared" si="59"/>
+        <v>393458.43687187496</v>
+      </c>
+      <c r="U88">
+        <f t="shared" si="60"/>
+        <v>13925104.448203124</v>
+      </c>
+      <c r="V88">
+        <f t="shared" si="61"/>
+        <v>2938907.0536874998</v>
+      </c>
+      <c r="W88">
+        <f t="shared" si="62"/>
+        <v>25277.324999999997</v>
+      </c>
+      <c r="X88">
+        <f t="shared" si="63"/>
+        <v>7768.125</v>
+      </c>
+      <c r="Y88">
+        <f t="shared" si="64"/>
+        <v>17290515</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>85</v>
       </c>
@@ -6620,8 +8591,84 @@
       <c r="D89">
         <v>7438500</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E89">
+        <f t="shared" si="91"/>
+        <v>10696.25</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="92"/>
+        <v>5182.75</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="93"/>
+        <v>5182.75</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="94"/>
+        <v>5456.125</v>
+      </c>
+      <c r="J89" s="3">
+        <f t="shared" si="70"/>
+        <v>107042.5</v>
+      </c>
+      <c r="K89" s="3">
+        <f t="shared" si="71"/>
+        <v>25993.75</v>
+      </c>
+      <c r="L89" s="3">
+        <f t="shared" si="72"/>
+        <v>26740.625</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="73"/>
+        <v>14511.699999999999</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="74"/>
+        <v>12835.5</v>
+      </c>
+      <c r="O89">
+        <f t="shared" si="75"/>
+        <v>9847.2250000000004</v>
+      </c>
+      <c r="P89">
+        <f t="shared" si="76"/>
+        <v>13603.625</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="77"/>
+        <v>10883.775</v>
+      </c>
+      <c r="R89">
+        <f t="shared" si="78"/>
+        <v>16915.55</v>
+      </c>
+      <c r="T89">
+        <f t="shared" si="59"/>
+        <v>396315.08862187492</v>
+      </c>
+      <c r="U89">
+        <f t="shared" si="60"/>
+        <v>14029528.991953123</v>
+      </c>
+      <c r="V89">
+        <f t="shared" si="61"/>
+        <v>2961175.8736874997</v>
+      </c>
+      <c r="W89">
+        <f t="shared" si="62"/>
+        <v>25373.324999999997</v>
+      </c>
+      <c r="X89">
+        <f t="shared" si="63"/>
+        <v>7798.125</v>
+      </c>
+      <c r="Y89">
+        <f t="shared" si="64"/>
+        <v>17420191</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>86</v>
       </c>
@@ -6634,8 +8681,84 @@
       <c r="D90">
         <v>7722400</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E90">
+        <f t="shared" si="91"/>
+        <v>10736.25</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="92"/>
+        <v>5202.75</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="93"/>
+        <v>5202.75</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="94"/>
+        <v>5476.125</v>
+      </c>
+      <c r="J90" s="3">
+        <f t="shared" si="70"/>
+        <v>107442.5</v>
+      </c>
+      <c r="K90" s="3">
+        <f t="shared" si="71"/>
+        <v>26093.75</v>
+      </c>
+      <c r="L90" s="3">
+        <f t="shared" si="72"/>
+        <v>26840.625</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="73"/>
+        <v>14567.699999999999</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="74"/>
+        <v>12883.5</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="75"/>
+        <v>9885.2250000000004</v>
+      </c>
+      <c r="P90">
+        <f t="shared" si="76"/>
+        <v>13653.625</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="77"/>
+        <v>10925.775</v>
+      </c>
+      <c r="R90">
+        <f t="shared" si="78"/>
+        <v>16979.55</v>
+      </c>
+      <c r="T90">
+        <f t="shared" si="59"/>
+        <v>399182.06037187501</v>
+      </c>
+      <c r="U90">
+        <f t="shared" si="60"/>
+        <v>14134343.535703123</v>
+      </c>
+      <c r="V90">
+        <f t="shared" si="61"/>
+        <v>2983528.6936875</v>
+      </c>
+      <c r="W90">
+        <f t="shared" si="62"/>
+        <v>25469.324999999997</v>
+      </c>
+      <c r="X90">
+        <f t="shared" si="63"/>
+        <v>7828.125</v>
+      </c>
+      <c r="Y90">
+        <f t="shared" si="64"/>
+        <v>17550351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>87</v>
       </c>
@@ -6648,8 +8771,84 @@
       <c r="D91">
         <v>8006300</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E91">
+        <f t="shared" si="91"/>
+        <v>10776.25</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="92"/>
+        <v>5222.75</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="93"/>
+        <v>5222.75</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="94"/>
+        <v>5496.125</v>
+      </c>
+      <c r="J91" s="3">
+        <f t="shared" si="70"/>
+        <v>107842.5</v>
+      </c>
+      <c r="K91" s="3">
+        <f t="shared" si="71"/>
+        <v>26193.75</v>
+      </c>
+      <c r="L91" s="3">
+        <f t="shared" si="72"/>
+        <v>26940.625</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="73"/>
+        <v>14623.699999999999</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="74"/>
+        <v>12931.5</v>
+      </c>
+      <c r="O91">
+        <f t="shared" si="75"/>
+        <v>9923.2250000000004</v>
+      </c>
+      <c r="P91">
+        <f t="shared" si="76"/>
+        <v>13703.625</v>
+      </c>
+      <c r="Q91">
+        <f t="shared" si="77"/>
+        <v>10967.775</v>
+      </c>
+      <c r="R91">
+        <f t="shared" si="78"/>
+        <v>17043.55</v>
+      </c>
+      <c r="T91">
+        <f t="shared" si="59"/>
+        <v>402059.35212187504</v>
+      </c>
+      <c r="U91">
+        <f t="shared" si="60"/>
+        <v>14239548.079453122</v>
+      </c>
+      <c r="V91">
+        <f t="shared" si="61"/>
+        <v>3005965.5136874998</v>
+      </c>
+      <c r="W91">
+        <f t="shared" si="62"/>
+        <v>25565.324999999997</v>
+      </c>
+      <c r="X91">
+        <f t="shared" si="63"/>
+        <v>7858.125</v>
+      </c>
+      <c r="Y91">
+        <f t="shared" si="64"/>
+        <v>17680996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>88</v>
       </c>
@@ -6662,8 +8861,84 @@
       <c r="D92">
         <v>8290200</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E92">
+        <f t="shared" si="91"/>
+        <v>10816.25</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="92"/>
+        <v>5242.75</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="93"/>
+        <v>5242.75</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="94"/>
+        <v>5516.125</v>
+      </c>
+      <c r="J92" s="3">
+        <f t="shared" si="70"/>
+        <v>108242.5</v>
+      </c>
+      <c r="K92" s="3">
+        <f t="shared" si="71"/>
+        <v>26293.75</v>
+      </c>
+      <c r="L92" s="3">
+        <f t="shared" si="72"/>
+        <v>27040.625</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="73"/>
+        <v>14679.699999999999</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="74"/>
+        <v>12979.5</v>
+      </c>
+      <c r="O92">
+        <f t="shared" si="75"/>
+        <v>9961.2250000000004</v>
+      </c>
+      <c r="P92">
+        <f t="shared" si="76"/>
+        <v>13753.625</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="77"/>
+        <v>11009.775</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="78"/>
+        <v>17107.55</v>
+      </c>
+      <c r="T92">
+        <f t="shared" si="59"/>
+        <v>404946.96387187502</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="60"/>
+        <v>14345142.623203121</v>
+      </c>
+      <c r="V92">
+        <f t="shared" si="61"/>
+        <v>3028486.3336874996</v>
+      </c>
+      <c r="W92">
+        <f t="shared" si="62"/>
+        <v>25661.324999999997</v>
+      </c>
+      <c r="X92">
+        <f t="shared" si="63"/>
+        <v>7888.125</v>
+      </c>
+      <c r="Y92">
+        <f t="shared" si="64"/>
+        <v>17812125</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>89</v>
       </c>
@@ -6676,8 +8951,84 @@
       <c r="D93">
         <v>8574100</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E93">
+        <f t="shared" si="91"/>
+        <v>10856.25</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="92"/>
+        <v>5262.75</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="93"/>
+        <v>5262.75</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="94"/>
+        <v>5536.125</v>
+      </c>
+      <c r="J93" s="3">
+        <f t="shared" si="70"/>
+        <v>108642.5</v>
+      </c>
+      <c r="K93" s="3">
+        <f t="shared" si="71"/>
+        <v>26393.75</v>
+      </c>
+      <c r="L93" s="3">
+        <f t="shared" si="72"/>
+        <v>27140.625</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="73"/>
+        <v>14735.699999999999</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="74"/>
+        <v>13027.5</v>
+      </c>
+      <c r="O93">
+        <f t="shared" si="75"/>
+        <v>9999.2250000000004</v>
+      </c>
+      <c r="P93">
+        <f t="shared" si="76"/>
+        <v>13803.625</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="77"/>
+        <v>11051.775</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="78"/>
+        <v>17171.55</v>
+      </c>
+      <c r="T93">
+        <f t="shared" si="59"/>
+        <v>407844.89562187501</v>
+      </c>
+      <c r="U93">
+        <f t="shared" si="60"/>
+        <v>14451127.166953122</v>
+      </c>
+      <c r="V93">
+        <f t="shared" si="61"/>
+        <v>3051091.1536874999</v>
+      </c>
+      <c r="W93">
+        <f t="shared" si="62"/>
+        <v>25757.324999999997</v>
+      </c>
+      <c r="X93">
+        <f t="shared" si="63"/>
+        <v>7918.125</v>
+      </c>
+      <c r="Y93">
+        <f t="shared" si="64"/>
+        <v>17943738</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>90</v>
       </c>
@@ -6689,6 +9040,82 @@
       </c>
       <c r="D94">
         <v>8858000</v>
+      </c>
+      <c r="E94">
+        <f t="shared" ref="E94" si="95">E93+40</f>
+        <v>10896.25</v>
+      </c>
+      <c r="F94">
+        <f t="shared" ref="F94" si="96">F93+20</f>
+        <v>5282.75</v>
+      </c>
+      <c r="G94">
+        <f t="shared" ref="G94" si="97">G93+20</f>
+        <v>5282.75</v>
+      </c>
+      <c r="H94">
+        <f t="shared" ref="H94" si="98">H93+20</f>
+        <v>5556.125</v>
+      </c>
+      <c r="J94" s="3">
+        <f t="shared" si="70"/>
+        <v>109042.5</v>
+      </c>
+      <c r="K94" s="3">
+        <f t="shared" si="71"/>
+        <v>26493.75</v>
+      </c>
+      <c r="L94" s="3">
+        <f t="shared" si="72"/>
+        <v>27240.625</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="73"/>
+        <v>14791.699999999999</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="74"/>
+        <v>13075.5</v>
+      </c>
+      <c r="O94">
+        <f t="shared" si="75"/>
+        <v>10037.225</v>
+      </c>
+      <c r="P94">
+        <f t="shared" si="76"/>
+        <v>13853.625</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="77"/>
+        <v>11093.775</v>
+      </c>
+      <c r="R94">
+        <f t="shared" si="78"/>
+        <v>17235.55</v>
+      </c>
+      <c r="T94">
+        <f t="shared" si="59"/>
+        <v>410753.14737187501</v>
+      </c>
+      <c r="U94">
+        <f t="shared" si="60"/>
+        <v>14557501.710703121</v>
+      </c>
+      <c r="V94">
+        <f t="shared" si="61"/>
+        <v>3073779.9736874998</v>
+      </c>
+      <c r="W94">
+        <f t="shared" si="62"/>
+        <v>25853.324999999997</v>
+      </c>
+      <c r="X94">
+        <f t="shared" si="63"/>
+        <v>7948.125</v>
+      </c>
+      <c r="Y94">
+        <f t="shared" si="64"/>
+        <v>18075836</v>
       </c>
     </row>
   </sheetData>
